--- a/inventario/STOCKINSUMO.xlsx
+++ b/inventario/STOCKINSUMO.xlsx
@@ -14,6 +14,7 @@
     <sheet name="PERDIDAS" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="PRODUCCION" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="COSTOS" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PRECIOS" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="ListaInsumos">INSUMOS!$B$5:$B$67</definedName>
@@ -173,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -227,6 +228,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -630,6 +637,13 @@
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
+          <t>8️⃣  PRECIOS → guardá el precio de venta de cada producto y mirá el IVA y la ganancia real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
           <t>💡 Este panel te muestra qué insumos están bajos o agotados.</t>
         </is>
       </c>
@@ -6372,13 +6386,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E504"/>
+  <dimension ref="A1:F504"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1">
@@ -6424,6 +6439,12 @@
 consumido</t>
         </is>
       </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Costo en el
+producto</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -6447,6 +6468,10 @@
         <f>IFERROR(C5*D5,0)</f>
         <v/>
       </c>
+      <c r="F5" s="10">
+        <f>IF(OR($A5="",$B5=""),"",IFERROR($C5*INDEX(INSUMOS!$K$5:$K$67,MATCH($B5,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -6470,6 +6495,10 @@
         <f>IFERROR(C6*D6,0)</f>
         <v/>
       </c>
+      <c r="F6" s="10">
+        <f>IF(OR($A6="",$B6=""),"",IFERROR($C6*INDEX(INSUMOS!$K$5:$K$67,MATCH($B6,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -6493,6 +6522,10 @@
         <f>IFERROR(C7*D7,0)</f>
         <v/>
       </c>
+      <c r="F7" s="10">
+        <f>IF(OR($A7="",$B7=""),"",IFERROR($C7*INDEX(INSUMOS!$K$5:$K$67,MATCH($B7,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -6516,6 +6549,10 @@
         <f>IFERROR(C8*D8,0)</f>
         <v/>
       </c>
+      <c r="F8" s="10">
+        <f>IF(OR($A8="",$B8=""),"",IFERROR($C8*INDEX(INSUMOS!$K$5:$K$67,MATCH($B8,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -6539,6 +6576,10 @@
         <f>IFERROR(C9*D9,0)</f>
         <v/>
       </c>
+      <c r="F9" s="10">
+        <f>IF(OR($A9="",$B9=""),"",IFERROR($C9*INDEX(INSUMOS!$K$5:$K$67,MATCH($B9,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -6562,6 +6603,10 @@
         <f>IFERROR(C10*D10,0)</f>
         <v/>
       </c>
+      <c r="F10" s="10">
+        <f>IF(OR($A10="",$B10=""),"",IFERROR($C10*INDEX(INSUMOS!$K$5:$K$67,MATCH($B10,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -6585,6 +6630,10 @@
         <f>IFERROR(C11*D11,0)</f>
         <v/>
       </c>
+      <c r="F11" s="10">
+        <f>IF(OR($A11="",$B11=""),"",IFERROR($C11*INDEX(INSUMOS!$K$5:$K$67,MATCH($B11,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -6608,6 +6657,10 @@
         <f>IFERROR(C12*D12,0)</f>
         <v/>
       </c>
+      <c r="F12" s="10">
+        <f>IF(OR($A12="",$B12=""),"",IFERROR($C12*INDEX(INSUMOS!$K$5:$K$67,MATCH($B12,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -6631,6 +6684,10 @@
         <f>IFERROR(C13*D13,0)</f>
         <v/>
       </c>
+      <c r="F13" s="10">
+        <f>IF(OR($A13="",$B13=""),"",IFERROR($C13*INDEX(INSUMOS!$K$5:$K$67,MATCH($B13,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -6654,6 +6711,10 @@
         <f>IFERROR(C14*D14,0)</f>
         <v/>
       </c>
+      <c r="F14" s="10">
+        <f>IF(OR($A14="",$B14=""),"",IFERROR($C14*INDEX(INSUMOS!$K$5:$K$67,MATCH($B14,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -6677,6 +6738,10 @@
         <f>IFERROR(C15*D15,0)</f>
         <v/>
       </c>
+      <c r="F15" s="10">
+        <f>IF(OR($A15="",$B15=""),"",IFERROR($C15*INDEX(INSUMOS!$K$5:$K$67,MATCH($B15,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -6700,6 +6765,10 @@
         <f>IFERROR(C16*D16,0)</f>
         <v/>
       </c>
+      <c r="F16" s="10">
+        <f>IF(OR($A16="",$B16=""),"",IFERROR($C16*INDEX(INSUMOS!$K$5:$K$67,MATCH($B16,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -6723,6 +6792,10 @@
         <f>IFERROR(C17*D17,0)</f>
         <v/>
       </c>
+      <c r="F17" s="10">
+        <f>IF(OR($A17="",$B17=""),"",IFERROR($C17*INDEX(INSUMOS!$K$5:$K$67,MATCH($B17,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -6746,6 +6819,10 @@
         <f>IFERROR(C18*D18,0)</f>
         <v/>
       </c>
+      <c r="F18" s="10">
+        <f>IF(OR($A18="",$B18=""),"",IFERROR($C18*INDEX(INSUMOS!$K$5:$K$67,MATCH($B18,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -6769,6 +6846,10 @@
         <f>IFERROR(C19*D19,0)</f>
         <v/>
       </c>
+      <c r="F19" s="10">
+        <f>IF(OR($A19="",$B19=""),"",IFERROR($C19*INDEX(INSUMOS!$K$5:$K$67,MATCH($B19,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -6792,6 +6873,10 @@
         <f>IFERROR(C20*D20,0)</f>
         <v/>
       </c>
+      <c r="F20" s="10">
+        <f>IF(OR($A20="",$B20=""),"",IFERROR($C20*INDEX(INSUMOS!$K$5:$K$67,MATCH($B20,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -6815,6 +6900,10 @@
         <f>IFERROR(C21*D21,0)</f>
         <v/>
       </c>
+      <c r="F21" s="10">
+        <f>IF(OR($A21="",$B21=""),"",IFERROR($C21*INDEX(INSUMOS!$K$5:$K$67,MATCH($B21,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -6838,6 +6927,10 @@
         <f>IFERROR(C22*D22,0)</f>
         <v/>
       </c>
+      <c r="F22" s="10">
+        <f>IF(OR($A22="",$B22=""),"",IFERROR($C22*INDEX(INSUMOS!$K$5:$K$67,MATCH($B22,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -6861,6 +6954,10 @@
         <f>IFERROR(C23*D23,0)</f>
         <v/>
       </c>
+      <c r="F23" s="10">
+        <f>IF(OR($A23="",$B23=""),"",IFERROR($C23*INDEX(INSUMOS!$K$5:$K$67,MATCH($B23,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -6884,6 +6981,10 @@
         <f>IFERROR(C24*D24,0)</f>
         <v/>
       </c>
+      <c r="F24" s="10">
+        <f>IF(OR($A24="",$B24=""),"",IFERROR($C24*INDEX(INSUMOS!$K$5:$K$67,MATCH($B24,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -6907,6 +7008,10 @@
         <f>IFERROR(C25*D25,0)</f>
         <v/>
       </c>
+      <c r="F25" s="10">
+        <f>IF(OR($A25="",$B25=""),"",IFERROR($C25*INDEX(INSUMOS!$K$5:$K$67,MATCH($B25,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -6930,6 +7035,10 @@
         <f>IFERROR(C26*D26,0)</f>
         <v/>
       </c>
+      <c r="F26" s="10">
+        <f>IF(OR($A26="",$B26=""),"",IFERROR($C26*INDEX(INSUMOS!$K$5:$K$67,MATCH($B26,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -6953,6 +7062,10 @@
         <f>IFERROR(C27*D27,0)</f>
         <v/>
       </c>
+      <c r="F27" s="10">
+        <f>IF(OR($A27="",$B27=""),"",IFERROR($C27*INDEX(INSUMOS!$K$5:$K$67,MATCH($B27,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -6976,6 +7089,10 @@
         <f>IFERROR(C28*D28,0)</f>
         <v/>
       </c>
+      <c r="F28" s="10">
+        <f>IF(OR($A28="",$B28=""),"",IFERROR($C28*INDEX(INSUMOS!$K$5:$K$67,MATCH($B28,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -6999,6 +7116,10 @@
         <f>IFERROR(C29*D29,0)</f>
         <v/>
       </c>
+      <c r="F29" s="10">
+        <f>IF(OR($A29="",$B29=""),"",IFERROR($C29*INDEX(INSUMOS!$K$5:$K$67,MATCH($B29,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -7022,6 +7143,10 @@
         <f>IFERROR(C30*D30,0)</f>
         <v/>
       </c>
+      <c r="F30" s="10">
+        <f>IF(OR($A30="",$B30=""),"",IFERROR($C30*INDEX(INSUMOS!$K$5:$K$67,MATCH($B30,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -7045,6 +7170,10 @@
         <f>IFERROR(C31*D31,0)</f>
         <v/>
       </c>
+      <c r="F31" s="10">
+        <f>IF(OR($A31="",$B31=""),"",IFERROR($C31*INDEX(INSUMOS!$K$5:$K$67,MATCH($B31,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -7068,6 +7197,10 @@
         <f>IFERROR(C32*D32,0)</f>
         <v/>
       </c>
+      <c r="F32" s="10">
+        <f>IF(OR($A32="",$B32=""),"",IFERROR($C32*INDEX(INSUMOS!$K$5:$K$67,MATCH($B32,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -7091,6 +7224,10 @@
         <f>IFERROR(C33*D33,0)</f>
         <v/>
       </c>
+      <c r="F33" s="10">
+        <f>IF(OR($A33="",$B33=""),"",IFERROR($C33*INDEX(INSUMOS!$K$5:$K$67,MATCH($B33,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -7114,6 +7251,10 @@
         <f>IFERROR(C34*D34,0)</f>
         <v/>
       </c>
+      <c r="F34" s="10">
+        <f>IF(OR($A34="",$B34=""),"",IFERROR($C34*INDEX(INSUMOS!$K$5:$K$67,MATCH($B34,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -7137,6 +7278,10 @@
         <f>IFERROR(C35*D35,0)</f>
         <v/>
       </c>
+      <c r="F35" s="10">
+        <f>IF(OR($A35="",$B35=""),"",IFERROR($C35*INDEX(INSUMOS!$K$5:$K$67,MATCH($B35,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -7160,6 +7305,10 @@
         <f>IFERROR(C36*D36,0)</f>
         <v/>
       </c>
+      <c r="F36" s="10">
+        <f>IF(OR($A36="",$B36=""),"",IFERROR($C36*INDEX(INSUMOS!$K$5:$K$67,MATCH($B36,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -7183,6 +7332,10 @@
         <f>IFERROR(C37*D37,0)</f>
         <v/>
       </c>
+      <c r="F37" s="10">
+        <f>IF(OR($A37="",$B37=""),"",IFERROR($C37*INDEX(INSUMOS!$K$5:$K$67,MATCH($B37,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -7206,6 +7359,10 @@
         <f>IFERROR(C38*D38,0)</f>
         <v/>
       </c>
+      <c r="F38" s="10">
+        <f>IF(OR($A38="",$B38=""),"",IFERROR($C38*INDEX(INSUMOS!$K$5:$K$67,MATCH($B38,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -7229,6 +7386,10 @@
         <f>IFERROR(C39*D39,0)</f>
         <v/>
       </c>
+      <c r="F39" s="10">
+        <f>IF(OR($A39="",$B39=""),"",IFERROR($C39*INDEX(INSUMOS!$K$5:$K$67,MATCH($B39,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -7252,6 +7413,10 @@
         <f>IFERROR(C40*D40,0)</f>
         <v/>
       </c>
+      <c r="F40" s="10">
+        <f>IF(OR($A40="",$B40=""),"",IFERROR($C40*INDEX(INSUMOS!$K$5:$K$67,MATCH($B40,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -7275,6 +7440,10 @@
         <f>IFERROR(C41*D41,0)</f>
         <v/>
       </c>
+      <c r="F41" s="10">
+        <f>IF(OR($A41="",$B41=""),"",IFERROR($C41*INDEX(INSUMOS!$K$5:$K$67,MATCH($B41,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -7298,6 +7467,10 @@
         <f>IFERROR(C42*D42,0)</f>
         <v/>
       </c>
+      <c r="F42" s="10">
+        <f>IF(OR($A42="",$B42=""),"",IFERROR($C42*INDEX(INSUMOS!$K$5:$K$67,MATCH($B42,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -7321,6 +7494,10 @@
         <f>IFERROR(C43*D43,0)</f>
         <v/>
       </c>
+      <c r="F43" s="10">
+        <f>IF(OR($A43="",$B43=""),"",IFERROR($C43*INDEX(INSUMOS!$K$5:$K$67,MATCH($B43,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -7344,6 +7521,10 @@
         <f>IFERROR(C44*D44,0)</f>
         <v/>
       </c>
+      <c r="F44" s="10">
+        <f>IF(OR($A44="",$B44=""),"",IFERROR($C44*INDEX(INSUMOS!$K$5:$K$67,MATCH($B44,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
@@ -7367,6 +7548,10 @@
         <f>IFERROR(C45*D45,0)</f>
         <v/>
       </c>
+      <c r="F45" s="10">
+        <f>IF(OR($A45="",$B45=""),"",IFERROR($C45*INDEX(INSUMOS!$K$5:$K$67,MATCH($B45,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
@@ -7390,6 +7575,10 @@
         <f>IFERROR(C46*D46,0)</f>
         <v/>
       </c>
+      <c r="F46" s="10">
+        <f>IF(OR($A46="",$B46=""),"",IFERROR($C46*INDEX(INSUMOS!$K$5:$K$67,MATCH($B46,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
@@ -7413,6 +7602,10 @@
         <f>IFERROR(C47*D47,0)</f>
         <v/>
       </c>
+      <c r="F47" s="10">
+        <f>IF(OR($A47="",$B47=""),"",IFERROR($C47*INDEX(INSUMOS!$K$5:$K$67,MATCH($B47,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
@@ -7436,6 +7629,10 @@
         <f>IFERROR(C48*D48,0)</f>
         <v/>
       </c>
+      <c r="F48" s="10">
+        <f>IF(OR($A48="",$B48=""),"",IFERROR($C48*INDEX(INSUMOS!$K$5:$K$67,MATCH($B48,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -7459,6 +7656,10 @@
         <f>IFERROR(C49*D49,0)</f>
         <v/>
       </c>
+      <c r="F49" s="10">
+        <f>IF(OR($A49="",$B49=""),"",IFERROR($C49*INDEX(INSUMOS!$K$5:$K$67,MATCH($B49,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
@@ -7482,6 +7683,10 @@
         <f>IFERROR(C50*D50,0)</f>
         <v/>
       </c>
+      <c r="F50" s="10">
+        <f>IF(OR($A50="",$B50=""),"",IFERROR($C50*INDEX(INSUMOS!$K$5:$K$67,MATCH($B50,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
@@ -7505,6 +7710,10 @@
         <f>IFERROR(C51*D51,0)</f>
         <v/>
       </c>
+      <c r="F51" s="10">
+        <f>IF(OR($A51="",$B51=""),"",IFERROR($C51*INDEX(INSUMOS!$K$5:$K$67,MATCH($B51,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
@@ -7528,6 +7737,10 @@
         <f>IFERROR(C52*D52,0)</f>
         <v/>
       </c>
+      <c r="F52" s="10">
+        <f>IF(OR($A52="",$B52=""),"",IFERROR($C52*INDEX(INSUMOS!$K$5:$K$67,MATCH($B52,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
@@ -7551,6 +7764,10 @@
         <f>IFERROR(C53*D53,0)</f>
         <v/>
       </c>
+      <c r="F53" s="10">
+        <f>IF(OR($A53="",$B53=""),"",IFERROR($C53*INDEX(INSUMOS!$K$5:$K$67,MATCH($B53,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
@@ -7574,6 +7791,10 @@
         <f>IFERROR(C54*D54,0)</f>
         <v/>
       </c>
+      <c r="F54" s="10">
+        <f>IF(OR($A54="",$B54=""),"",IFERROR($C54*INDEX(INSUMOS!$K$5:$K$67,MATCH($B54,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
@@ -7597,6 +7818,10 @@
         <f>IFERROR(C55*D55,0)</f>
         <v/>
       </c>
+      <c r="F55" s="10">
+        <f>IF(OR($A55="",$B55=""),"",IFERROR($C55*INDEX(INSUMOS!$K$5:$K$67,MATCH($B55,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -7620,6 +7845,10 @@
         <f>IFERROR(C56*D56,0)</f>
         <v/>
       </c>
+      <c r="F56" s="10">
+        <f>IF(OR($A56="",$B56=""),"",IFERROR($C56*INDEX(INSUMOS!$K$5:$K$67,MATCH($B56,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -7643,6 +7872,10 @@
         <f>IFERROR(C57*D57,0)</f>
         <v/>
       </c>
+      <c r="F57" s="10">
+        <f>IF(OR($A57="",$B57=""),"",IFERROR($C57*INDEX(INSUMOS!$K$5:$K$67,MATCH($B57,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
@@ -7666,6 +7899,10 @@
         <f>IFERROR(C58*D58,0)</f>
         <v/>
       </c>
+      <c r="F58" s="10">
+        <f>IF(OR($A58="",$B58=""),"",IFERROR($C58*INDEX(INSUMOS!$K$5:$K$67,MATCH($B58,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
@@ -7689,6 +7926,10 @@
         <f>IFERROR(C59*D59,0)</f>
         <v/>
       </c>
+      <c r="F59" s="10">
+        <f>IF(OR($A59="",$B59=""),"",IFERROR($C59*INDEX(INSUMOS!$K$5:$K$67,MATCH($B59,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
@@ -7712,6 +7953,10 @@
         <f>IFERROR(C60*D60,0)</f>
         <v/>
       </c>
+      <c r="F60" s="10">
+        <f>IF(OR($A60="",$B60=""),"",IFERROR($C60*INDEX(INSUMOS!$K$5:$K$67,MATCH($B60,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
@@ -7735,6 +7980,10 @@
         <f>IFERROR(C61*D61,0)</f>
         <v/>
       </c>
+      <c r="F61" s="10">
+        <f>IF(OR($A61="",$B61=""),"",IFERROR($C61*INDEX(INSUMOS!$K$5:$K$67,MATCH($B61,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
@@ -7758,6 +8007,10 @@
         <f>IFERROR(C62*D62,0)</f>
         <v/>
       </c>
+      <c r="F62" s="10">
+        <f>IF(OR($A62="",$B62=""),"",IFERROR($C62*INDEX(INSUMOS!$K$5:$K$67,MATCH($B62,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
@@ -7781,6 +8034,10 @@
         <f>IFERROR(C63*D63,0)</f>
         <v/>
       </c>
+      <c r="F63" s="10">
+        <f>IF(OR($A63="",$B63=""),"",IFERROR($C63*INDEX(INSUMOS!$K$5:$K$67,MATCH($B63,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
@@ -7804,6 +8061,10 @@
         <f>IFERROR(C64*D64,0)</f>
         <v/>
       </c>
+      <c r="F64" s="10">
+        <f>IF(OR($A64="",$B64=""),"",IFERROR($C64*INDEX(INSUMOS!$K$5:$K$67,MATCH($B64,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
@@ -7827,6 +8088,10 @@
         <f>IFERROR(C65*D65,0)</f>
         <v/>
       </c>
+      <c r="F65" s="10">
+        <f>IF(OR($A65="",$B65=""),"",IFERROR($C65*INDEX(INSUMOS!$K$5:$K$67,MATCH($B65,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
@@ -7850,6 +8115,10 @@
         <f>IFERROR(C66*D66,0)</f>
         <v/>
       </c>
+      <c r="F66" s="10">
+        <f>IF(OR($A66="",$B66=""),"",IFERROR($C66*INDEX(INSUMOS!$K$5:$K$67,MATCH($B66,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
@@ -7873,6 +8142,10 @@
         <f>IFERROR(C67*D67,0)</f>
         <v/>
       </c>
+      <c r="F67" s="10">
+        <f>IF(OR($A67="",$B67=""),"",IFERROR($C67*INDEX(INSUMOS!$K$5:$K$67,MATCH($B67,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
@@ -7896,6 +8169,10 @@
         <f>IFERROR(C68*D68,0)</f>
         <v/>
       </c>
+      <c r="F68" s="10">
+        <f>IF(OR($A68="",$B68=""),"",IFERROR($C68*INDEX(INSUMOS!$K$5:$K$67,MATCH($B68,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
@@ -7919,6 +8196,10 @@
         <f>IFERROR(C69*D69,0)</f>
         <v/>
       </c>
+      <c r="F69" s="10">
+        <f>IF(OR($A69="",$B69=""),"",IFERROR($C69*INDEX(INSUMOS!$K$5:$K$67,MATCH($B69,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
@@ -7942,6 +8223,10 @@
         <f>IFERROR(C70*D70,0)</f>
         <v/>
       </c>
+      <c r="F70" s="10">
+        <f>IF(OR($A70="",$B70=""),"",IFERROR($C70*INDEX(INSUMOS!$K$5:$K$67,MATCH($B70,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
@@ -7965,6 +8250,10 @@
         <f>IFERROR(C71*D71,0)</f>
         <v/>
       </c>
+      <c r="F71" s="10">
+        <f>IF(OR($A71="",$B71=""),"",IFERROR($C71*INDEX(INSUMOS!$K$5:$K$67,MATCH($B71,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
@@ -7988,6 +8277,10 @@
         <f>IFERROR(C72*D72,0)</f>
         <v/>
       </c>
+      <c r="F72" s="10">
+        <f>IF(OR($A72="",$B72=""),"",IFERROR($C72*INDEX(INSUMOS!$K$5:$K$67,MATCH($B72,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
@@ -8011,6 +8304,10 @@
         <f>IFERROR(C73*D73,0)</f>
         <v/>
       </c>
+      <c r="F73" s="10">
+        <f>IF(OR($A73="",$B73=""),"",IFERROR($C73*INDEX(INSUMOS!$K$5:$K$67,MATCH($B73,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
@@ -8034,6 +8331,10 @@
         <f>IFERROR(C74*D74,0)</f>
         <v/>
       </c>
+      <c r="F74" s="10">
+        <f>IF(OR($A74="",$B74=""),"",IFERROR($C74*INDEX(INSUMOS!$K$5:$K$67,MATCH($B74,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
@@ -8057,6 +8358,10 @@
         <f>IFERROR(C75*D75,0)</f>
         <v/>
       </c>
+      <c r="F75" s="10">
+        <f>IF(OR($A75="",$B75=""),"",IFERROR($C75*INDEX(INSUMOS!$K$5:$K$67,MATCH($B75,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
@@ -8080,6 +8385,10 @@
         <f>IFERROR(C76*D76,0)</f>
         <v/>
       </c>
+      <c r="F76" s="10">
+        <f>IF(OR($A76="",$B76=""),"",IFERROR($C76*INDEX(INSUMOS!$K$5:$K$67,MATCH($B76,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
@@ -8103,6 +8412,10 @@
         <f>IFERROR(C77*D77,0)</f>
         <v/>
       </c>
+      <c r="F77" s="10">
+        <f>IF(OR($A77="",$B77=""),"",IFERROR($C77*INDEX(INSUMOS!$K$5:$K$67,MATCH($B77,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
@@ -8126,6 +8439,10 @@
         <f>IFERROR(C78*D78,0)</f>
         <v/>
       </c>
+      <c r="F78" s="10">
+        <f>IF(OR($A78="",$B78=""),"",IFERROR($C78*INDEX(INSUMOS!$K$5:$K$67,MATCH($B78,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
@@ -8149,6 +8466,10 @@
         <f>IFERROR(C79*D79,0)</f>
         <v/>
       </c>
+      <c r="F79" s="10">
+        <f>IF(OR($A79="",$B79=""),"",IFERROR($C79*INDEX(INSUMOS!$K$5:$K$67,MATCH($B79,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
@@ -8172,6 +8493,10 @@
         <f>IFERROR(C80*D80,0)</f>
         <v/>
       </c>
+      <c r="F80" s="10">
+        <f>IF(OR($A80="",$B80=""),"",IFERROR($C80*INDEX(INSUMOS!$K$5:$K$67,MATCH($B80,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -8195,6 +8520,10 @@
         <f>IFERROR(C81*D81,0)</f>
         <v/>
       </c>
+      <c r="F81" s="10">
+        <f>IF(OR($A81="",$B81=""),"",IFERROR($C81*INDEX(INSUMOS!$K$5:$K$67,MATCH($B81,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
@@ -8218,6 +8547,10 @@
         <f>IFERROR(C82*D82,0)</f>
         <v/>
       </c>
+      <c r="F82" s="10">
+        <f>IF(OR($A82="",$B82=""),"",IFERROR($C82*INDEX(INSUMOS!$K$5:$K$67,MATCH($B82,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
@@ -8241,6 +8574,10 @@
         <f>IFERROR(C83*D83,0)</f>
         <v/>
       </c>
+      <c r="F83" s="10">
+        <f>IF(OR($A83="",$B83=""),"",IFERROR($C83*INDEX(INSUMOS!$K$5:$K$67,MATCH($B83,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
@@ -8264,6 +8601,10 @@
         <f>IFERROR(C84*D84,0)</f>
         <v/>
       </c>
+      <c r="F84" s="10">
+        <f>IF(OR($A84="",$B84=""),"",IFERROR($C84*INDEX(INSUMOS!$K$5:$K$67,MATCH($B84,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
@@ -8287,6 +8628,10 @@
         <f>IFERROR(C85*D85,0)</f>
         <v/>
       </c>
+      <c r="F85" s="10">
+        <f>IF(OR($A85="",$B85=""),"",IFERROR($C85*INDEX(INSUMOS!$K$5:$K$67,MATCH($B85,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
@@ -8310,6 +8655,10 @@
         <f>IFERROR(C86*D86,0)</f>
         <v/>
       </c>
+      <c r="F86" s="10">
+        <f>IF(OR($A86="",$B86=""),"",IFERROR($C86*INDEX(INSUMOS!$K$5:$K$67,MATCH($B86,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
@@ -8333,6 +8682,10 @@
         <f>IFERROR(C87*D87,0)</f>
         <v/>
       </c>
+      <c r="F87" s="10">
+        <f>IF(OR($A87="",$B87=""),"",IFERROR($C87*INDEX(INSUMOS!$K$5:$K$67,MATCH($B87,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
@@ -8356,6 +8709,10 @@
         <f>IFERROR(C88*D88,0)</f>
         <v/>
       </c>
+      <c r="F88" s="10">
+        <f>IF(OR($A88="",$B88=""),"",IFERROR($C88*INDEX(INSUMOS!$K$5:$K$67,MATCH($B88,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
@@ -8379,6 +8736,10 @@
         <f>IFERROR(C89*D89,0)</f>
         <v/>
       </c>
+      <c r="F89" s="10">
+        <f>IF(OR($A89="",$B89=""),"",IFERROR($C89*INDEX(INSUMOS!$K$5:$K$67,MATCH($B89,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
@@ -8402,6 +8763,10 @@
         <f>IFERROR(C90*D90,0)</f>
         <v/>
       </c>
+      <c r="F90" s="10">
+        <f>IF(OR($A90="",$B90=""),"",IFERROR($C90*INDEX(INSUMOS!$K$5:$K$67,MATCH($B90,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
@@ -8425,6 +8790,10 @@
         <f>IFERROR(C91*D91,0)</f>
         <v/>
       </c>
+      <c r="F91" s="10">
+        <f>IF(OR($A91="",$B91=""),"",IFERROR($C91*INDEX(INSUMOS!$K$5:$K$67,MATCH($B91,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
@@ -8448,6 +8817,10 @@
         <f>IFERROR(C92*D92,0)</f>
         <v/>
       </c>
+      <c r="F92" s="10">
+        <f>IF(OR($A92="",$B92=""),"",IFERROR($C92*INDEX(INSUMOS!$K$5:$K$67,MATCH($B92,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
@@ -8471,6 +8844,10 @@
         <f>IFERROR(C93*D93,0)</f>
         <v/>
       </c>
+      <c r="F93" s="10">
+        <f>IF(OR($A93="",$B93=""),"",IFERROR($C93*INDEX(INSUMOS!$K$5:$K$67,MATCH($B93,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
@@ -8494,6 +8871,10 @@
         <f>IFERROR(C94*D94,0)</f>
         <v/>
       </c>
+      <c r="F94" s="10">
+        <f>IF(OR($A94="",$B94=""),"",IFERROR($C94*INDEX(INSUMOS!$K$5:$K$67,MATCH($B94,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
@@ -8517,6 +8898,10 @@
         <f>IFERROR(C95*D95,0)</f>
         <v/>
       </c>
+      <c r="F95" s="10">
+        <f>IF(OR($A95="",$B95=""),"",IFERROR($C95*INDEX(INSUMOS!$K$5:$K$67,MATCH($B95,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
@@ -8540,6 +8925,10 @@
         <f>IFERROR(C96*D96,0)</f>
         <v/>
       </c>
+      <c r="F96" s="10">
+        <f>IF(OR($A96="",$B96=""),"",IFERROR($C96*INDEX(INSUMOS!$K$5:$K$67,MATCH($B96,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
@@ -8563,6 +8952,10 @@
         <f>IFERROR(C97*D97,0)</f>
         <v/>
       </c>
+      <c r="F97" s="10">
+        <f>IF(OR($A97="",$B97=""),"",IFERROR($C97*INDEX(INSUMOS!$K$5:$K$67,MATCH($B97,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
@@ -8586,6 +8979,10 @@
         <f>IFERROR(C98*D98,0)</f>
         <v/>
       </c>
+      <c r="F98" s="10">
+        <f>IF(OR($A98="",$B98=""),"",IFERROR($C98*INDEX(INSUMOS!$K$5:$K$67,MATCH($B98,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
@@ -8609,6 +9006,10 @@
         <f>IFERROR(C99*D99,0)</f>
         <v/>
       </c>
+      <c r="F99" s="10">
+        <f>IF(OR($A99="",$B99=""),"",IFERROR($C99*INDEX(INSUMOS!$K$5:$K$67,MATCH($B99,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
@@ -8632,6 +9033,10 @@
         <f>IFERROR(C100*D100,0)</f>
         <v/>
       </c>
+      <c r="F100" s="10">
+        <f>IF(OR($A100="",$B100=""),"",IFERROR($C100*INDEX(INSUMOS!$K$5:$K$67,MATCH($B100,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
@@ -8655,6 +9060,10 @@
         <f>IFERROR(C101*D101,0)</f>
         <v/>
       </c>
+      <c r="F101" s="10">
+        <f>IF(OR($A101="",$B101=""),"",IFERROR($C101*INDEX(INSUMOS!$K$5:$K$67,MATCH($B101,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
@@ -8678,6 +9087,10 @@
         <f>IFERROR(C102*D102,0)</f>
         <v/>
       </c>
+      <c r="F102" s="10">
+        <f>IF(OR($A102="",$B102=""),"",IFERROR($C102*INDEX(INSUMOS!$K$5:$K$67,MATCH($B102,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
@@ -8701,6 +9114,10 @@
         <f>IFERROR(C103*D103,0)</f>
         <v/>
       </c>
+      <c r="F103" s="10">
+        <f>IF(OR($A103="",$B103=""),"",IFERROR($C103*INDEX(INSUMOS!$K$5:$K$67,MATCH($B103,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
@@ -8722,6 +9139,10 @@
       </c>
       <c r="E104" s="8">
         <f>IFERROR(C104*D104,0)</f>
+        <v/>
+      </c>
+      <c r="F104" s="10">
+        <f>IF(OR($A104="",$B104=""),"",IFERROR($C104*INDEX(INSUMOS!$K$5:$K$67,MATCH($B104,INSUMOS!$B$5:$B$67,0)),0))</f>
         <v/>
       </c>
     </row>
@@ -8743,6 +9164,10 @@
       </c>
       <c r="E105" s="8">
         <f>IFERROR(C105*D105,0)</f>
+        <v/>
+      </c>
+      <c r="F105" s="10">
+        <f>IF(OR($A105="",$B105=""),"",IFERROR($C105*INDEX(INSUMOS!$K$5:$K$67,MATCH($B105,INSUMOS!$B$5:$B$67,0)),0))</f>
         <v/>
       </c>
     </row>
@@ -8758,6 +9183,10 @@
         <f>IFERROR(C106*D106,0)</f>
         <v/>
       </c>
+      <c r="F106" s="10">
+        <f>IF(OR($A106="",$B106=""),"",IFERROR($C106*INDEX(INSUMOS!$K$5:$K$67,MATCH($B106,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n"/>
@@ -8771,6 +9200,10 @@
         <f>IFERROR(C107*D107,0)</f>
         <v/>
       </c>
+      <c r="F107" s="10">
+        <f>IF(OR($A107="",$B107=""),"",IFERROR($C107*INDEX(INSUMOS!$K$5:$K$67,MATCH($B107,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n"/>
@@ -8784,6 +9217,10 @@
         <f>IFERROR(C108*D108,0)</f>
         <v/>
       </c>
+      <c r="F108" s="10">
+        <f>IF(OR($A108="",$B108=""),"",IFERROR($C108*INDEX(INSUMOS!$K$5:$K$67,MATCH($B108,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="n"/>
@@ -8797,6 +9234,10 @@
         <f>IFERROR(C109*D109,0)</f>
         <v/>
       </c>
+      <c r="F109" s="10">
+        <f>IF(OR($A109="",$B109=""),"",IFERROR($C109*INDEX(INSUMOS!$K$5:$K$67,MATCH($B109,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n"/>
@@ -8810,6 +9251,10 @@
         <f>IFERROR(C110*D110,0)</f>
         <v/>
       </c>
+      <c r="F110" s="10">
+        <f>IF(OR($A110="",$B110=""),"",IFERROR($C110*INDEX(INSUMOS!$K$5:$K$67,MATCH($B110,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="n"/>
@@ -8823,6 +9268,10 @@
         <f>IFERROR(C111*D111,0)</f>
         <v/>
       </c>
+      <c r="F111" s="10">
+        <f>IF(OR($A111="",$B111=""),"",IFERROR($C111*INDEX(INSUMOS!$K$5:$K$67,MATCH($B111,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n"/>
@@ -8836,6 +9285,10 @@
         <f>IFERROR(C112*D112,0)</f>
         <v/>
       </c>
+      <c r="F112" s="10">
+        <f>IF(OR($A112="",$B112=""),"",IFERROR($C112*INDEX(INSUMOS!$K$5:$K$67,MATCH($B112,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="n"/>
@@ -8849,6 +9302,10 @@
         <f>IFERROR(C113*D113,0)</f>
         <v/>
       </c>
+      <c r="F113" s="10">
+        <f>IF(OR($A113="",$B113=""),"",IFERROR($C113*INDEX(INSUMOS!$K$5:$K$67,MATCH($B113,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="n"/>
@@ -8862,6 +9319,10 @@
         <f>IFERROR(C114*D114,0)</f>
         <v/>
       </c>
+      <c r="F114" s="10">
+        <f>IF(OR($A114="",$B114=""),"",IFERROR($C114*INDEX(INSUMOS!$K$5:$K$67,MATCH($B114,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="7" t="n"/>
@@ -8875,6 +9336,10 @@
         <f>IFERROR(C115*D115,0)</f>
         <v/>
       </c>
+      <c r="F115" s="10">
+        <f>IF(OR($A115="",$B115=""),"",IFERROR($C115*INDEX(INSUMOS!$K$5:$K$67,MATCH($B115,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="n"/>
@@ -8888,6 +9353,10 @@
         <f>IFERROR(C116*D116,0)</f>
         <v/>
       </c>
+      <c r="F116" s="10">
+        <f>IF(OR($A116="",$B116=""),"",IFERROR($C116*INDEX(INSUMOS!$K$5:$K$67,MATCH($B116,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="7" t="n"/>
@@ -8901,6 +9370,10 @@
         <f>IFERROR(C117*D117,0)</f>
         <v/>
       </c>
+      <c r="F117" s="10">
+        <f>IF(OR($A117="",$B117=""),"",IFERROR($C117*INDEX(INSUMOS!$K$5:$K$67,MATCH($B117,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="n"/>
@@ -8914,6 +9387,10 @@
         <f>IFERROR(C118*D118,0)</f>
         <v/>
       </c>
+      <c r="F118" s="10">
+        <f>IF(OR($A118="",$B118=""),"",IFERROR($C118*INDEX(INSUMOS!$K$5:$K$67,MATCH($B118,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="7" t="n"/>
@@ -8927,6 +9404,10 @@
         <f>IFERROR(C119*D119,0)</f>
         <v/>
       </c>
+      <c r="F119" s="10">
+        <f>IF(OR($A119="",$B119=""),"",IFERROR($C119*INDEX(INSUMOS!$K$5:$K$67,MATCH($B119,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="n"/>
@@ -8940,6 +9421,10 @@
         <f>IFERROR(C120*D120,0)</f>
         <v/>
       </c>
+      <c r="F120" s="10">
+        <f>IF(OR($A120="",$B120=""),"",IFERROR($C120*INDEX(INSUMOS!$K$5:$K$67,MATCH($B120,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="7" t="n"/>
@@ -8953,6 +9438,10 @@
         <f>IFERROR(C121*D121,0)</f>
         <v/>
       </c>
+      <c r="F121" s="10">
+        <f>IF(OR($A121="",$B121=""),"",IFERROR($C121*INDEX(INSUMOS!$K$5:$K$67,MATCH($B121,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="n"/>
@@ -8966,6 +9455,10 @@
         <f>IFERROR(C122*D122,0)</f>
         <v/>
       </c>
+      <c r="F122" s="10">
+        <f>IF(OR($A122="",$B122=""),"",IFERROR($C122*INDEX(INSUMOS!$K$5:$K$67,MATCH($B122,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="7" t="n"/>
@@ -8979,6 +9472,10 @@
         <f>IFERROR(C123*D123,0)</f>
         <v/>
       </c>
+      <c r="F123" s="10">
+        <f>IF(OR($A123="",$B123=""),"",IFERROR($C123*INDEX(INSUMOS!$K$5:$K$67,MATCH($B123,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="n"/>
@@ -8992,6 +9489,10 @@
         <f>IFERROR(C124*D124,0)</f>
         <v/>
       </c>
+      <c r="F124" s="10">
+        <f>IF(OR($A124="",$B124=""),"",IFERROR($C124*INDEX(INSUMOS!$K$5:$K$67,MATCH($B124,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="7" t="n"/>
@@ -9005,6 +9506,10 @@
         <f>IFERROR(C125*D125,0)</f>
         <v/>
       </c>
+      <c r="F125" s="10">
+        <f>IF(OR($A125="",$B125=""),"",IFERROR($C125*INDEX(INSUMOS!$K$5:$K$67,MATCH($B125,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="n"/>
@@ -9018,6 +9523,10 @@
         <f>IFERROR(C126*D126,0)</f>
         <v/>
       </c>
+      <c r="F126" s="10">
+        <f>IF(OR($A126="",$B126=""),"",IFERROR($C126*INDEX(INSUMOS!$K$5:$K$67,MATCH($B126,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="7" t="n"/>
@@ -9031,6 +9540,10 @@
         <f>IFERROR(C127*D127,0)</f>
         <v/>
       </c>
+      <c r="F127" s="10">
+        <f>IF(OR($A127="",$B127=""),"",IFERROR($C127*INDEX(INSUMOS!$K$5:$K$67,MATCH($B127,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="7" t="n"/>
@@ -9044,6 +9557,10 @@
         <f>IFERROR(C128*D128,0)</f>
         <v/>
       </c>
+      <c r="F128" s="10">
+        <f>IF(OR($A128="",$B128=""),"",IFERROR($C128*INDEX(INSUMOS!$K$5:$K$67,MATCH($B128,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="7" t="n"/>
@@ -9057,6 +9574,10 @@
         <f>IFERROR(C129*D129,0)</f>
         <v/>
       </c>
+      <c r="F129" s="10">
+        <f>IF(OR($A129="",$B129=""),"",IFERROR($C129*INDEX(INSUMOS!$K$5:$K$67,MATCH($B129,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="7" t="n"/>
@@ -9070,6 +9591,10 @@
         <f>IFERROR(C130*D130,0)</f>
         <v/>
       </c>
+      <c r="F130" s="10">
+        <f>IF(OR($A130="",$B130=""),"",IFERROR($C130*INDEX(INSUMOS!$K$5:$K$67,MATCH($B130,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="7" t="n"/>
@@ -9083,6 +9608,10 @@
         <f>IFERROR(C131*D131,0)</f>
         <v/>
       </c>
+      <c r="F131" s="10">
+        <f>IF(OR($A131="",$B131=""),"",IFERROR($C131*INDEX(INSUMOS!$K$5:$K$67,MATCH($B131,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="7" t="n"/>
@@ -9096,6 +9625,10 @@
         <f>IFERROR(C132*D132,0)</f>
         <v/>
       </c>
+      <c r="F132" s="10">
+        <f>IF(OR($A132="",$B132=""),"",IFERROR($C132*INDEX(INSUMOS!$K$5:$K$67,MATCH($B132,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="7" t="n"/>
@@ -9109,6 +9642,10 @@
         <f>IFERROR(C133*D133,0)</f>
         <v/>
       </c>
+      <c r="F133" s="10">
+        <f>IF(OR($A133="",$B133=""),"",IFERROR($C133*INDEX(INSUMOS!$K$5:$K$67,MATCH($B133,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="n"/>
@@ -9122,6 +9659,10 @@
         <f>IFERROR(C134*D134,0)</f>
         <v/>
       </c>
+      <c r="F134" s="10">
+        <f>IF(OR($A134="",$B134=""),"",IFERROR($C134*INDEX(INSUMOS!$K$5:$K$67,MATCH($B134,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="7" t="n"/>
@@ -9135,6 +9676,10 @@
         <f>IFERROR(C135*D135,0)</f>
         <v/>
       </c>
+      <c r="F135" s="10">
+        <f>IF(OR($A135="",$B135=""),"",IFERROR($C135*INDEX(INSUMOS!$K$5:$K$67,MATCH($B135,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="n"/>
@@ -9148,6 +9693,10 @@
         <f>IFERROR(C136*D136,0)</f>
         <v/>
       </c>
+      <c r="F136" s="10">
+        <f>IF(OR($A136="",$B136=""),"",IFERROR($C136*INDEX(INSUMOS!$K$5:$K$67,MATCH($B136,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="7" t="n"/>
@@ -9161,6 +9710,10 @@
         <f>IFERROR(C137*D137,0)</f>
         <v/>
       </c>
+      <c r="F137" s="10">
+        <f>IF(OR($A137="",$B137=""),"",IFERROR($C137*INDEX(INSUMOS!$K$5:$K$67,MATCH($B137,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="7" t="n"/>
@@ -9174,6 +9727,10 @@
         <f>IFERROR(C138*D138,0)</f>
         <v/>
       </c>
+      <c r="F138" s="10">
+        <f>IF(OR($A138="",$B138=""),"",IFERROR($C138*INDEX(INSUMOS!$K$5:$K$67,MATCH($B138,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="7" t="n"/>
@@ -9187,6 +9744,10 @@
         <f>IFERROR(C139*D139,0)</f>
         <v/>
       </c>
+      <c r="F139" s="10">
+        <f>IF(OR($A139="",$B139=""),"",IFERROR($C139*INDEX(INSUMOS!$K$5:$K$67,MATCH($B139,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="7" t="n"/>
@@ -9200,6 +9761,10 @@
         <f>IFERROR(C140*D140,0)</f>
         <v/>
       </c>
+      <c r="F140" s="10">
+        <f>IF(OR($A140="",$B140=""),"",IFERROR($C140*INDEX(INSUMOS!$K$5:$K$67,MATCH($B140,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="7" t="n"/>
@@ -9213,6 +9778,10 @@
         <f>IFERROR(C141*D141,0)</f>
         <v/>
       </c>
+      <c r="F141" s="10">
+        <f>IF(OR($A141="",$B141=""),"",IFERROR($C141*INDEX(INSUMOS!$K$5:$K$67,MATCH($B141,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="7" t="n"/>
@@ -9226,6 +9795,10 @@
         <f>IFERROR(C142*D142,0)</f>
         <v/>
       </c>
+      <c r="F142" s="10">
+        <f>IF(OR($A142="",$B142=""),"",IFERROR($C142*INDEX(INSUMOS!$K$5:$K$67,MATCH($B142,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="7" t="n"/>
@@ -9239,6 +9812,10 @@
         <f>IFERROR(C143*D143,0)</f>
         <v/>
       </c>
+      <c r="F143" s="10">
+        <f>IF(OR($A143="",$B143=""),"",IFERROR($C143*INDEX(INSUMOS!$K$5:$K$67,MATCH($B143,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="7" t="n"/>
@@ -9252,6 +9829,10 @@
         <f>IFERROR(C144*D144,0)</f>
         <v/>
       </c>
+      <c r="F144" s="10">
+        <f>IF(OR($A144="",$B144=""),"",IFERROR($C144*INDEX(INSUMOS!$K$5:$K$67,MATCH($B144,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="7" t="n"/>
@@ -9265,6 +9846,10 @@
         <f>IFERROR(C145*D145,0)</f>
         <v/>
       </c>
+      <c r="F145" s="10">
+        <f>IF(OR($A145="",$B145=""),"",IFERROR($C145*INDEX(INSUMOS!$K$5:$K$67,MATCH($B145,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="7" t="n"/>
@@ -9278,6 +9863,10 @@
         <f>IFERROR(C146*D146,0)</f>
         <v/>
       </c>
+      <c r="F146" s="10">
+        <f>IF(OR($A146="",$B146=""),"",IFERROR($C146*INDEX(INSUMOS!$K$5:$K$67,MATCH($B146,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="7" t="n"/>
@@ -9291,6 +9880,10 @@
         <f>IFERROR(C147*D147,0)</f>
         <v/>
       </c>
+      <c r="F147" s="10">
+        <f>IF(OR($A147="",$B147=""),"",IFERROR($C147*INDEX(INSUMOS!$K$5:$K$67,MATCH($B147,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="7" t="n"/>
@@ -9304,6 +9897,10 @@
         <f>IFERROR(C148*D148,0)</f>
         <v/>
       </c>
+      <c r="F148" s="10">
+        <f>IF(OR($A148="",$B148=""),"",IFERROR($C148*INDEX(INSUMOS!$K$5:$K$67,MATCH($B148,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="7" t="n"/>
@@ -9317,6 +9914,10 @@
         <f>IFERROR(C149*D149,0)</f>
         <v/>
       </c>
+      <c r="F149" s="10">
+        <f>IF(OR($A149="",$B149=""),"",IFERROR($C149*INDEX(INSUMOS!$K$5:$K$67,MATCH($B149,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="7" t="n"/>
@@ -9330,6 +9931,10 @@
         <f>IFERROR(C150*D150,0)</f>
         <v/>
       </c>
+      <c r="F150" s="10">
+        <f>IF(OR($A150="",$B150=""),"",IFERROR($C150*INDEX(INSUMOS!$K$5:$K$67,MATCH($B150,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="7" t="n"/>
@@ -9343,6 +9948,10 @@
         <f>IFERROR(C151*D151,0)</f>
         <v/>
       </c>
+      <c r="F151" s="10">
+        <f>IF(OR($A151="",$B151=""),"",IFERROR($C151*INDEX(INSUMOS!$K$5:$K$67,MATCH($B151,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="7" t="n"/>
@@ -9356,6 +9965,10 @@
         <f>IFERROR(C152*D152,0)</f>
         <v/>
       </c>
+      <c r="F152" s="10">
+        <f>IF(OR($A152="",$B152=""),"",IFERROR($C152*INDEX(INSUMOS!$K$5:$K$67,MATCH($B152,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="7" t="n"/>
@@ -9369,6 +9982,10 @@
         <f>IFERROR(C153*D153,0)</f>
         <v/>
       </c>
+      <c r="F153" s="10">
+        <f>IF(OR($A153="",$B153=""),"",IFERROR($C153*INDEX(INSUMOS!$K$5:$K$67,MATCH($B153,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="7" t="n"/>
@@ -9382,6 +9999,10 @@
         <f>IFERROR(C154*D154,0)</f>
         <v/>
       </c>
+      <c r="F154" s="10">
+        <f>IF(OR($A154="",$B154=""),"",IFERROR($C154*INDEX(INSUMOS!$K$5:$K$67,MATCH($B154,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="7" t="n"/>
@@ -9395,6 +10016,10 @@
         <f>IFERROR(C155*D155,0)</f>
         <v/>
       </c>
+      <c r="F155" s="10">
+        <f>IF(OR($A155="",$B155=""),"",IFERROR($C155*INDEX(INSUMOS!$K$5:$K$67,MATCH($B155,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="7" t="n"/>
@@ -9408,6 +10033,10 @@
         <f>IFERROR(C156*D156,0)</f>
         <v/>
       </c>
+      <c r="F156" s="10">
+        <f>IF(OR($A156="",$B156=""),"",IFERROR($C156*INDEX(INSUMOS!$K$5:$K$67,MATCH($B156,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="7" t="n"/>
@@ -9421,6 +10050,10 @@
         <f>IFERROR(C157*D157,0)</f>
         <v/>
       </c>
+      <c r="F157" s="10">
+        <f>IF(OR($A157="",$B157=""),"",IFERROR($C157*INDEX(INSUMOS!$K$5:$K$67,MATCH($B157,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="7" t="n"/>
@@ -9434,6 +10067,10 @@
         <f>IFERROR(C158*D158,0)</f>
         <v/>
       </c>
+      <c r="F158" s="10">
+        <f>IF(OR($A158="",$B158=""),"",IFERROR($C158*INDEX(INSUMOS!$K$5:$K$67,MATCH($B158,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="7" t="n"/>
@@ -9447,6 +10084,10 @@
         <f>IFERROR(C159*D159,0)</f>
         <v/>
       </c>
+      <c r="F159" s="10">
+        <f>IF(OR($A159="",$B159=""),"",IFERROR($C159*INDEX(INSUMOS!$K$5:$K$67,MATCH($B159,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="7" t="n"/>
@@ -9460,6 +10101,10 @@
         <f>IFERROR(C160*D160,0)</f>
         <v/>
       </c>
+      <c r="F160" s="10">
+        <f>IF(OR($A160="",$B160=""),"",IFERROR($C160*INDEX(INSUMOS!$K$5:$K$67,MATCH($B160,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="7" t="n"/>
@@ -9473,6 +10118,10 @@
         <f>IFERROR(C161*D161,0)</f>
         <v/>
       </c>
+      <c r="F161" s="10">
+        <f>IF(OR($A161="",$B161=""),"",IFERROR($C161*INDEX(INSUMOS!$K$5:$K$67,MATCH($B161,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="7" t="n"/>
@@ -9486,6 +10135,10 @@
         <f>IFERROR(C162*D162,0)</f>
         <v/>
       </c>
+      <c r="F162" s="10">
+        <f>IF(OR($A162="",$B162=""),"",IFERROR($C162*INDEX(INSUMOS!$K$5:$K$67,MATCH($B162,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="7" t="n"/>
@@ -9499,6 +10152,10 @@
         <f>IFERROR(C163*D163,0)</f>
         <v/>
       </c>
+      <c r="F163" s="10">
+        <f>IF(OR($A163="",$B163=""),"",IFERROR($C163*INDEX(INSUMOS!$K$5:$K$67,MATCH($B163,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="7" t="n"/>
@@ -9512,6 +10169,10 @@
         <f>IFERROR(C164*D164,0)</f>
         <v/>
       </c>
+      <c r="F164" s="10">
+        <f>IF(OR($A164="",$B164=""),"",IFERROR($C164*INDEX(INSUMOS!$K$5:$K$67,MATCH($B164,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="7" t="n"/>
@@ -9525,6 +10186,10 @@
         <f>IFERROR(C165*D165,0)</f>
         <v/>
       </c>
+      <c r="F165" s="10">
+        <f>IF(OR($A165="",$B165=""),"",IFERROR($C165*INDEX(INSUMOS!$K$5:$K$67,MATCH($B165,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="7" t="n"/>
@@ -9538,6 +10203,10 @@
         <f>IFERROR(C166*D166,0)</f>
         <v/>
       </c>
+      <c r="F166" s="10">
+        <f>IF(OR($A166="",$B166=""),"",IFERROR($C166*INDEX(INSUMOS!$K$5:$K$67,MATCH($B166,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="7" t="n"/>
@@ -9551,6 +10220,10 @@
         <f>IFERROR(C167*D167,0)</f>
         <v/>
       </c>
+      <c r="F167" s="10">
+        <f>IF(OR($A167="",$B167=""),"",IFERROR($C167*INDEX(INSUMOS!$K$5:$K$67,MATCH($B167,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="7" t="n"/>
@@ -9564,6 +10237,10 @@
         <f>IFERROR(C168*D168,0)</f>
         <v/>
       </c>
+      <c r="F168" s="10">
+        <f>IF(OR($A168="",$B168=""),"",IFERROR($C168*INDEX(INSUMOS!$K$5:$K$67,MATCH($B168,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="7" t="n"/>
@@ -9577,6 +10254,10 @@
         <f>IFERROR(C169*D169,0)</f>
         <v/>
       </c>
+      <c r="F169" s="10">
+        <f>IF(OR($A169="",$B169=""),"",IFERROR($C169*INDEX(INSUMOS!$K$5:$K$67,MATCH($B169,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="7" t="n"/>
@@ -9590,6 +10271,10 @@
         <f>IFERROR(C170*D170,0)</f>
         <v/>
       </c>
+      <c r="F170" s="10">
+        <f>IF(OR($A170="",$B170=""),"",IFERROR($C170*INDEX(INSUMOS!$K$5:$K$67,MATCH($B170,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="7" t="n"/>
@@ -9603,6 +10288,10 @@
         <f>IFERROR(C171*D171,0)</f>
         <v/>
       </c>
+      <c r="F171" s="10">
+        <f>IF(OR($A171="",$B171=""),"",IFERROR($C171*INDEX(INSUMOS!$K$5:$K$67,MATCH($B171,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="7" t="n"/>
@@ -9616,6 +10305,10 @@
         <f>IFERROR(C172*D172,0)</f>
         <v/>
       </c>
+      <c r="F172" s="10">
+        <f>IF(OR($A172="",$B172=""),"",IFERROR($C172*INDEX(INSUMOS!$K$5:$K$67,MATCH($B172,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="7" t="n"/>
@@ -9629,6 +10322,10 @@
         <f>IFERROR(C173*D173,0)</f>
         <v/>
       </c>
+      <c r="F173" s="10">
+        <f>IF(OR($A173="",$B173=""),"",IFERROR($C173*INDEX(INSUMOS!$K$5:$K$67,MATCH($B173,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="7" t="n"/>
@@ -9642,6 +10339,10 @@
         <f>IFERROR(C174*D174,0)</f>
         <v/>
       </c>
+      <c r="F174" s="10">
+        <f>IF(OR($A174="",$B174=""),"",IFERROR($C174*INDEX(INSUMOS!$K$5:$K$67,MATCH($B174,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="7" t="n"/>
@@ -9655,6 +10356,10 @@
         <f>IFERROR(C175*D175,0)</f>
         <v/>
       </c>
+      <c r="F175" s="10">
+        <f>IF(OR($A175="",$B175=""),"",IFERROR($C175*INDEX(INSUMOS!$K$5:$K$67,MATCH($B175,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="7" t="n"/>
@@ -9668,6 +10373,10 @@
         <f>IFERROR(C176*D176,0)</f>
         <v/>
       </c>
+      <c r="F176" s="10">
+        <f>IF(OR($A176="",$B176=""),"",IFERROR($C176*INDEX(INSUMOS!$K$5:$K$67,MATCH($B176,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="7" t="n"/>
@@ -9681,6 +10390,10 @@
         <f>IFERROR(C177*D177,0)</f>
         <v/>
       </c>
+      <c r="F177" s="10">
+        <f>IF(OR($A177="",$B177=""),"",IFERROR($C177*INDEX(INSUMOS!$K$5:$K$67,MATCH($B177,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="7" t="n"/>
@@ -9694,6 +10407,10 @@
         <f>IFERROR(C178*D178,0)</f>
         <v/>
       </c>
+      <c r="F178" s="10">
+        <f>IF(OR($A178="",$B178=""),"",IFERROR($C178*INDEX(INSUMOS!$K$5:$K$67,MATCH($B178,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="7" t="n"/>
@@ -9707,6 +10424,10 @@
         <f>IFERROR(C179*D179,0)</f>
         <v/>
       </c>
+      <c r="F179" s="10">
+        <f>IF(OR($A179="",$B179=""),"",IFERROR($C179*INDEX(INSUMOS!$K$5:$K$67,MATCH($B179,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="7" t="n"/>
@@ -9720,6 +10441,10 @@
         <f>IFERROR(C180*D180,0)</f>
         <v/>
       </c>
+      <c r="F180" s="10">
+        <f>IF(OR($A180="",$B180=""),"",IFERROR($C180*INDEX(INSUMOS!$K$5:$K$67,MATCH($B180,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="7" t="n"/>
@@ -9733,6 +10458,10 @@
         <f>IFERROR(C181*D181,0)</f>
         <v/>
       </c>
+      <c r="F181" s="10">
+        <f>IF(OR($A181="",$B181=""),"",IFERROR($C181*INDEX(INSUMOS!$K$5:$K$67,MATCH($B181,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="7" t="n"/>
@@ -9746,6 +10475,10 @@
         <f>IFERROR(C182*D182,0)</f>
         <v/>
       </c>
+      <c r="F182" s="10">
+        <f>IF(OR($A182="",$B182=""),"",IFERROR($C182*INDEX(INSUMOS!$K$5:$K$67,MATCH($B182,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="7" t="n"/>
@@ -9759,6 +10492,10 @@
         <f>IFERROR(C183*D183,0)</f>
         <v/>
       </c>
+      <c r="F183" s="10">
+        <f>IF(OR($A183="",$B183=""),"",IFERROR($C183*INDEX(INSUMOS!$K$5:$K$67,MATCH($B183,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="7" t="n"/>
@@ -9772,6 +10509,10 @@
         <f>IFERROR(C184*D184,0)</f>
         <v/>
       </c>
+      <c r="F184" s="10">
+        <f>IF(OR($A184="",$B184=""),"",IFERROR($C184*INDEX(INSUMOS!$K$5:$K$67,MATCH($B184,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="7" t="n"/>
@@ -9785,6 +10526,10 @@
         <f>IFERROR(C185*D185,0)</f>
         <v/>
       </c>
+      <c r="F185" s="10">
+        <f>IF(OR($A185="",$B185=""),"",IFERROR($C185*INDEX(INSUMOS!$K$5:$K$67,MATCH($B185,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="7" t="n"/>
@@ -9798,6 +10543,10 @@
         <f>IFERROR(C186*D186,0)</f>
         <v/>
       </c>
+      <c r="F186" s="10">
+        <f>IF(OR($A186="",$B186=""),"",IFERROR($C186*INDEX(INSUMOS!$K$5:$K$67,MATCH($B186,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="7" t="n"/>
@@ -9811,6 +10560,10 @@
         <f>IFERROR(C187*D187,0)</f>
         <v/>
       </c>
+      <c r="F187" s="10">
+        <f>IF(OR($A187="",$B187=""),"",IFERROR($C187*INDEX(INSUMOS!$K$5:$K$67,MATCH($B187,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="7" t="n"/>
@@ -9824,6 +10577,10 @@
         <f>IFERROR(C188*D188,0)</f>
         <v/>
       </c>
+      <c r="F188" s="10">
+        <f>IF(OR($A188="",$B188=""),"",IFERROR($C188*INDEX(INSUMOS!$K$5:$K$67,MATCH($B188,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="7" t="n"/>
@@ -9837,6 +10594,10 @@
         <f>IFERROR(C189*D189,0)</f>
         <v/>
       </c>
+      <c r="F189" s="10">
+        <f>IF(OR($A189="",$B189=""),"",IFERROR($C189*INDEX(INSUMOS!$K$5:$K$67,MATCH($B189,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="7" t="n"/>
@@ -9850,6 +10611,10 @@
         <f>IFERROR(C190*D190,0)</f>
         <v/>
       </c>
+      <c r="F190" s="10">
+        <f>IF(OR($A190="",$B190=""),"",IFERROR($C190*INDEX(INSUMOS!$K$5:$K$67,MATCH($B190,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="7" t="n"/>
@@ -9863,6 +10628,10 @@
         <f>IFERROR(C191*D191,0)</f>
         <v/>
       </c>
+      <c r="F191" s="10">
+        <f>IF(OR($A191="",$B191=""),"",IFERROR($C191*INDEX(INSUMOS!$K$5:$K$67,MATCH($B191,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="7" t="n"/>
@@ -9876,6 +10645,10 @@
         <f>IFERROR(C192*D192,0)</f>
         <v/>
       </c>
+      <c r="F192" s="10">
+        <f>IF(OR($A192="",$B192=""),"",IFERROR($C192*INDEX(INSUMOS!$K$5:$K$67,MATCH($B192,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="7" t="n"/>
@@ -9889,6 +10662,10 @@
         <f>IFERROR(C193*D193,0)</f>
         <v/>
       </c>
+      <c r="F193" s="10">
+        <f>IF(OR($A193="",$B193=""),"",IFERROR($C193*INDEX(INSUMOS!$K$5:$K$67,MATCH($B193,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="7" t="n"/>
@@ -9902,6 +10679,10 @@
         <f>IFERROR(C194*D194,0)</f>
         <v/>
       </c>
+      <c r="F194" s="10">
+        <f>IF(OR($A194="",$B194=""),"",IFERROR($C194*INDEX(INSUMOS!$K$5:$K$67,MATCH($B194,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="7" t="n"/>
@@ -9915,6 +10696,10 @@
         <f>IFERROR(C195*D195,0)</f>
         <v/>
       </c>
+      <c r="F195" s="10">
+        <f>IF(OR($A195="",$B195=""),"",IFERROR($C195*INDEX(INSUMOS!$K$5:$K$67,MATCH($B195,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="7" t="n"/>
@@ -9928,6 +10713,10 @@
         <f>IFERROR(C196*D196,0)</f>
         <v/>
       </c>
+      <c r="F196" s="10">
+        <f>IF(OR($A196="",$B196=""),"",IFERROR($C196*INDEX(INSUMOS!$K$5:$K$67,MATCH($B196,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="7" t="n"/>
@@ -9941,6 +10730,10 @@
         <f>IFERROR(C197*D197,0)</f>
         <v/>
       </c>
+      <c r="F197" s="10">
+        <f>IF(OR($A197="",$B197=""),"",IFERROR($C197*INDEX(INSUMOS!$K$5:$K$67,MATCH($B197,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="7" t="n"/>
@@ -9954,6 +10747,10 @@
         <f>IFERROR(C198*D198,0)</f>
         <v/>
       </c>
+      <c r="F198" s="10">
+        <f>IF(OR($A198="",$B198=""),"",IFERROR($C198*INDEX(INSUMOS!$K$5:$K$67,MATCH($B198,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="7" t="n"/>
@@ -9967,6 +10764,10 @@
         <f>IFERROR(C199*D199,0)</f>
         <v/>
       </c>
+      <c r="F199" s="10">
+        <f>IF(OR($A199="",$B199=""),"",IFERROR($C199*INDEX(INSUMOS!$K$5:$K$67,MATCH($B199,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="7" t="n"/>
@@ -9980,6 +10781,10 @@
         <f>IFERROR(C200*D200,0)</f>
         <v/>
       </c>
+      <c r="F200" s="10">
+        <f>IF(OR($A200="",$B200=""),"",IFERROR($C200*INDEX(INSUMOS!$K$5:$K$67,MATCH($B200,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="7" t="n"/>
@@ -9993,6 +10798,10 @@
         <f>IFERROR(C201*D201,0)</f>
         <v/>
       </c>
+      <c r="F201" s="10">
+        <f>IF(OR($A201="",$B201=""),"",IFERROR($C201*INDEX(INSUMOS!$K$5:$K$67,MATCH($B201,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="7" t="n"/>
@@ -10006,6 +10815,10 @@
         <f>IFERROR(C202*D202,0)</f>
         <v/>
       </c>
+      <c r="F202" s="10">
+        <f>IF(OR($A202="",$B202=""),"",IFERROR($C202*INDEX(INSUMOS!$K$5:$K$67,MATCH($B202,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="7" t="n"/>
@@ -10019,6 +10832,10 @@
         <f>IFERROR(C203*D203,0)</f>
         <v/>
       </c>
+      <c r="F203" s="10">
+        <f>IF(OR($A203="",$B203=""),"",IFERROR($C203*INDEX(INSUMOS!$K$5:$K$67,MATCH($B203,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="7" t="n"/>
@@ -10032,6 +10849,10 @@
         <f>IFERROR(C204*D204,0)</f>
         <v/>
       </c>
+      <c r="F204" s="10">
+        <f>IF(OR($A204="",$B204=""),"",IFERROR($C204*INDEX(INSUMOS!$K$5:$K$67,MATCH($B204,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="7" t="n"/>
@@ -10045,6 +10866,10 @@
         <f>IFERROR(C205*D205,0)</f>
         <v/>
       </c>
+      <c r="F205" s="10">
+        <f>IF(OR($A205="",$B205=""),"",IFERROR($C205*INDEX(INSUMOS!$K$5:$K$67,MATCH($B205,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="7" t="n"/>
@@ -10058,6 +10883,10 @@
         <f>IFERROR(C206*D206,0)</f>
         <v/>
       </c>
+      <c r="F206" s="10">
+        <f>IF(OR($A206="",$B206=""),"",IFERROR($C206*INDEX(INSUMOS!$K$5:$K$67,MATCH($B206,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="7" t="n"/>
@@ -10071,6 +10900,10 @@
         <f>IFERROR(C207*D207,0)</f>
         <v/>
       </c>
+      <c r="F207" s="10">
+        <f>IF(OR($A207="",$B207=""),"",IFERROR($C207*INDEX(INSUMOS!$K$5:$K$67,MATCH($B207,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="7" t="n"/>
@@ -10084,6 +10917,10 @@
         <f>IFERROR(C208*D208,0)</f>
         <v/>
       </c>
+      <c r="F208" s="10">
+        <f>IF(OR($A208="",$B208=""),"",IFERROR($C208*INDEX(INSUMOS!$K$5:$K$67,MATCH($B208,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="7" t="n"/>
@@ -10097,6 +10934,10 @@
         <f>IFERROR(C209*D209,0)</f>
         <v/>
       </c>
+      <c r="F209" s="10">
+        <f>IF(OR($A209="",$B209=""),"",IFERROR($C209*INDEX(INSUMOS!$K$5:$K$67,MATCH($B209,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="7" t="n"/>
@@ -10110,6 +10951,10 @@
         <f>IFERROR(C210*D210,0)</f>
         <v/>
       </c>
+      <c r="F210" s="10">
+        <f>IF(OR($A210="",$B210=""),"",IFERROR($C210*INDEX(INSUMOS!$K$5:$K$67,MATCH($B210,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="7" t="n"/>
@@ -10123,6 +10968,10 @@
         <f>IFERROR(C211*D211,0)</f>
         <v/>
       </c>
+      <c r="F211" s="10">
+        <f>IF(OR($A211="",$B211=""),"",IFERROR($C211*INDEX(INSUMOS!$K$5:$K$67,MATCH($B211,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="7" t="n"/>
@@ -10136,6 +10985,10 @@
         <f>IFERROR(C212*D212,0)</f>
         <v/>
       </c>
+      <c r="F212" s="10">
+        <f>IF(OR($A212="",$B212=""),"",IFERROR($C212*INDEX(INSUMOS!$K$5:$K$67,MATCH($B212,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="7" t="n"/>
@@ -10149,6 +11002,10 @@
         <f>IFERROR(C213*D213,0)</f>
         <v/>
       </c>
+      <c r="F213" s="10">
+        <f>IF(OR($A213="",$B213=""),"",IFERROR($C213*INDEX(INSUMOS!$K$5:$K$67,MATCH($B213,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="7" t="n"/>
@@ -10162,6 +11019,10 @@
         <f>IFERROR(C214*D214,0)</f>
         <v/>
       </c>
+      <c r="F214" s="10">
+        <f>IF(OR($A214="",$B214=""),"",IFERROR($C214*INDEX(INSUMOS!$K$5:$K$67,MATCH($B214,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="7" t="n"/>
@@ -10175,6 +11036,10 @@
         <f>IFERROR(C215*D215,0)</f>
         <v/>
       </c>
+      <c r="F215" s="10">
+        <f>IF(OR($A215="",$B215=""),"",IFERROR($C215*INDEX(INSUMOS!$K$5:$K$67,MATCH($B215,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="7" t="n"/>
@@ -10188,6 +11053,10 @@
         <f>IFERROR(C216*D216,0)</f>
         <v/>
       </c>
+      <c r="F216" s="10">
+        <f>IF(OR($A216="",$B216=""),"",IFERROR($C216*INDEX(INSUMOS!$K$5:$K$67,MATCH($B216,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="7" t="n"/>
@@ -10201,6 +11070,10 @@
         <f>IFERROR(C217*D217,0)</f>
         <v/>
       </c>
+      <c r="F217" s="10">
+        <f>IF(OR($A217="",$B217=""),"",IFERROR($C217*INDEX(INSUMOS!$K$5:$K$67,MATCH($B217,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="7" t="n"/>
@@ -10214,6 +11087,10 @@
         <f>IFERROR(C218*D218,0)</f>
         <v/>
       </c>
+      <c r="F218" s="10">
+        <f>IF(OR($A218="",$B218=""),"",IFERROR($C218*INDEX(INSUMOS!$K$5:$K$67,MATCH($B218,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="7" t="n"/>
@@ -10227,6 +11104,10 @@
         <f>IFERROR(C219*D219,0)</f>
         <v/>
       </c>
+      <c r="F219" s="10">
+        <f>IF(OR($A219="",$B219=""),"",IFERROR($C219*INDEX(INSUMOS!$K$5:$K$67,MATCH($B219,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="7" t="n"/>
@@ -10240,6 +11121,10 @@
         <f>IFERROR(C220*D220,0)</f>
         <v/>
       </c>
+      <c r="F220" s="10">
+        <f>IF(OR($A220="",$B220=""),"",IFERROR($C220*INDEX(INSUMOS!$K$5:$K$67,MATCH($B220,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="7" t="n"/>
@@ -10253,6 +11138,10 @@
         <f>IFERROR(C221*D221,0)</f>
         <v/>
       </c>
+      <c r="F221" s="10">
+        <f>IF(OR($A221="",$B221=""),"",IFERROR($C221*INDEX(INSUMOS!$K$5:$K$67,MATCH($B221,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="7" t="n"/>
@@ -10266,6 +11155,10 @@
         <f>IFERROR(C222*D222,0)</f>
         <v/>
       </c>
+      <c r="F222" s="10">
+        <f>IF(OR($A222="",$B222=""),"",IFERROR($C222*INDEX(INSUMOS!$K$5:$K$67,MATCH($B222,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="7" t="n"/>
@@ -10279,6 +11172,10 @@
         <f>IFERROR(C223*D223,0)</f>
         <v/>
       </c>
+      <c r="F223" s="10">
+        <f>IF(OR($A223="",$B223=""),"",IFERROR($C223*INDEX(INSUMOS!$K$5:$K$67,MATCH($B223,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="7" t="n"/>
@@ -10292,6 +11189,10 @@
         <f>IFERROR(C224*D224,0)</f>
         <v/>
       </c>
+      <c r="F224" s="10">
+        <f>IF(OR($A224="",$B224=""),"",IFERROR($C224*INDEX(INSUMOS!$K$5:$K$67,MATCH($B224,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="7" t="n"/>
@@ -10305,6 +11206,10 @@
         <f>IFERROR(C225*D225,0)</f>
         <v/>
       </c>
+      <c r="F225" s="10">
+        <f>IF(OR($A225="",$B225=""),"",IFERROR($C225*INDEX(INSUMOS!$K$5:$K$67,MATCH($B225,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="7" t="n"/>
@@ -10318,6 +11223,10 @@
         <f>IFERROR(C226*D226,0)</f>
         <v/>
       </c>
+      <c r="F226" s="10">
+        <f>IF(OR($A226="",$B226=""),"",IFERROR($C226*INDEX(INSUMOS!$K$5:$K$67,MATCH($B226,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="7" t="n"/>
@@ -10331,6 +11240,10 @@
         <f>IFERROR(C227*D227,0)</f>
         <v/>
       </c>
+      <c r="F227" s="10">
+        <f>IF(OR($A227="",$B227=""),"",IFERROR($C227*INDEX(INSUMOS!$K$5:$K$67,MATCH($B227,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="7" t="n"/>
@@ -10344,6 +11257,10 @@
         <f>IFERROR(C228*D228,0)</f>
         <v/>
       </c>
+      <c r="F228" s="10">
+        <f>IF(OR($A228="",$B228=""),"",IFERROR($C228*INDEX(INSUMOS!$K$5:$K$67,MATCH($B228,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="7" t="n"/>
@@ -10357,6 +11274,10 @@
         <f>IFERROR(C229*D229,0)</f>
         <v/>
       </c>
+      <c r="F229" s="10">
+        <f>IF(OR($A229="",$B229=""),"",IFERROR($C229*INDEX(INSUMOS!$K$5:$K$67,MATCH($B229,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="7" t="n"/>
@@ -10370,6 +11291,10 @@
         <f>IFERROR(C230*D230,0)</f>
         <v/>
       </c>
+      <c r="F230" s="10">
+        <f>IF(OR($A230="",$B230=""),"",IFERROR($C230*INDEX(INSUMOS!$K$5:$K$67,MATCH($B230,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="7" t="n"/>
@@ -10383,6 +11308,10 @@
         <f>IFERROR(C231*D231,0)</f>
         <v/>
       </c>
+      <c r="F231" s="10">
+        <f>IF(OR($A231="",$B231=""),"",IFERROR($C231*INDEX(INSUMOS!$K$5:$K$67,MATCH($B231,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="7" t="n"/>
@@ -10396,6 +11325,10 @@
         <f>IFERROR(C232*D232,0)</f>
         <v/>
       </c>
+      <c r="F232" s="10">
+        <f>IF(OR($A232="",$B232=""),"",IFERROR($C232*INDEX(INSUMOS!$K$5:$K$67,MATCH($B232,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="7" t="n"/>
@@ -10409,6 +11342,10 @@
         <f>IFERROR(C233*D233,0)</f>
         <v/>
       </c>
+      <c r="F233" s="10">
+        <f>IF(OR($A233="",$B233=""),"",IFERROR($C233*INDEX(INSUMOS!$K$5:$K$67,MATCH($B233,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="7" t="n"/>
@@ -10422,6 +11359,10 @@
         <f>IFERROR(C234*D234,0)</f>
         <v/>
       </c>
+      <c r="F234" s="10">
+        <f>IF(OR($A234="",$B234=""),"",IFERROR($C234*INDEX(INSUMOS!$K$5:$K$67,MATCH($B234,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="7" t="n"/>
@@ -10435,6 +11376,10 @@
         <f>IFERROR(C235*D235,0)</f>
         <v/>
       </c>
+      <c r="F235" s="10">
+        <f>IF(OR($A235="",$B235=""),"",IFERROR($C235*INDEX(INSUMOS!$K$5:$K$67,MATCH($B235,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="7" t="n"/>
@@ -10448,6 +11393,10 @@
         <f>IFERROR(C236*D236,0)</f>
         <v/>
       </c>
+      <c r="F236" s="10">
+        <f>IF(OR($A236="",$B236=""),"",IFERROR($C236*INDEX(INSUMOS!$K$5:$K$67,MATCH($B236,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="7" t="n"/>
@@ -10461,6 +11410,10 @@
         <f>IFERROR(C237*D237,0)</f>
         <v/>
       </c>
+      <c r="F237" s="10">
+        <f>IF(OR($A237="",$B237=""),"",IFERROR($C237*INDEX(INSUMOS!$K$5:$K$67,MATCH($B237,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="7" t="n"/>
@@ -10474,6 +11427,10 @@
         <f>IFERROR(C238*D238,0)</f>
         <v/>
       </c>
+      <c r="F238" s="10">
+        <f>IF(OR($A238="",$B238=""),"",IFERROR($C238*INDEX(INSUMOS!$K$5:$K$67,MATCH($B238,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="7" t="n"/>
@@ -10487,6 +11444,10 @@
         <f>IFERROR(C239*D239,0)</f>
         <v/>
       </c>
+      <c r="F239" s="10">
+        <f>IF(OR($A239="",$B239=""),"",IFERROR($C239*INDEX(INSUMOS!$K$5:$K$67,MATCH($B239,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="7" t="n"/>
@@ -10500,6 +11461,10 @@
         <f>IFERROR(C240*D240,0)</f>
         <v/>
       </c>
+      <c r="F240" s="10">
+        <f>IF(OR($A240="",$B240=""),"",IFERROR($C240*INDEX(INSUMOS!$K$5:$K$67,MATCH($B240,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="7" t="n"/>
@@ -10513,6 +11478,10 @@
         <f>IFERROR(C241*D241,0)</f>
         <v/>
       </c>
+      <c r="F241" s="10">
+        <f>IF(OR($A241="",$B241=""),"",IFERROR($C241*INDEX(INSUMOS!$K$5:$K$67,MATCH($B241,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="7" t="n"/>
@@ -10526,6 +11495,10 @@
         <f>IFERROR(C242*D242,0)</f>
         <v/>
       </c>
+      <c r="F242" s="10">
+        <f>IF(OR($A242="",$B242=""),"",IFERROR($C242*INDEX(INSUMOS!$K$5:$K$67,MATCH($B242,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="7" t="n"/>
@@ -10539,6 +11512,10 @@
         <f>IFERROR(C243*D243,0)</f>
         <v/>
       </c>
+      <c r="F243" s="10">
+        <f>IF(OR($A243="",$B243=""),"",IFERROR($C243*INDEX(INSUMOS!$K$5:$K$67,MATCH($B243,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="7" t="n"/>
@@ -10552,6 +11529,10 @@
         <f>IFERROR(C244*D244,0)</f>
         <v/>
       </c>
+      <c r="F244" s="10">
+        <f>IF(OR($A244="",$B244=""),"",IFERROR($C244*INDEX(INSUMOS!$K$5:$K$67,MATCH($B244,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="7" t="n"/>
@@ -10565,6 +11546,10 @@
         <f>IFERROR(C245*D245,0)</f>
         <v/>
       </c>
+      <c r="F245" s="10">
+        <f>IF(OR($A245="",$B245=""),"",IFERROR($C245*INDEX(INSUMOS!$K$5:$K$67,MATCH($B245,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="7" t="n"/>
@@ -10578,6 +11563,10 @@
         <f>IFERROR(C246*D246,0)</f>
         <v/>
       </c>
+      <c r="F246" s="10">
+        <f>IF(OR($A246="",$B246=""),"",IFERROR($C246*INDEX(INSUMOS!$K$5:$K$67,MATCH($B246,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="7" t="n"/>
@@ -10591,6 +11580,10 @@
         <f>IFERROR(C247*D247,0)</f>
         <v/>
       </c>
+      <c r="F247" s="10">
+        <f>IF(OR($A247="",$B247=""),"",IFERROR($C247*INDEX(INSUMOS!$K$5:$K$67,MATCH($B247,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="7" t="n"/>
@@ -10604,6 +11597,10 @@
         <f>IFERROR(C248*D248,0)</f>
         <v/>
       </c>
+      <c r="F248" s="10">
+        <f>IF(OR($A248="",$B248=""),"",IFERROR($C248*INDEX(INSUMOS!$K$5:$K$67,MATCH($B248,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="7" t="n"/>
@@ -10617,6 +11614,10 @@
         <f>IFERROR(C249*D249,0)</f>
         <v/>
       </c>
+      <c r="F249" s="10">
+        <f>IF(OR($A249="",$B249=""),"",IFERROR($C249*INDEX(INSUMOS!$K$5:$K$67,MATCH($B249,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="7" t="n"/>
@@ -10630,6 +11631,10 @@
         <f>IFERROR(C250*D250,0)</f>
         <v/>
       </c>
+      <c r="F250" s="10">
+        <f>IF(OR($A250="",$B250=""),"",IFERROR($C250*INDEX(INSUMOS!$K$5:$K$67,MATCH($B250,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="7" t="n"/>
@@ -10643,6 +11648,10 @@
         <f>IFERROR(C251*D251,0)</f>
         <v/>
       </c>
+      <c r="F251" s="10">
+        <f>IF(OR($A251="",$B251=""),"",IFERROR($C251*INDEX(INSUMOS!$K$5:$K$67,MATCH($B251,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="7" t="n"/>
@@ -10656,6 +11665,10 @@
         <f>IFERROR(C252*D252,0)</f>
         <v/>
       </c>
+      <c r="F252" s="10">
+        <f>IF(OR($A252="",$B252=""),"",IFERROR($C252*INDEX(INSUMOS!$K$5:$K$67,MATCH($B252,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="7" t="n"/>
@@ -10669,6 +11682,10 @@
         <f>IFERROR(C253*D253,0)</f>
         <v/>
       </c>
+      <c r="F253" s="10">
+        <f>IF(OR($A253="",$B253=""),"",IFERROR($C253*INDEX(INSUMOS!$K$5:$K$67,MATCH($B253,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="7" t="n"/>
@@ -10682,6 +11699,10 @@
         <f>IFERROR(C254*D254,0)</f>
         <v/>
       </c>
+      <c r="F254" s="10">
+        <f>IF(OR($A254="",$B254=""),"",IFERROR($C254*INDEX(INSUMOS!$K$5:$K$67,MATCH($B254,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="7" t="n"/>
@@ -10695,6 +11716,10 @@
         <f>IFERROR(C255*D255,0)</f>
         <v/>
       </c>
+      <c r="F255" s="10">
+        <f>IF(OR($A255="",$B255=""),"",IFERROR($C255*INDEX(INSUMOS!$K$5:$K$67,MATCH($B255,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="7" t="n"/>
@@ -10708,6 +11733,10 @@
         <f>IFERROR(C256*D256,0)</f>
         <v/>
       </c>
+      <c r="F256" s="10">
+        <f>IF(OR($A256="",$B256=""),"",IFERROR($C256*INDEX(INSUMOS!$K$5:$K$67,MATCH($B256,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="7" t="n"/>
@@ -10721,6 +11750,10 @@
         <f>IFERROR(C257*D257,0)</f>
         <v/>
       </c>
+      <c r="F257" s="10">
+        <f>IF(OR($A257="",$B257=""),"",IFERROR($C257*INDEX(INSUMOS!$K$5:$K$67,MATCH($B257,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="7" t="n"/>
@@ -10734,6 +11767,10 @@
         <f>IFERROR(C258*D258,0)</f>
         <v/>
       </c>
+      <c r="F258" s="10">
+        <f>IF(OR($A258="",$B258=""),"",IFERROR($C258*INDEX(INSUMOS!$K$5:$K$67,MATCH($B258,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="7" t="n"/>
@@ -10747,6 +11784,10 @@
         <f>IFERROR(C259*D259,0)</f>
         <v/>
       </c>
+      <c r="F259" s="10">
+        <f>IF(OR($A259="",$B259=""),"",IFERROR($C259*INDEX(INSUMOS!$K$5:$K$67,MATCH($B259,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="7" t="n"/>
@@ -10760,6 +11801,10 @@
         <f>IFERROR(C260*D260,0)</f>
         <v/>
       </c>
+      <c r="F260" s="10">
+        <f>IF(OR($A260="",$B260=""),"",IFERROR($C260*INDEX(INSUMOS!$K$5:$K$67,MATCH($B260,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="7" t="n"/>
@@ -10773,6 +11818,10 @@
         <f>IFERROR(C261*D261,0)</f>
         <v/>
       </c>
+      <c r="F261" s="10">
+        <f>IF(OR($A261="",$B261=""),"",IFERROR($C261*INDEX(INSUMOS!$K$5:$K$67,MATCH($B261,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="7" t="n"/>
@@ -10786,6 +11835,10 @@
         <f>IFERROR(C262*D262,0)</f>
         <v/>
       </c>
+      <c r="F262" s="10">
+        <f>IF(OR($A262="",$B262=""),"",IFERROR($C262*INDEX(INSUMOS!$K$5:$K$67,MATCH($B262,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="7" t="n"/>
@@ -10799,6 +11852,10 @@
         <f>IFERROR(C263*D263,0)</f>
         <v/>
       </c>
+      <c r="F263" s="10">
+        <f>IF(OR($A263="",$B263=""),"",IFERROR($C263*INDEX(INSUMOS!$K$5:$K$67,MATCH($B263,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="7" t="n"/>
@@ -10812,6 +11869,10 @@
         <f>IFERROR(C264*D264,0)</f>
         <v/>
       </c>
+      <c r="F264" s="10">
+        <f>IF(OR($A264="",$B264=""),"",IFERROR($C264*INDEX(INSUMOS!$K$5:$K$67,MATCH($B264,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="7" t="n"/>
@@ -10825,6 +11886,10 @@
         <f>IFERROR(C265*D265,0)</f>
         <v/>
       </c>
+      <c r="F265" s="10">
+        <f>IF(OR($A265="",$B265=""),"",IFERROR($C265*INDEX(INSUMOS!$K$5:$K$67,MATCH($B265,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="7" t="n"/>
@@ -10838,6 +11903,10 @@
         <f>IFERROR(C266*D266,0)</f>
         <v/>
       </c>
+      <c r="F266" s="10">
+        <f>IF(OR($A266="",$B266=""),"",IFERROR($C266*INDEX(INSUMOS!$K$5:$K$67,MATCH($B266,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="7" t="n"/>
@@ -10851,6 +11920,10 @@
         <f>IFERROR(C267*D267,0)</f>
         <v/>
       </c>
+      <c r="F267" s="10">
+        <f>IF(OR($A267="",$B267=""),"",IFERROR($C267*INDEX(INSUMOS!$K$5:$K$67,MATCH($B267,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="7" t="n"/>
@@ -10864,6 +11937,10 @@
         <f>IFERROR(C268*D268,0)</f>
         <v/>
       </c>
+      <c r="F268" s="10">
+        <f>IF(OR($A268="",$B268=""),"",IFERROR($C268*INDEX(INSUMOS!$K$5:$K$67,MATCH($B268,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="7" t="n"/>
@@ -10877,6 +11954,10 @@
         <f>IFERROR(C269*D269,0)</f>
         <v/>
       </c>
+      <c r="F269" s="10">
+        <f>IF(OR($A269="",$B269=""),"",IFERROR($C269*INDEX(INSUMOS!$K$5:$K$67,MATCH($B269,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="7" t="n"/>
@@ -10890,6 +11971,10 @@
         <f>IFERROR(C270*D270,0)</f>
         <v/>
       </c>
+      <c r="F270" s="10">
+        <f>IF(OR($A270="",$B270=""),"",IFERROR($C270*INDEX(INSUMOS!$K$5:$K$67,MATCH($B270,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="7" t="n"/>
@@ -10903,6 +11988,10 @@
         <f>IFERROR(C271*D271,0)</f>
         <v/>
       </c>
+      <c r="F271" s="10">
+        <f>IF(OR($A271="",$B271=""),"",IFERROR($C271*INDEX(INSUMOS!$K$5:$K$67,MATCH($B271,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="7" t="n"/>
@@ -10916,6 +12005,10 @@
         <f>IFERROR(C272*D272,0)</f>
         <v/>
       </c>
+      <c r="F272" s="10">
+        <f>IF(OR($A272="",$B272=""),"",IFERROR($C272*INDEX(INSUMOS!$K$5:$K$67,MATCH($B272,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="7" t="n"/>
@@ -10929,6 +12022,10 @@
         <f>IFERROR(C273*D273,0)</f>
         <v/>
       </c>
+      <c r="F273" s="10">
+        <f>IF(OR($A273="",$B273=""),"",IFERROR($C273*INDEX(INSUMOS!$K$5:$K$67,MATCH($B273,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="7" t="n"/>
@@ -10942,6 +12039,10 @@
         <f>IFERROR(C274*D274,0)</f>
         <v/>
       </c>
+      <c r="F274" s="10">
+        <f>IF(OR($A274="",$B274=""),"",IFERROR($C274*INDEX(INSUMOS!$K$5:$K$67,MATCH($B274,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="7" t="n"/>
@@ -10955,6 +12056,10 @@
         <f>IFERROR(C275*D275,0)</f>
         <v/>
       </c>
+      <c r="F275" s="10">
+        <f>IF(OR($A275="",$B275=""),"",IFERROR($C275*INDEX(INSUMOS!$K$5:$K$67,MATCH($B275,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="7" t="n"/>
@@ -10968,6 +12073,10 @@
         <f>IFERROR(C276*D276,0)</f>
         <v/>
       </c>
+      <c r="F276" s="10">
+        <f>IF(OR($A276="",$B276=""),"",IFERROR($C276*INDEX(INSUMOS!$K$5:$K$67,MATCH($B276,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="7" t="n"/>
@@ -10981,6 +12090,10 @@
         <f>IFERROR(C277*D277,0)</f>
         <v/>
       </c>
+      <c r="F277" s="10">
+        <f>IF(OR($A277="",$B277=""),"",IFERROR($C277*INDEX(INSUMOS!$K$5:$K$67,MATCH($B277,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="7" t="n"/>
@@ -10994,6 +12107,10 @@
         <f>IFERROR(C278*D278,0)</f>
         <v/>
       </c>
+      <c r="F278" s="10">
+        <f>IF(OR($A278="",$B278=""),"",IFERROR($C278*INDEX(INSUMOS!$K$5:$K$67,MATCH($B278,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="7" t="n"/>
@@ -11007,6 +12124,10 @@
         <f>IFERROR(C279*D279,0)</f>
         <v/>
       </c>
+      <c r="F279" s="10">
+        <f>IF(OR($A279="",$B279=""),"",IFERROR($C279*INDEX(INSUMOS!$K$5:$K$67,MATCH($B279,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="7" t="n"/>
@@ -11020,6 +12141,10 @@
         <f>IFERROR(C280*D280,0)</f>
         <v/>
       </c>
+      <c r="F280" s="10">
+        <f>IF(OR($A280="",$B280=""),"",IFERROR($C280*INDEX(INSUMOS!$K$5:$K$67,MATCH($B280,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="7" t="n"/>
@@ -11033,6 +12158,10 @@
         <f>IFERROR(C281*D281,0)</f>
         <v/>
       </c>
+      <c r="F281" s="10">
+        <f>IF(OR($A281="",$B281=""),"",IFERROR($C281*INDEX(INSUMOS!$K$5:$K$67,MATCH($B281,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="7" t="n"/>
@@ -11046,6 +12175,10 @@
         <f>IFERROR(C282*D282,0)</f>
         <v/>
       </c>
+      <c r="F282" s="10">
+        <f>IF(OR($A282="",$B282=""),"",IFERROR($C282*INDEX(INSUMOS!$K$5:$K$67,MATCH($B282,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="7" t="n"/>
@@ -11059,6 +12192,10 @@
         <f>IFERROR(C283*D283,0)</f>
         <v/>
       </c>
+      <c r="F283" s="10">
+        <f>IF(OR($A283="",$B283=""),"",IFERROR($C283*INDEX(INSUMOS!$K$5:$K$67,MATCH($B283,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="7" t="n"/>
@@ -11072,6 +12209,10 @@
         <f>IFERROR(C284*D284,0)</f>
         <v/>
       </c>
+      <c r="F284" s="10">
+        <f>IF(OR($A284="",$B284=""),"",IFERROR($C284*INDEX(INSUMOS!$K$5:$K$67,MATCH($B284,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="7" t="n"/>
@@ -11085,6 +12226,10 @@
         <f>IFERROR(C285*D285,0)</f>
         <v/>
       </c>
+      <c r="F285" s="10">
+        <f>IF(OR($A285="",$B285=""),"",IFERROR($C285*INDEX(INSUMOS!$K$5:$K$67,MATCH($B285,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="7" t="n"/>
@@ -11098,6 +12243,10 @@
         <f>IFERROR(C286*D286,0)</f>
         <v/>
       </c>
+      <c r="F286" s="10">
+        <f>IF(OR($A286="",$B286=""),"",IFERROR($C286*INDEX(INSUMOS!$K$5:$K$67,MATCH($B286,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="7" t="n"/>
@@ -11111,6 +12260,10 @@
         <f>IFERROR(C287*D287,0)</f>
         <v/>
       </c>
+      <c r="F287" s="10">
+        <f>IF(OR($A287="",$B287=""),"",IFERROR($C287*INDEX(INSUMOS!$K$5:$K$67,MATCH($B287,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="7" t="n"/>
@@ -11124,6 +12277,10 @@
         <f>IFERROR(C288*D288,0)</f>
         <v/>
       </c>
+      <c r="F288" s="10">
+        <f>IF(OR($A288="",$B288=""),"",IFERROR($C288*INDEX(INSUMOS!$K$5:$K$67,MATCH($B288,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="7" t="n"/>
@@ -11137,6 +12294,10 @@
         <f>IFERROR(C289*D289,0)</f>
         <v/>
       </c>
+      <c r="F289" s="10">
+        <f>IF(OR($A289="",$B289=""),"",IFERROR($C289*INDEX(INSUMOS!$K$5:$K$67,MATCH($B289,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="7" t="n"/>
@@ -11150,6 +12311,10 @@
         <f>IFERROR(C290*D290,0)</f>
         <v/>
       </c>
+      <c r="F290" s="10">
+        <f>IF(OR($A290="",$B290=""),"",IFERROR($C290*INDEX(INSUMOS!$K$5:$K$67,MATCH($B290,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="7" t="n"/>
@@ -11163,6 +12328,10 @@
         <f>IFERROR(C291*D291,0)</f>
         <v/>
       </c>
+      <c r="F291" s="10">
+        <f>IF(OR($A291="",$B291=""),"",IFERROR($C291*INDEX(INSUMOS!$K$5:$K$67,MATCH($B291,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="7" t="n"/>
@@ -11176,6 +12345,10 @@
         <f>IFERROR(C292*D292,0)</f>
         <v/>
       </c>
+      <c r="F292" s="10">
+        <f>IF(OR($A292="",$B292=""),"",IFERROR($C292*INDEX(INSUMOS!$K$5:$K$67,MATCH($B292,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="7" t="n"/>
@@ -11189,6 +12362,10 @@
         <f>IFERROR(C293*D293,0)</f>
         <v/>
       </c>
+      <c r="F293" s="10">
+        <f>IF(OR($A293="",$B293=""),"",IFERROR($C293*INDEX(INSUMOS!$K$5:$K$67,MATCH($B293,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="7" t="n"/>
@@ -11202,6 +12379,10 @@
         <f>IFERROR(C294*D294,0)</f>
         <v/>
       </c>
+      <c r="F294" s="10">
+        <f>IF(OR($A294="",$B294=""),"",IFERROR($C294*INDEX(INSUMOS!$K$5:$K$67,MATCH($B294,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="7" t="n"/>
@@ -11215,6 +12396,10 @@
         <f>IFERROR(C295*D295,0)</f>
         <v/>
       </c>
+      <c r="F295" s="10">
+        <f>IF(OR($A295="",$B295=""),"",IFERROR($C295*INDEX(INSUMOS!$K$5:$K$67,MATCH($B295,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="7" t="n"/>
@@ -11228,6 +12413,10 @@
         <f>IFERROR(C296*D296,0)</f>
         <v/>
       </c>
+      <c r="F296" s="10">
+        <f>IF(OR($A296="",$B296=""),"",IFERROR($C296*INDEX(INSUMOS!$K$5:$K$67,MATCH($B296,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="7" t="n"/>
@@ -11241,6 +12430,10 @@
         <f>IFERROR(C297*D297,0)</f>
         <v/>
       </c>
+      <c r="F297" s="10">
+        <f>IF(OR($A297="",$B297=""),"",IFERROR($C297*INDEX(INSUMOS!$K$5:$K$67,MATCH($B297,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="7" t="n"/>
@@ -11254,6 +12447,10 @@
         <f>IFERROR(C298*D298,0)</f>
         <v/>
       </c>
+      <c r="F298" s="10">
+        <f>IF(OR($A298="",$B298=""),"",IFERROR($C298*INDEX(INSUMOS!$K$5:$K$67,MATCH($B298,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="7" t="n"/>
@@ -11267,6 +12464,10 @@
         <f>IFERROR(C299*D299,0)</f>
         <v/>
       </c>
+      <c r="F299" s="10">
+        <f>IF(OR($A299="",$B299=""),"",IFERROR($C299*INDEX(INSUMOS!$K$5:$K$67,MATCH($B299,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="7" t="n"/>
@@ -11280,6 +12481,10 @@
         <f>IFERROR(C300*D300,0)</f>
         <v/>
       </c>
+      <c r="F300" s="10">
+        <f>IF(OR($A300="",$B300=""),"",IFERROR($C300*INDEX(INSUMOS!$K$5:$K$67,MATCH($B300,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="7" t="n"/>
@@ -11293,6 +12498,10 @@
         <f>IFERROR(C301*D301,0)</f>
         <v/>
       </c>
+      <c r="F301" s="10">
+        <f>IF(OR($A301="",$B301=""),"",IFERROR($C301*INDEX(INSUMOS!$K$5:$K$67,MATCH($B301,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="7" t="n"/>
@@ -11306,6 +12515,10 @@
         <f>IFERROR(C302*D302,0)</f>
         <v/>
       </c>
+      <c r="F302" s="10">
+        <f>IF(OR($A302="",$B302=""),"",IFERROR($C302*INDEX(INSUMOS!$K$5:$K$67,MATCH($B302,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="7" t="n"/>
@@ -11319,6 +12532,10 @@
         <f>IFERROR(C303*D303,0)</f>
         <v/>
       </c>
+      <c r="F303" s="10">
+        <f>IF(OR($A303="",$B303=""),"",IFERROR($C303*INDEX(INSUMOS!$K$5:$K$67,MATCH($B303,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="7" t="n"/>
@@ -11332,6 +12549,10 @@
         <f>IFERROR(C304*D304,0)</f>
         <v/>
       </c>
+      <c r="F304" s="10">
+        <f>IF(OR($A304="",$B304=""),"",IFERROR($C304*INDEX(INSUMOS!$K$5:$K$67,MATCH($B304,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="7" t="n"/>
@@ -11345,6 +12566,10 @@
         <f>IFERROR(C305*D305,0)</f>
         <v/>
       </c>
+      <c r="F305" s="10">
+        <f>IF(OR($A305="",$B305=""),"",IFERROR($C305*INDEX(INSUMOS!$K$5:$K$67,MATCH($B305,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="7" t="n"/>
@@ -11358,6 +12583,10 @@
         <f>IFERROR(C306*D306,0)</f>
         <v/>
       </c>
+      <c r="F306" s="10">
+        <f>IF(OR($A306="",$B306=""),"",IFERROR($C306*INDEX(INSUMOS!$K$5:$K$67,MATCH($B306,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="7" t="n"/>
@@ -11371,6 +12600,10 @@
         <f>IFERROR(C307*D307,0)</f>
         <v/>
       </c>
+      <c r="F307" s="10">
+        <f>IF(OR($A307="",$B307=""),"",IFERROR($C307*INDEX(INSUMOS!$K$5:$K$67,MATCH($B307,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="7" t="n"/>
@@ -11384,6 +12617,10 @@
         <f>IFERROR(C308*D308,0)</f>
         <v/>
       </c>
+      <c r="F308" s="10">
+        <f>IF(OR($A308="",$B308=""),"",IFERROR($C308*INDEX(INSUMOS!$K$5:$K$67,MATCH($B308,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="7" t="n"/>
@@ -11397,6 +12634,10 @@
         <f>IFERROR(C309*D309,0)</f>
         <v/>
       </c>
+      <c r="F309" s="10">
+        <f>IF(OR($A309="",$B309=""),"",IFERROR($C309*INDEX(INSUMOS!$K$5:$K$67,MATCH($B309,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="7" t="n"/>
@@ -11410,6 +12651,10 @@
         <f>IFERROR(C310*D310,0)</f>
         <v/>
       </c>
+      <c r="F310" s="10">
+        <f>IF(OR($A310="",$B310=""),"",IFERROR($C310*INDEX(INSUMOS!$K$5:$K$67,MATCH($B310,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="7" t="n"/>
@@ -11423,6 +12668,10 @@
         <f>IFERROR(C311*D311,0)</f>
         <v/>
       </c>
+      <c r="F311" s="10">
+        <f>IF(OR($A311="",$B311=""),"",IFERROR($C311*INDEX(INSUMOS!$K$5:$K$67,MATCH($B311,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="7" t="n"/>
@@ -11436,6 +12685,10 @@
         <f>IFERROR(C312*D312,0)</f>
         <v/>
       </c>
+      <c r="F312" s="10">
+        <f>IF(OR($A312="",$B312=""),"",IFERROR($C312*INDEX(INSUMOS!$K$5:$K$67,MATCH($B312,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="7" t="n"/>
@@ -11449,6 +12702,10 @@
         <f>IFERROR(C313*D313,0)</f>
         <v/>
       </c>
+      <c r="F313" s="10">
+        <f>IF(OR($A313="",$B313=""),"",IFERROR($C313*INDEX(INSUMOS!$K$5:$K$67,MATCH($B313,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="7" t="n"/>
@@ -11462,6 +12719,10 @@
         <f>IFERROR(C314*D314,0)</f>
         <v/>
       </c>
+      <c r="F314" s="10">
+        <f>IF(OR($A314="",$B314=""),"",IFERROR($C314*INDEX(INSUMOS!$K$5:$K$67,MATCH($B314,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="7" t="n"/>
@@ -11475,6 +12736,10 @@
         <f>IFERROR(C315*D315,0)</f>
         <v/>
       </c>
+      <c r="F315" s="10">
+        <f>IF(OR($A315="",$B315=""),"",IFERROR($C315*INDEX(INSUMOS!$K$5:$K$67,MATCH($B315,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="7" t="n"/>
@@ -11488,6 +12753,10 @@
         <f>IFERROR(C316*D316,0)</f>
         <v/>
       </c>
+      <c r="F316" s="10">
+        <f>IF(OR($A316="",$B316=""),"",IFERROR($C316*INDEX(INSUMOS!$K$5:$K$67,MATCH($B316,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="7" t="n"/>
@@ -11501,6 +12770,10 @@
         <f>IFERROR(C317*D317,0)</f>
         <v/>
       </c>
+      <c r="F317" s="10">
+        <f>IF(OR($A317="",$B317=""),"",IFERROR($C317*INDEX(INSUMOS!$K$5:$K$67,MATCH($B317,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="7" t="n"/>
@@ -11514,6 +12787,10 @@
         <f>IFERROR(C318*D318,0)</f>
         <v/>
       </c>
+      <c r="F318" s="10">
+        <f>IF(OR($A318="",$B318=""),"",IFERROR($C318*INDEX(INSUMOS!$K$5:$K$67,MATCH($B318,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="7" t="n"/>
@@ -11527,6 +12804,10 @@
         <f>IFERROR(C319*D319,0)</f>
         <v/>
       </c>
+      <c r="F319" s="10">
+        <f>IF(OR($A319="",$B319=""),"",IFERROR($C319*INDEX(INSUMOS!$K$5:$K$67,MATCH($B319,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="7" t="n"/>
@@ -11540,6 +12821,10 @@
         <f>IFERROR(C320*D320,0)</f>
         <v/>
       </c>
+      <c r="F320" s="10">
+        <f>IF(OR($A320="",$B320=""),"",IFERROR($C320*INDEX(INSUMOS!$K$5:$K$67,MATCH($B320,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="7" t="n"/>
@@ -11553,6 +12838,10 @@
         <f>IFERROR(C321*D321,0)</f>
         <v/>
       </c>
+      <c r="F321" s="10">
+        <f>IF(OR($A321="",$B321=""),"",IFERROR($C321*INDEX(INSUMOS!$K$5:$K$67,MATCH($B321,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="7" t="n"/>
@@ -11566,6 +12855,10 @@
         <f>IFERROR(C322*D322,0)</f>
         <v/>
       </c>
+      <c r="F322" s="10">
+        <f>IF(OR($A322="",$B322=""),"",IFERROR($C322*INDEX(INSUMOS!$K$5:$K$67,MATCH($B322,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="7" t="n"/>
@@ -11579,6 +12872,10 @@
         <f>IFERROR(C323*D323,0)</f>
         <v/>
       </c>
+      <c r="F323" s="10">
+        <f>IF(OR($A323="",$B323=""),"",IFERROR($C323*INDEX(INSUMOS!$K$5:$K$67,MATCH($B323,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="7" t="n"/>
@@ -11592,6 +12889,10 @@
         <f>IFERROR(C324*D324,0)</f>
         <v/>
       </c>
+      <c r="F324" s="10">
+        <f>IF(OR($A324="",$B324=""),"",IFERROR($C324*INDEX(INSUMOS!$K$5:$K$67,MATCH($B324,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="7" t="n"/>
@@ -11605,6 +12906,10 @@
         <f>IFERROR(C325*D325,0)</f>
         <v/>
       </c>
+      <c r="F325" s="10">
+        <f>IF(OR($A325="",$B325=""),"",IFERROR($C325*INDEX(INSUMOS!$K$5:$K$67,MATCH($B325,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="7" t="n"/>
@@ -11618,6 +12923,10 @@
         <f>IFERROR(C326*D326,0)</f>
         <v/>
       </c>
+      <c r="F326" s="10">
+        <f>IF(OR($A326="",$B326=""),"",IFERROR($C326*INDEX(INSUMOS!$K$5:$K$67,MATCH($B326,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="7" t="n"/>
@@ -11631,6 +12940,10 @@
         <f>IFERROR(C327*D327,0)</f>
         <v/>
       </c>
+      <c r="F327" s="10">
+        <f>IF(OR($A327="",$B327=""),"",IFERROR($C327*INDEX(INSUMOS!$K$5:$K$67,MATCH($B327,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="7" t="n"/>
@@ -11644,6 +12957,10 @@
         <f>IFERROR(C328*D328,0)</f>
         <v/>
       </c>
+      <c r="F328" s="10">
+        <f>IF(OR($A328="",$B328=""),"",IFERROR($C328*INDEX(INSUMOS!$K$5:$K$67,MATCH($B328,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="7" t="n"/>
@@ -11657,6 +12974,10 @@
         <f>IFERROR(C329*D329,0)</f>
         <v/>
       </c>
+      <c r="F329" s="10">
+        <f>IF(OR($A329="",$B329=""),"",IFERROR($C329*INDEX(INSUMOS!$K$5:$K$67,MATCH($B329,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="7" t="n"/>
@@ -11670,6 +12991,10 @@
         <f>IFERROR(C330*D330,0)</f>
         <v/>
       </c>
+      <c r="F330" s="10">
+        <f>IF(OR($A330="",$B330=""),"",IFERROR($C330*INDEX(INSUMOS!$K$5:$K$67,MATCH($B330,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="7" t="n"/>
@@ -11683,6 +13008,10 @@
         <f>IFERROR(C331*D331,0)</f>
         <v/>
       </c>
+      <c r="F331" s="10">
+        <f>IF(OR($A331="",$B331=""),"",IFERROR($C331*INDEX(INSUMOS!$K$5:$K$67,MATCH($B331,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="7" t="n"/>
@@ -11696,6 +13025,10 @@
         <f>IFERROR(C332*D332,0)</f>
         <v/>
       </c>
+      <c r="F332" s="10">
+        <f>IF(OR($A332="",$B332=""),"",IFERROR($C332*INDEX(INSUMOS!$K$5:$K$67,MATCH($B332,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="7" t="n"/>
@@ -11709,6 +13042,10 @@
         <f>IFERROR(C333*D333,0)</f>
         <v/>
       </c>
+      <c r="F333" s="10">
+        <f>IF(OR($A333="",$B333=""),"",IFERROR($C333*INDEX(INSUMOS!$K$5:$K$67,MATCH($B333,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="7" t="n"/>
@@ -11722,6 +13059,10 @@
         <f>IFERROR(C334*D334,0)</f>
         <v/>
       </c>
+      <c r="F334" s="10">
+        <f>IF(OR($A334="",$B334=""),"",IFERROR($C334*INDEX(INSUMOS!$K$5:$K$67,MATCH($B334,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="7" t="n"/>
@@ -11735,6 +13076,10 @@
         <f>IFERROR(C335*D335,0)</f>
         <v/>
       </c>
+      <c r="F335" s="10">
+        <f>IF(OR($A335="",$B335=""),"",IFERROR($C335*INDEX(INSUMOS!$K$5:$K$67,MATCH($B335,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="7" t="n"/>
@@ -11748,6 +13093,10 @@
         <f>IFERROR(C336*D336,0)</f>
         <v/>
       </c>
+      <c r="F336" s="10">
+        <f>IF(OR($A336="",$B336=""),"",IFERROR($C336*INDEX(INSUMOS!$K$5:$K$67,MATCH($B336,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="7" t="n"/>
@@ -11761,6 +13110,10 @@
         <f>IFERROR(C337*D337,0)</f>
         <v/>
       </c>
+      <c r="F337" s="10">
+        <f>IF(OR($A337="",$B337=""),"",IFERROR($C337*INDEX(INSUMOS!$K$5:$K$67,MATCH($B337,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="7" t="n"/>
@@ -11774,6 +13127,10 @@
         <f>IFERROR(C338*D338,0)</f>
         <v/>
       </c>
+      <c r="F338" s="10">
+        <f>IF(OR($A338="",$B338=""),"",IFERROR($C338*INDEX(INSUMOS!$K$5:$K$67,MATCH($B338,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="7" t="n"/>
@@ -11787,6 +13144,10 @@
         <f>IFERROR(C339*D339,0)</f>
         <v/>
       </c>
+      <c r="F339" s="10">
+        <f>IF(OR($A339="",$B339=""),"",IFERROR($C339*INDEX(INSUMOS!$K$5:$K$67,MATCH($B339,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="7" t="n"/>
@@ -11800,6 +13161,10 @@
         <f>IFERROR(C340*D340,0)</f>
         <v/>
       </c>
+      <c r="F340" s="10">
+        <f>IF(OR($A340="",$B340=""),"",IFERROR($C340*INDEX(INSUMOS!$K$5:$K$67,MATCH($B340,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="7" t="n"/>
@@ -11813,6 +13178,10 @@
         <f>IFERROR(C341*D341,0)</f>
         <v/>
       </c>
+      <c r="F341" s="10">
+        <f>IF(OR($A341="",$B341=""),"",IFERROR($C341*INDEX(INSUMOS!$K$5:$K$67,MATCH($B341,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="7" t="n"/>
@@ -11826,6 +13195,10 @@
         <f>IFERROR(C342*D342,0)</f>
         <v/>
       </c>
+      <c r="F342" s="10">
+        <f>IF(OR($A342="",$B342=""),"",IFERROR($C342*INDEX(INSUMOS!$K$5:$K$67,MATCH($B342,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="7" t="n"/>
@@ -11839,6 +13212,10 @@
         <f>IFERROR(C343*D343,0)</f>
         <v/>
       </c>
+      <c r="F343" s="10">
+        <f>IF(OR($A343="",$B343=""),"",IFERROR($C343*INDEX(INSUMOS!$K$5:$K$67,MATCH($B343,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="7" t="n"/>
@@ -11852,6 +13229,10 @@
         <f>IFERROR(C344*D344,0)</f>
         <v/>
       </c>
+      <c r="F344" s="10">
+        <f>IF(OR($A344="",$B344=""),"",IFERROR($C344*INDEX(INSUMOS!$K$5:$K$67,MATCH($B344,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="7" t="n"/>
@@ -11865,6 +13246,10 @@
         <f>IFERROR(C345*D345,0)</f>
         <v/>
       </c>
+      <c r="F345" s="10">
+        <f>IF(OR($A345="",$B345=""),"",IFERROR($C345*INDEX(INSUMOS!$K$5:$K$67,MATCH($B345,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="7" t="n"/>
@@ -11878,6 +13263,10 @@
         <f>IFERROR(C346*D346,0)</f>
         <v/>
       </c>
+      <c r="F346" s="10">
+        <f>IF(OR($A346="",$B346=""),"",IFERROR($C346*INDEX(INSUMOS!$K$5:$K$67,MATCH($B346,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="7" t="n"/>
@@ -11891,6 +13280,10 @@
         <f>IFERROR(C347*D347,0)</f>
         <v/>
       </c>
+      <c r="F347" s="10">
+        <f>IF(OR($A347="",$B347=""),"",IFERROR($C347*INDEX(INSUMOS!$K$5:$K$67,MATCH($B347,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="7" t="n"/>
@@ -11904,6 +13297,10 @@
         <f>IFERROR(C348*D348,0)</f>
         <v/>
       </c>
+      <c r="F348" s="10">
+        <f>IF(OR($A348="",$B348=""),"",IFERROR($C348*INDEX(INSUMOS!$K$5:$K$67,MATCH($B348,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="7" t="n"/>
@@ -11917,6 +13314,10 @@
         <f>IFERROR(C349*D349,0)</f>
         <v/>
       </c>
+      <c r="F349" s="10">
+        <f>IF(OR($A349="",$B349=""),"",IFERROR($C349*INDEX(INSUMOS!$K$5:$K$67,MATCH($B349,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="7" t="n"/>
@@ -11930,6 +13331,10 @@
         <f>IFERROR(C350*D350,0)</f>
         <v/>
       </c>
+      <c r="F350" s="10">
+        <f>IF(OR($A350="",$B350=""),"",IFERROR($C350*INDEX(INSUMOS!$K$5:$K$67,MATCH($B350,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="7" t="n"/>
@@ -11943,6 +13348,10 @@
         <f>IFERROR(C351*D351,0)</f>
         <v/>
       </c>
+      <c r="F351" s="10">
+        <f>IF(OR($A351="",$B351=""),"",IFERROR($C351*INDEX(INSUMOS!$K$5:$K$67,MATCH($B351,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="7" t="n"/>
@@ -11956,6 +13365,10 @@
         <f>IFERROR(C352*D352,0)</f>
         <v/>
       </c>
+      <c r="F352" s="10">
+        <f>IF(OR($A352="",$B352=""),"",IFERROR($C352*INDEX(INSUMOS!$K$5:$K$67,MATCH($B352,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="7" t="n"/>
@@ -11969,6 +13382,10 @@
         <f>IFERROR(C353*D353,0)</f>
         <v/>
       </c>
+      <c r="F353" s="10">
+        <f>IF(OR($A353="",$B353=""),"",IFERROR($C353*INDEX(INSUMOS!$K$5:$K$67,MATCH($B353,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="7" t="n"/>
@@ -11982,6 +13399,10 @@
         <f>IFERROR(C354*D354,0)</f>
         <v/>
       </c>
+      <c r="F354" s="10">
+        <f>IF(OR($A354="",$B354=""),"",IFERROR($C354*INDEX(INSUMOS!$K$5:$K$67,MATCH($B354,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="7" t="n"/>
@@ -11995,6 +13416,10 @@
         <f>IFERROR(C355*D355,0)</f>
         <v/>
       </c>
+      <c r="F355" s="10">
+        <f>IF(OR($A355="",$B355=""),"",IFERROR($C355*INDEX(INSUMOS!$K$5:$K$67,MATCH($B355,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="7" t="n"/>
@@ -12008,6 +13433,10 @@
         <f>IFERROR(C356*D356,0)</f>
         <v/>
       </c>
+      <c r="F356" s="10">
+        <f>IF(OR($A356="",$B356=""),"",IFERROR($C356*INDEX(INSUMOS!$K$5:$K$67,MATCH($B356,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="7" t="n"/>
@@ -12021,6 +13450,10 @@
         <f>IFERROR(C357*D357,0)</f>
         <v/>
       </c>
+      <c r="F357" s="10">
+        <f>IF(OR($A357="",$B357=""),"",IFERROR($C357*INDEX(INSUMOS!$K$5:$K$67,MATCH($B357,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="7" t="n"/>
@@ -12034,6 +13467,10 @@
         <f>IFERROR(C358*D358,0)</f>
         <v/>
       </c>
+      <c r="F358" s="10">
+        <f>IF(OR($A358="",$B358=""),"",IFERROR($C358*INDEX(INSUMOS!$K$5:$K$67,MATCH($B358,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="7" t="n"/>
@@ -12047,6 +13484,10 @@
         <f>IFERROR(C359*D359,0)</f>
         <v/>
       </c>
+      <c r="F359" s="10">
+        <f>IF(OR($A359="",$B359=""),"",IFERROR($C359*INDEX(INSUMOS!$K$5:$K$67,MATCH($B359,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="7" t="n"/>
@@ -12060,6 +13501,10 @@
         <f>IFERROR(C360*D360,0)</f>
         <v/>
       </c>
+      <c r="F360" s="10">
+        <f>IF(OR($A360="",$B360=""),"",IFERROR($C360*INDEX(INSUMOS!$K$5:$K$67,MATCH($B360,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="7" t="n"/>
@@ -12073,6 +13518,10 @@
         <f>IFERROR(C361*D361,0)</f>
         <v/>
       </c>
+      <c r="F361" s="10">
+        <f>IF(OR($A361="",$B361=""),"",IFERROR($C361*INDEX(INSUMOS!$K$5:$K$67,MATCH($B361,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="7" t="n"/>
@@ -12086,6 +13535,10 @@
         <f>IFERROR(C362*D362,0)</f>
         <v/>
       </c>
+      <c r="F362" s="10">
+        <f>IF(OR($A362="",$B362=""),"",IFERROR($C362*INDEX(INSUMOS!$K$5:$K$67,MATCH($B362,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="7" t="n"/>
@@ -12099,6 +13552,10 @@
         <f>IFERROR(C363*D363,0)</f>
         <v/>
       </c>
+      <c r="F363" s="10">
+        <f>IF(OR($A363="",$B363=""),"",IFERROR($C363*INDEX(INSUMOS!$K$5:$K$67,MATCH($B363,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="7" t="n"/>
@@ -12112,6 +13569,10 @@
         <f>IFERROR(C364*D364,0)</f>
         <v/>
       </c>
+      <c r="F364" s="10">
+        <f>IF(OR($A364="",$B364=""),"",IFERROR($C364*INDEX(INSUMOS!$K$5:$K$67,MATCH($B364,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="7" t="n"/>
@@ -12125,6 +13586,10 @@
         <f>IFERROR(C365*D365,0)</f>
         <v/>
       </c>
+      <c r="F365" s="10">
+        <f>IF(OR($A365="",$B365=""),"",IFERROR($C365*INDEX(INSUMOS!$K$5:$K$67,MATCH($B365,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="7" t="n"/>
@@ -12138,6 +13603,10 @@
         <f>IFERROR(C366*D366,0)</f>
         <v/>
       </c>
+      <c r="F366" s="10">
+        <f>IF(OR($A366="",$B366=""),"",IFERROR($C366*INDEX(INSUMOS!$K$5:$K$67,MATCH($B366,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="7" t="n"/>
@@ -12151,6 +13620,10 @@
         <f>IFERROR(C367*D367,0)</f>
         <v/>
       </c>
+      <c r="F367" s="10">
+        <f>IF(OR($A367="",$B367=""),"",IFERROR($C367*INDEX(INSUMOS!$K$5:$K$67,MATCH($B367,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="7" t="n"/>
@@ -12164,6 +13637,10 @@
         <f>IFERROR(C368*D368,0)</f>
         <v/>
       </c>
+      <c r="F368" s="10">
+        <f>IF(OR($A368="",$B368=""),"",IFERROR($C368*INDEX(INSUMOS!$K$5:$K$67,MATCH($B368,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="7" t="n"/>
@@ -12177,6 +13654,10 @@
         <f>IFERROR(C369*D369,0)</f>
         <v/>
       </c>
+      <c r="F369" s="10">
+        <f>IF(OR($A369="",$B369=""),"",IFERROR($C369*INDEX(INSUMOS!$K$5:$K$67,MATCH($B369,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="7" t="n"/>
@@ -12190,6 +13671,10 @@
         <f>IFERROR(C370*D370,0)</f>
         <v/>
       </c>
+      <c r="F370" s="10">
+        <f>IF(OR($A370="",$B370=""),"",IFERROR($C370*INDEX(INSUMOS!$K$5:$K$67,MATCH($B370,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="7" t="n"/>
@@ -12203,6 +13688,10 @@
         <f>IFERROR(C371*D371,0)</f>
         <v/>
       </c>
+      <c r="F371" s="10">
+        <f>IF(OR($A371="",$B371=""),"",IFERROR($C371*INDEX(INSUMOS!$K$5:$K$67,MATCH($B371,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="7" t="n"/>
@@ -12216,6 +13705,10 @@
         <f>IFERROR(C372*D372,0)</f>
         <v/>
       </c>
+      <c r="F372" s="10">
+        <f>IF(OR($A372="",$B372=""),"",IFERROR($C372*INDEX(INSUMOS!$K$5:$K$67,MATCH($B372,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="7" t="n"/>
@@ -12229,6 +13722,10 @@
         <f>IFERROR(C373*D373,0)</f>
         <v/>
       </c>
+      <c r="F373" s="10">
+        <f>IF(OR($A373="",$B373=""),"",IFERROR($C373*INDEX(INSUMOS!$K$5:$K$67,MATCH($B373,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="7" t="n"/>
@@ -12242,6 +13739,10 @@
         <f>IFERROR(C374*D374,0)</f>
         <v/>
       </c>
+      <c r="F374" s="10">
+        <f>IF(OR($A374="",$B374=""),"",IFERROR($C374*INDEX(INSUMOS!$K$5:$K$67,MATCH($B374,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="7" t="n"/>
@@ -12255,6 +13756,10 @@
         <f>IFERROR(C375*D375,0)</f>
         <v/>
       </c>
+      <c r="F375" s="10">
+        <f>IF(OR($A375="",$B375=""),"",IFERROR($C375*INDEX(INSUMOS!$K$5:$K$67,MATCH($B375,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="7" t="n"/>
@@ -12268,6 +13773,10 @@
         <f>IFERROR(C376*D376,0)</f>
         <v/>
       </c>
+      <c r="F376" s="10">
+        <f>IF(OR($A376="",$B376=""),"",IFERROR($C376*INDEX(INSUMOS!$K$5:$K$67,MATCH($B376,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="7" t="n"/>
@@ -12281,6 +13790,10 @@
         <f>IFERROR(C377*D377,0)</f>
         <v/>
       </c>
+      <c r="F377" s="10">
+        <f>IF(OR($A377="",$B377=""),"",IFERROR($C377*INDEX(INSUMOS!$K$5:$K$67,MATCH($B377,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="7" t="n"/>
@@ -12294,6 +13807,10 @@
         <f>IFERROR(C378*D378,0)</f>
         <v/>
       </c>
+      <c r="F378" s="10">
+        <f>IF(OR($A378="",$B378=""),"",IFERROR($C378*INDEX(INSUMOS!$K$5:$K$67,MATCH($B378,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="7" t="n"/>
@@ -12307,6 +13824,10 @@
         <f>IFERROR(C379*D379,0)</f>
         <v/>
       </c>
+      <c r="F379" s="10">
+        <f>IF(OR($A379="",$B379=""),"",IFERROR($C379*INDEX(INSUMOS!$K$5:$K$67,MATCH($B379,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="7" t="n"/>
@@ -12320,6 +13841,10 @@
         <f>IFERROR(C380*D380,0)</f>
         <v/>
       </c>
+      <c r="F380" s="10">
+        <f>IF(OR($A380="",$B380=""),"",IFERROR($C380*INDEX(INSUMOS!$K$5:$K$67,MATCH($B380,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="7" t="n"/>
@@ -12333,6 +13858,10 @@
         <f>IFERROR(C381*D381,0)</f>
         <v/>
       </c>
+      <c r="F381" s="10">
+        <f>IF(OR($A381="",$B381=""),"",IFERROR($C381*INDEX(INSUMOS!$K$5:$K$67,MATCH($B381,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="7" t="n"/>
@@ -12346,6 +13875,10 @@
         <f>IFERROR(C382*D382,0)</f>
         <v/>
       </c>
+      <c r="F382" s="10">
+        <f>IF(OR($A382="",$B382=""),"",IFERROR($C382*INDEX(INSUMOS!$K$5:$K$67,MATCH($B382,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="7" t="n"/>
@@ -12359,6 +13892,10 @@
         <f>IFERROR(C383*D383,0)</f>
         <v/>
       </c>
+      <c r="F383" s="10">
+        <f>IF(OR($A383="",$B383=""),"",IFERROR($C383*INDEX(INSUMOS!$K$5:$K$67,MATCH($B383,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="7" t="n"/>
@@ -12372,6 +13909,10 @@
         <f>IFERROR(C384*D384,0)</f>
         <v/>
       </c>
+      <c r="F384" s="10">
+        <f>IF(OR($A384="",$B384=""),"",IFERROR($C384*INDEX(INSUMOS!$K$5:$K$67,MATCH($B384,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="7" t="n"/>
@@ -12385,6 +13926,10 @@
         <f>IFERROR(C385*D385,0)</f>
         <v/>
       </c>
+      <c r="F385" s="10">
+        <f>IF(OR($A385="",$B385=""),"",IFERROR($C385*INDEX(INSUMOS!$K$5:$K$67,MATCH($B385,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="7" t="n"/>
@@ -12398,6 +13943,10 @@
         <f>IFERROR(C386*D386,0)</f>
         <v/>
       </c>
+      <c r="F386" s="10">
+        <f>IF(OR($A386="",$B386=""),"",IFERROR($C386*INDEX(INSUMOS!$K$5:$K$67,MATCH($B386,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="7" t="n"/>
@@ -12411,6 +13960,10 @@
         <f>IFERROR(C387*D387,0)</f>
         <v/>
       </c>
+      <c r="F387" s="10">
+        <f>IF(OR($A387="",$B387=""),"",IFERROR($C387*INDEX(INSUMOS!$K$5:$K$67,MATCH($B387,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="7" t="n"/>
@@ -12424,6 +13977,10 @@
         <f>IFERROR(C388*D388,0)</f>
         <v/>
       </c>
+      <c r="F388" s="10">
+        <f>IF(OR($A388="",$B388=""),"",IFERROR($C388*INDEX(INSUMOS!$K$5:$K$67,MATCH($B388,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="7" t="n"/>
@@ -12437,6 +13994,10 @@
         <f>IFERROR(C389*D389,0)</f>
         <v/>
       </c>
+      <c r="F389" s="10">
+        <f>IF(OR($A389="",$B389=""),"",IFERROR($C389*INDEX(INSUMOS!$K$5:$K$67,MATCH($B389,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="7" t="n"/>
@@ -12450,6 +14011,10 @@
         <f>IFERROR(C390*D390,0)</f>
         <v/>
       </c>
+      <c r="F390" s="10">
+        <f>IF(OR($A390="",$B390=""),"",IFERROR($C390*INDEX(INSUMOS!$K$5:$K$67,MATCH($B390,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="7" t="n"/>
@@ -12463,6 +14028,10 @@
         <f>IFERROR(C391*D391,0)</f>
         <v/>
       </c>
+      <c r="F391" s="10">
+        <f>IF(OR($A391="",$B391=""),"",IFERROR($C391*INDEX(INSUMOS!$K$5:$K$67,MATCH($B391,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="7" t="n"/>
@@ -12476,6 +14045,10 @@
         <f>IFERROR(C392*D392,0)</f>
         <v/>
       </c>
+      <c r="F392" s="10">
+        <f>IF(OR($A392="",$B392=""),"",IFERROR($C392*INDEX(INSUMOS!$K$5:$K$67,MATCH($B392,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="7" t="n"/>
@@ -12489,6 +14062,10 @@
         <f>IFERROR(C393*D393,0)</f>
         <v/>
       </c>
+      <c r="F393" s="10">
+        <f>IF(OR($A393="",$B393=""),"",IFERROR($C393*INDEX(INSUMOS!$K$5:$K$67,MATCH($B393,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="7" t="n"/>
@@ -12502,6 +14079,10 @@
         <f>IFERROR(C394*D394,0)</f>
         <v/>
       </c>
+      <c r="F394" s="10">
+        <f>IF(OR($A394="",$B394=""),"",IFERROR($C394*INDEX(INSUMOS!$K$5:$K$67,MATCH($B394,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="7" t="n"/>
@@ -12515,6 +14096,10 @@
         <f>IFERROR(C395*D395,0)</f>
         <v/>
       </c>
+      <c r="F395" s="10">
+        <f>IF(OR($A395="",$B395=""),"",IFERROR($C395*INDEX(INSUMOS!$K$5:$K$67,MATCH($B395,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="7" t="n"/>
@@ -12528,6 +14113,10 @@
         <f>IFERROR(C396*D396,0)</f>
         <v/>
       </c>
+      <c r="F396" s="10">
+        <f>IF(OR($A396="",$B396=""),"",IFERROR($C396*INDEX(INSUMOS!$K$5:$K$67,MATCH($B396,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="7" t="n"/>
@@ -12541,6 +14130,10 @@
         <f>IFERROR(C397*D397,0)</f>
         <v/>
       </c>
+      <c r="F397" s="10">
+        <f>IF(OR($A397="",$B397=""),"",IFERROR($C397*INDEX(INSUMOS!$K$5:$K$67,MATCH($B397,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="7" t="n"/>
@@ -12554,6 +14147,10 @@
         <f>IFERROR(C398*D398,0)</f>
         <v/>
       </c>
+      <c r="F398" s="10">
+        <f>IF(OR($A398="",$B398=""),"",IFERROR($C398*INDEX(INSUMOS!$K$5:$K$67,MATCH($B398,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="7" t="n"/>
@@ -12567,6 +14164,10 @@
         <f>IFERROR(C399*D399,0)</f>
         <v/>
       </c>
+      <c r="F399" s="10">
+        <f>IF(OR($A399="",$B399=""),"",IFERROR($C399*INDEX(INSUMOS!$K$5:$K$67,MATCH($B399,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="7" t="n"/>
@@ -12580,6 +14181,10 @@
         <f>IFERROR(C400*D400,0)</f>
         <v/>
       </c>
+      <c r="F400" s="10">
+        <f>IF(OR($A400="",$B400=""),"",IFERROR($C400*INDEX(INSUMOS!$K$5:$K$67,MATCH($B400,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="7" t="n"/>
@@ -12593,6 +14198,10 @@
         <f>IFERROR(C401*D401,0)</f>
         <v/>
       </c>
+      <c r="F401" s="10">
+        <f>IF(OR($A401="",$B401=""),"",IFERROR($C401*INDEX(INSUMOS!$K$5:$K$67,MATCH($B401,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="7" t="n"/>
@@ -12606,6 +14215,10 @@
         <f>IFERROR(C402*D402,0)</f>
         <v/>
       </c>
+      <c r="F402" s="10">
+        <f>IF(OR($A402="",$B402=""),"",IFERROR($C402*INDEX(INSUMOS!$K$5:$K$67,MATCH($B402,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="7" t="n"/>
@@ -12619,6 +14232,10 @@
         <f>IFERROR(C403*D403,0)</f>
         <v/>
       </c>
+      <c r="F403" s="10">
+        <f>IF(OR($A403="",$B403=""),"",IFERROR($C403*INDEX(INSUMOS!$K$5:$K$67,MATCH($B403,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="7" t="n"/>
@@ -12632,6 +14249,10 @@
         <f>IFERROR(C404*D404,0)</f>
         <v/>
       </c>
+      <c r="F404" s="10">
+        <f>IF(OR($A404="",$B404=""),"",IFERROR($C404*INDEX(INSUMOS!$K$5:$K$67,MATCH($B404,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="7" t="n"/>
@@ -12645,6 +14266,10 @@
         <f>IFERROR(C405*D405,0)</f>
         <v/>
       </c>
+      <c r="F405" s="10">
+        <f>IF(OR($A405="",$B405=""),"",IFERROR($C405*INDEX(INSUMOS!$K$5:$K$67,MATCH($B405,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="7" t="n"/>
@@ -12658,6 +14283,10 @@
         <f>IFERROR(C406*D406,0)</f>
         <v/>
       </c>
+      <c r="F406" s="10">
+        <f>IF(OR($A406="",$B406=""),"",IFERROR($C406*INDEX(INSUMOS!$K$5:$K$67,MATCH($B406,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="7" t="n"/>
@@ -12671,6 +14300,10 @@
         <f>IFERROR(C407*D407,0)</f>
         <v/>
       </c>
+      <c r="F407" s="10">
+        <f>IF(OR($A407="",$B407=""),"",IFERROR($C407*INDEX(INSUMOS!$K$5:$K$67,MATCH($B407,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="7" t="n"/>
@@ -12684,6 +14317,10 @@
         <f>IFERROR(C408*D408,0)</f>
         <v/>
       </c>
+      <c r="F408" s="10">
+        <f>IF(OR($A408="",$B408=""),"",IFERROR($C408*INDEX(INSUMOS!$K$5:$K$67,MATCH($B408,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="7" t="n"/>
@@ -12697,6 +14334,10 @@
         <f>IFERROR(C409*D409,0)</f>
         <v/>
       </c>
+      <c r="F409" s="10">
+        <f>IF(OR($A409="",$B409=""),"",IFERROR($C409*INDEX(INSUMOS!$K$5:$K$67,MATCH($B409,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="7" t="n"/>
@@ -12710,6 +14351,10 @@
         <f>IFERROR(C410*D410,0)</f>
         <v/>
       </c>
+      <c r="F410" s="10">
+        <f>IF(OR($A410="",$B410=""),"",IFERROR($C410*INDEX(INSUMOS!$K$5:$K$67,MATCH($B410,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="7" t="n"/>
@@ -12723,6 +14368,10 @@
         <f>IFERROR(C411*D411,0)</f>
         <v/>
       </c>
+      <c r="F411" s="10">
+        <f>IF(OR($A411="",$B411=""),"",IFERROR($C411*INDEX(INSUMOS!$K$5:$K$67,MATCH($B411,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="7" t="n"/>
@@ -12736,6 +14385,10 @@
         <f>IFERROR(C412*D412,0)</f>
         <v/>
       </c>
+      <c r="F412" s="10">
+        <f>IF(OR($A412="",$B412=""),"",IFERROR($C412*INDEX(INSUMOS!$K$5:$K$67,MATCH($B412,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="7" t="n"/>
@@ -12749,6 +14402,10 @@
         <f>IFERROR(C413*D413,0)</f>
         <v/>
       </c>
+      <c r="F413" s="10">
+        <f>IF(OR($A413="",$B413=""),"",IFERROR($C413*INDEX(INSUMOS!$K$5:$K$67,MATCH($B413,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="7" t="n"/>
@@ -12762,6 +14419,10 @@
         <f>IFERROR(C414*D414,0)</f>
         <v/>
       </c>
+      <c r="F414" s="10">
+        <f>IF(OR($A414="",$B414=""),"",IFERROR($C414*INDEX(INSUMOS!$K$5:$K$67,MATCH($B414,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="7" t="n"/>
@@ -12775,6 +14436,10 @@
         <f>IFERROR(C415*D415,0)</f>
         <v/>
       </c>
+      <c r="F415" s="10">
+        <f>IF(OR($A415="",$B415=""),"",IFERROR($C415*INDEX(INSUMOS!$K$5:$K$67,MATCH($B415,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="7" t="n"/>
@@ -12788,6 +14453,10 @@
         <f>IFERROR(C416*D416,0)</f>
         <v/>
       </c>
+      <c r="F416" s="10">
+        <f>IF(OR($A416="",$B416=""),"",IFERROR($C416*INDEX(INSUMOS!$K$5:$K$67,MATCH($B416,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="7" t="n"/>
@@ -12801,6 +14470,10 @@
         <f>IFERROR(C417*D417,0)</f>
         <v/>
       </c>
+      <c r="F417" s="10">
+        <f>IF(OR($A417="",$B417=""),"",IFERROR($C417*INDEX(INSUMOS!$K$5:$K$67,MATCH($B417,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="7" t="n"/>
@@ -12814,6 +14487,10 @@
         <f>IFERROR(C418*D418,0)</f>
         <v/>
       </c>
+      <c r="F418" s="10">
+        <f>IF(OR($A418="",$B418=""),"",IFERROR($C418*INDEX(INSUMOS!$K$5:$K$67,MATCH($B418,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="7" t="n"/>
@@ -12827,6 +14504,10 @@
         <f>IFERROR(C419*D419,0)</f>
         <v/>
       </c>
+      <c r="F419" s="10">
+        <f>IF(OR($A419="",$B419=""),"",IFERROR($C419*INDEX(INSUMOS!$K$5:$K$67,MATCH($B419,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="7" t="n"/>
@@ -12840,6 +14521,10 @@
         <f>IFERROR(C420*D420,0)</f>
         <v/>
       </c>
+      <c r="F420" s="10">
+        <f>IF(OR($A420="",$B420=""),"",IFERROR($C420*INDEX(INSUMOS!$K$5:$K$67,MATCH($B420,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="7" t="n"/>
@@ -12853,6 +14538,10 @@
         <f>IFERROR(C421*D421,0)</f>
         <v/>
       </c>
+      <c r="F421" s="10">
+        <f>IF(OR($A421="",$B421=""),"",IFERROR($C421*INDEX(INSUMOS!$K$5:$K$67,MATCH($B421,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="7" t="n"/>
@@ -12866,6 +14555,10 @@
         <f>IFERROR(C422*D422,0)</f>
         <v/>
       </c>
+      <c r="F422" s="10">
+        <f>IF(OR($A422="",$B422=""),"",IFERROR($C422*INDEX(INSUMOS!$K$5:$K$67,MATCH($B422,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="7" t="n"/>
@@ -12879,6 +14572,10 @@
         <f>IFERROR(C423*D423,0)</f>
         <v/>
       </c>
+      <c r="F423" s="10">
+        <f>IF(OR($A423="",$B423=""),"",IFERROR($C423*INDEX(INSUMOS!$K$5:$K$67,MATCH($B423,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="7" t="n"/>
@@ -12892,6 +14589,10 @@
         <f>IFERROR(C424*D424,0)</f>
         <v/>
       </c>
+      <c r="F424" s="10">
+        <f>IF(OR($A424="",$B424=""),"",IFERROR($C424*INDEX(INSUMOS!$K$5:$K$67,MATCH($B424,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="7" t="n"/>
@@ -12905,6 +14606,10 @@
         <f>IFERROR(C425*D425,0)</f>
         <v/>
       </c>
+      <c r="F425" s="10">
+        <f>IF(OR($A425="",$B425=""),"",IFERROR($C425*INDEX(INSUMOS!$K$5:$K$67,MATCH($B425,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="7" t="n"/>
@@ -12918,6 +14623,10 @@
         <f>IFERROR(C426*D426,0)</f>
         <v/>
       </c>
+      <c r="F426" s="10">
+        <f>IF(OR($A426="",$B426=""),"",IFERROR($C426*INDEX(INSUMOS!$K$5:$K$67,MATCH($B426,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="7" t="n"/>
@@ -12931,6 +14640,10 @@
         <f>IFERROR(C427*D427,0)</f>
         <v/>
       </c>
+      <c r="F427" s="10">
+        <f>IF(OR($A427="",$B427=""),"",IFERROR($C427*INDEX(INSUMOS!$K$5:$K$67,MATCH($B427,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="7" t="n"/>
@@ -12944,6 +14657,10 @@
         <f>IFERROR(C428*D428,0)</f>
         <v/>
       </c>
+      <c r="F428" s="10">
+        <f>IF(OR($A428="",$B428=""),"",IFERROR($C428*INDEX(INSUMOS!$K$5:$K$67,MATCH($B428,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="7" t="n"/>
@@ -12957,6 +14674,10 @@
         <f>IFERROR(C429*D429,0)</f>
         <v/>
       </c>
+      <c r="F429" s="10">
+        <f>IF(OR($A429="",$B429=""),"",IFERROR($C429*INDEX(INSUMOS!$K$5:$K$67,MATCH($B429,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="7" t="n"/>
@@ -12970,6 +14691,10 @@
         <f>IFERROR(C430*D430,0)</f>
         <v/>
       </c>
+      <c r="F430" s="10">
+        <f>IF(OR($A430="",$B430=""),"",IFERROR($C430*INDEX(INSUMOS!$K$5:$K$67,MATCH($B430,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="7" t="n"/>
@@ -12983,6 +14708,10 @@
         <f>IFERROR(C431*D431,0)</f>
         <v/>
       </c>
+      <c r="F431" s="10">
+        <f>IF(OR($A431="",$B431=""),"",IFERROR($C431*INDEX(INSUMOS!$K$5:$K$67,MATCH($B431,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="7" t="n"/>
@@ -12996,6 +14725,10 @@
         <f>IFERROR(C432*D432,0)</f>
         <v/>
       </c>
+      <c r="F432" s="10">
+        <f>IF(OR($A432="",$B432=""),"",IFERROR($C432*INDEX(INSUMOS!$K$5:$K$67,MATCH($B432,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="7" t="n"/>
@@ -13009,6 +14742,10 @@
         <f>IFERROR(C433*D433,0)</f>
         <v/>
       </c>
+      <c r="F433" s="10">
+        <f>IF(OR($A433="",$B433=""),"",IFERROR($C433*INDEX(INSUMOS!$K$5:$K$67,MATCH($B433,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="7" t="n"/>
@@ -13022,6 +14759,10 @@
         <f>IFERROR(C434*D434,0)</f>
         <v/>
       </c>
+      <c r="F434" s="10">
+        <f>IF(OR($A434="",$B434=""),"",IFERROR($C434*INDEX(INSUMOS!$K$5:$K$67,MATCH($B434,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="7" t="n"/>
@@ -13035,6 +14776,10 @@
         <f>IFERROR(C435*D435,0)</f>
         <v/>
       </c>
+      <c r="F435" s="10">
+        <f>IF(OR($A435="",$B435=""),"",IFERROR($C435*INDEX(INSUMOS!$K$5:$K$67,MATCH($B435,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="7" t="n"/>
@@ -13048,6 +14793,10 @@
         <f>IFERROR(C436*D436,0)</f>
         <v/>
       </c>
+      <c r="F436" s="10">
+        <f>IF(OR($A436="",$B436=""),"",IFERROR($C436*INDEX(INSUMOS!$K$5:$K$67,MATCH($B436,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="7" t="n"/>
@@ -13061,6 +14810,10 @@
         <f>IFERROR(C437*D437,0)</f>
         <v/>
       </c>
+      <c r="F437" s="10">
+        <f>IF(OR($A437="",$B437=""),"",IFERROR($C437*INDEX(INSUMOS!$K$5:$K$67,MATCH($B437,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="7" t="n"/>
@@ -13074,6 +14827,10 @@
         <f>IFERROR(C438*D438,0)</f>
         <v/>
       </c>
+      <c r="F438" s="10">
+        <f>IF(OR($A438="",$B438=""),"",IFERROR($C438*INDEX(INSUMOS!$K$5:$K$67,MATCH($B438,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="7" t="n"/>
@@ -13087,6 +14844,10 @@
         <f>IFERROR(C439*D439,0)</f>
         <v/>
       </c>
+      <c r="F439" s="10">
+        <f>IF(OR($A439="",$B439=""),"",IFERROR($C439*INDEX(INSUMOS!$K$5:$K$67,MATCH($B439,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="7" t="n"/>
@@ -13100,6 +14861,10 @@
         <f>IFERROR(C440*D440,0)</f>
         <v/>
       </c>
+      <c r="F440" s="10">
+        <f>IF(OR($A440="",$B440=""),"",IFERROR($C440*INDEX(INSUMOS!$K$5:$K$67,MATCH($B440,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="7" t="n"/>
@@ -13113,6 +14878,10 @@
         <f>IFERROR(C441*D441,0)</f>
         <v/>
       </c>
+      <c r="F441" s="10">
+        <f>IF(OR($A441="",$B441=""),"",IFERROR($C441*INDEX(INSUMOS!$K$5:$K$67,MATCH($B441,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="7" t="n"/>
@@ -13126,6 +14895,10 @@
         <f>IFERROR(C442*D442,0)</f>
         <v/>
       </c>
+      <c r="F442" s="10">
+        <f>IF(OR($A442="",$B442=""),"",IFERROR($C442*INDEX(INSUMOS!$K$5:$K$67,MATCH($B442,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="7" t="n"/>
@@ -13139,6 +14912,10 @@
         <f>IFERROR(C443*D443,0)</f>
         <v/>
       </c>
+      <c r="F443" s="10">
+        <f>IF(OR($A443="",$B443=""),"",IFERROR($C443*INDEX(INSUMOS!$K$5:$K$67,MATCH($B443,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="7" t="n"/>
@@ -13152,6 +14929,10 @@
         <f>IFERROR(C444*D444,0)</f>
         <v/>
       </c>
+      <c r="F444" s="10">
+        <f>IF(OR($A444="",$B444=""),"",IFERROR($C444*INDEX(INSUMOS!$K$5:$K$67,MATCH($B444,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="7" t="n"/>
@@ -13165,6 +14946,10 @@
         <f>IFERROR(C445*D445,0)</f>
         <v/>
       </c>
+      <c r="F445" s="10">
+        <f>IF(OR($A445="",$B445=""),"",IFERROR($C445*INDEX(INSUMOS!$K$5:$K$67,MATCH($B445,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="7" t="n"/>
@@ -13178,6 +14963,10 @@
         <f>IFERROR(C446*D446,0)</f>
         <v/>
       </c>
+      <c r="F446" s="10">
+        <f>IF(OR($A446="",$B446=""),"",IFERROR($C446*INDEX(INSUMOS!$K$5:$K$67,MATCH($B446,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="7" t="n"/>
@@ -13191,6 +14980,10 @@
         <f>IFERROR(C447*D447,0)</f>
         <v/>
       </c>
+      <c r="F447" s="10">
+        <f>IF(OR($A447="",$B447=""),"",IFERROR($C447*INDEX(INSUMOS!$K$5:$K$67,MATCH($B447,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="7" t="n"/>
@@ -13204,6 +14997,10 @@
         <f>IFERROR(C448*D448,0)</f>
         <v/>
       </c>
+      <c r="F448" s="10">
+        <f>IF(OR($A448="",$B448=""),"",IFERROR($C448*INDEX(INSUMOS!$K$5:$K$67,MATCH($B448,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="7" t="n"/>
@@ -13217,6 +15014,10 @@
         <f>IFERROR(C449*D449,0)</f>
         <v/>
       </c>
+      <c r="F449" s="10">
+        <f>IF(OR($A449="",$B449=""),"",IFERROR($C449*INDEX(INSUMOS!$K$5:$K$67,MATCH($B449,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="7" t="n"/>
@@ -13230,6 +15031,10 @@
         <f>IFERROR(C450*D450,0)</f>
         <v/>
       </c>
+      <c r="F450" s="10">
+        <f>IF(OR($A450="",$B450=""),"",IFERROR($C450*INDEX(INSUMOS!$K$5:$K$67,MATCH($B450,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="7" t="n"/>
@@ -13243,6 +15048,10 @@
         <f>IFERROR(C451*D451,0)</f>
         <v/>
       </c>
+      <c r="F451" s="10">
+        <f>IF(OR($A451="",$B451=""),"",IFERROR($C451*INDEX(INSUMOS!$K$5:$K$67,MATCH($B451,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="7" t="n"/>
@@ -13256,6 +15065,10 @@
         <f>IFERROR(C452*D452,0)</f>
         <v/>
       </c>
+      <c r="F452" s="10">
+        <f>IF(OR($A452="",$B452=""),"",IFERROR($C452*INDEX(INSUMOS!$K$5:$K$67,MATCH($B452,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="7" t="n"/>
@@ -13269,6 +15082,10 @@
         <f>IFERROR(C453*D453,0)</f>
         <v/>
       </c>
+      <c r="F453" s="10">
+        <f>IF(OR($A453="",$B453=""),"",IFERROR($C453*INDEX(INSUMOS!$K$5:$K$67,MATCH($B453,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="7" t="n"/>
@@ -13282,6 +15099,10 @@
         <f>IFERROR(C454*D454,0)</f>
         <v/>
       </c>
+      <c r="F454" s="10">
+        <f>IF(OR($A454="",$B454=""),"",IFERROR($C454*INDEX(INSUMOS!$K$5:$K$67,MATCH($B454,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="7" t="n"/>
@@ -13295,6 +15116,10 @@
         <f>IFERROR(C455*D455,0)</f>
         <v/>
       </c>
+      <c r="F455" s="10">
+        <f>IF(OR($A455="",$B455=""),"",IFERROR($C455*INDEX(INSUMOS!$K$5:$K$67,MATCH($B455,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="7" t="n"/>
@@ -13308,6 +15133,10 @@
         <f>IFERROR(C456*D456,0)</f>
         <v/>
       </c>
+      <c r="F456" s="10">
+        <f>IF(OR($A456="",$B456=""),"",IFERROR($C456*INDEX(INSUMOS!$K$5:$K$67,MATCH($B456,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="7" t="n"/>
@@ -13321,6 +15150,10 @@
         <f>IFERROR(C457*D457,0)</f>
         <v/>
       </c>
+      <c r="F457" s="10">
+        <f>IF(OR($A457="",$B457=""),"",IFERROR($C457*INDEX(INSUMOS!$K$5:$K$67,MATCH($B457,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="7" t="n"/>
@@ -13334,6 +15167,10 @@
         <f>IFERROR(C458*D458,0)</f>
         <v/>
       </c>
+      <c r="F458" s="10">
+        <f>IF(OR($A458="",$B458=""),"",IFERROR($C458*INDEX(INSUMOS!$K$5:$K$67,MATCH($B458,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="7" t="n"/>
@@ -13347,6 +15184,10 @@
         <f>IFERROR(C459*D459,0)</f>
         <v/>
       </c>
+      <c r="F459" s="10">
+        <f>IF(OR($A459="",$B459=""),"",IFERROR($C459*INDEX(INSUMOS!$K$5:$K$67,MATCH($B459,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="7" t="n"/>
@@ -13360,6 +15201,10 @@
         <f>IFERROR(C460*D460,0)</f>
         <v/>
       </c>
+      <c r="F460" s="10">
+        <f>IF(OR($A460="",$B460=""),"",IFERROR($C460*INDEX(INSUMOS!$K$5:$K$67,MATCH($B460,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="7" t="n"/>
@@ -13373,6 +15218,10 @@
         <f>IFERROR(C461*D461,0)</f>
         <v/>
       </c>
+      <c r="F461" s="10">
+        <f>IF(OR($A461="",$B461=""),"",IFERROR($C461*INDEX(INSUMOS!$K$5:$K$67,MATCH($B461,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="7" t="n"/>
@@ -13386,6 +15235,10 @@
         <f>IFERROR(C462*D462,0)</f>
         <v/>
       </c>
+      <c r="F462" s="10">
+        <f>IF(OR($A462="",$B462=""),"",IFERROR($C462*INDEX(INSUMOS!$K$5:$K$67,MATCH($B462,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="7" t="n"/>
@@ -13399,6 +15252,10 @@
         <f>IFERROR(C463*D463,0)</f>
         <v/>
       </c>
+      <c r="F463" s="10">
+        <f>IF(OR($A463="",$B463=""),"",IFERROR($C463*INDEX(INSUMOS!$K$5:$K$67,MATCH($B463,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="464">
       <c r="A464" s="7" t="n"/>
@@ -13412,6 +15269,10 @@
         <f>IFERROR(C464*D464,0)</f>
         <v/>
       </c>
+      <c r="F464" s="10">
+        <f>IF(OR($A464="",$B464=""),"",IFERROR($C464*INDEX(INSUMOS!$K$5:$K$67,MATCH($B464,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="7" t="n"/>
@@ -13425,6 +15286,10 @@
         <f>IFERROR(C465*D465,0)</f>
         <v/>
       </c>
+      <c r="F465" s="10">
+        <f>IF(OR($A465="",$B465=""),"",IFERROR($C465*INDEX(INSUMOS!$K$5:$K$67,MATCH($B465,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="7" t="n"/>
@@ -13438,6 +15303,10 @@
         <f>IFERROR(C466*D466,0)</f>
         <v/>
       </c>
+      <c r="F466" s="10">
+        <f>IF(OR($A466="",$B466=""),"",IFERROR($C466*INDEX(INSUMOS!$K$5:$K$67,MATCH($B466,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="7" t="n"/>
@@ -13451,6 +15320,10 @@
         <f>IFERROR(C467*D467,0)</f>
         <v/>
       </c>
+      <c r="F467" s="10">
+        <f>IF(OR($A467="",$B467=""),"",IFERROR($C467*INDEX(INSUMOS!$K$5:$K$67,MATCH($B467,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="7" t="n"/>
@@ -13464,6 +15337,10 @@
         <f>IFERROR(C468*D468,0)</f>
         <v/>
       </c>
+      <c r="F468" s="10">
+        <f>IF(OR($A468="",$B468=""),"",IFERROR($C468*INDEX(INSUMOS!$K$5:$K$67,MATCH($B468,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="7" t="n"/>
@@ -13477,6 +15354,10 @@
         <f>IFERROR(C469*D469,0)</f>
         <v/>
       </c>
+      <c r="F469" s="10">
+        <f>IF(OR($A469="",$B469=""),"",IFERROR($C469*INDEX(INSUMOS!$K$5:$K$67,MATCH($B469,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="7" t="n"/>
@@ -13490,6 +15371,10 @@
         <f>IFERROR(C470*D470,0)</f>
         <v/>
       </c>
+      <c r="F470" s="10">
+        <f>IF(OR($A470="",$B470=""),"",IFERROR($C470*INDEX(INSUMOS!$K$5:$K$67,MATCH($B470,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="7" t="n"/>
@@ -13503,6 +15388,10 @@
         <f>IFERROR(C471*D471,0)</f>
         <v/>
       </c>
+      <c r="F471" s="10">
+        <f>IF(OR($A471="",$B471=""),"",IFERROR($C471*INDEX(INSUMOS!$K$5:$K$67,MATCH($B471,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="7" t="n"/>
@@ -13516,6 +15405,10 @@
         <f>IFERROR(C472*D472,0)</f>
         <v/>
       </c>
+      <c r="F472" s="10">
+        <f>IF(OR($A472="",$B472=""),"",IFERROR($C472*INDEX(INSUMOS!$K$5:$K$67,MATCH($B472,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="7" t="n"/>
@@ -13529,6 +15422,10 @@
         <f>IFERROR(C473*D473,0)</f>
         <v/>
       </c>
+      <c r="F473" s="10">
+        <f>IF(OR($A473="",$B473=""),"",IFERROR($C473*INDEX(INSUMOS!$K$5:$K$67,MATCH($B473,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="7" t="n"/>
@@ -13542,6 +15439,10 @@
         <f>IFERROR(C474*D474,0)</f>
         <v/>
       </c>
+      <c r="F474" s="10">
+        <f>IF(OR($A474="",$B474=""),"",IFERROR($C474*INDEX(INSUMOS!$K$5:$K$67,MATCH($B474,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="475">
       <c r="A475" s="7" t="n"/>
@@ -13555,6 +15456,10 @@
         <f>IFERROR(C475*D475,0)</f>
         <v/>
       </c>
+      <c r="F475" s="10">
+        <f>IF(OR($A475="",$B475=""),"",IFERROR($C475*INDEX(INSUMOS!$K$5:$K$67,MATCH($B475,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="476">
       <c r="A476" s="7" t="n"/>
@@ -13568,6 +15473,10 @@
         <f>IFERROR(C476*D476,0)</f>
         <v/>
       </c>
+      <c r="F476" s="10">
+        <f>IF(OR($A476="",$B476=""),"",IFERROR($C476*INDEX(INSUMOS!$K$5:$K$67,MATCH($B476,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="7" t="n"/>
@@ -13581,6 +15490,10 @@
         <f>IFERROR(C477*D477,0)</f>
         <v/>
       </c>
+      <c r="F477" s="10">
+        <f>IF(OR($A477="",$B477=""),"",IFERROR($C477*INDEX(INSUMOS!$K$5:$K$67,MATCH($B477,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="7" t="n"/>
@@ -13594,6 +15507,10 @@
         <f>IFERROR(C478*D478,0)</f>
         <v/>
       </c>
+      <c r="F478" s="10">
+        <f>IF(OR($A478="",$B478=""),"",IFERROR($C478*INDEX(INSUMOS!$K$5:$K$67,MATCH($B478,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="7" t="n"/>
@@ -13607,6 +15524,10 @@
         <f>IFERROR(C479*D479,0)</f>
         <v/>
       </c>
+      <c r="F479" s="10">
+        <f>IF(OR($A479="",$B479=""),"",IFERROR($C479*INDEX(INSUMOS!$K$5:$K$67,MATCH($B479,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="7" t="n"/>
@@ -13620,6 +15541,10 @@
         <f>IFERROR(C480*D480,0)</f>
         <v/>
       </c>
+      <c r="F480" s="10">
+        <f>IF(OR($A480="",$B480=""),"",IFERROR($C480*INDEX(INSUMOS!$K$5:$K$67,MATCH($B480,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="7" t="n"/>
@@ -13633,6 +15558,10 @@
         <f>IFERROR(C481*D481,0)</f>
         <v/>
       </c>
+      <c r="F481" s="10">
+        <f>IF(OR($A481="",$B481=""),"",IFERROR($C481*INDEX(INSUMOS!$K$5:$K$67,MATCH($B481,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="7" t="n"/>
@@ -13646,6 +15575,10 @@
         <f>IFERROR(C482*D482,0)</f>
         <v/>
       </c>
+      <c r="F482" s="10">
+        <f>IF(OR($A482="",$B482=""),"",IFERROR($C482*INDEX(INSUMOS!$K$5:$K$67,MATCH($B482,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="483">
       <c r="A483" s="7" t="n"/>
@@ -13659,6 +15592,10 @@
         <f>IFERROR(C483*D483,0)</f>
         <v/>
       </c>
+      <c r="F483" s="10">
+        <f>IF(OR($A483="",$B483=""),"",IFERROR($C483*INDEX(INSUMOS!$K$5:$K$67,MATCH($B483,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="7" t="n"/>
@@ -13672,6 +15609,10 @@
         <f>IFERROR(C484*D484,0)</f>
         <v/>
       </c>
+      <c r="F484" s="10">
+        <f>IF(OR($A484="",$B484=""),"",IFERROR($C484*INDEX(INSUMOS!$K$5:$K$67,MATCH($B484,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="7" t="n"/>
@@ -13685,6 +15626,10 @@
         <f>IFERROR(C485*D485,0)</f>
         <v/>
       </c>
+      <c r="F485" s="10">
+        <f>IF(OR($A485="",$B485=""),"",IFERROR($C485*INDEX(INSUMOS!$K$5:$K$67,MATCH($B485,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="7" t="n"/>
@@ -13698,6 +15643,10 @@
         <f>IFERROR(C486*D486,0)</f>
         <v/>
       </c>
+      <c r="F486" s="10">
+        <f>IF(OR($A486="",$B486=""),"",IFERROR($C486*INDEX(INSUMOS!$K$5:$K$67,MATCH($B486,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="487">
       <c r="A487" s="7" t="n"/>
@@ -13711,6 +15660,10 @@
         <f>IFERROR(C487*D487,0)</f>
         <v/>
       </c>
+      <c r="F487" s="10">
+        <f>IF(OR($A487="",$B487=""),"",IFERROR($C487*INDEX(INSUMOS!$K$5:$K$67,MATCH($B487,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="488">
       <c r="A488" s="7" t="n"/>
@@ -13724,6 +15677,10 @@
         <f>IFERROR(C488*D488,0)</f>
         <v/>
       </c>
+      <c r="F488" s="10">
+        <f>IF(OR($A488="",$B488=""),"",IFERROR($C488*INDEX(INSUMOS!$K$5:$K$67,MATCH($B488,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="489">
       <c r="A489" s="7" t="n"/>
@@ -13737,6 +15694,10 @@
         <f>IFERROR(C489*D489,0)</f>
         <v/>
       </c>
+      <c r="F489" s="10">
+        <f>IF(OR($A489="",$B489=""),"",IFERROR($C489*INDEX(INSUMOS!$K$5:$K$67,MATCH($B489,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="7" t="n"/>
@@ -13750,6 +15711,10 @@
         <f>IFERROR(C490*D490,0)</f>
         <v/>
       </c>
+      <c r="F490" s="10">
+        <f>IF(OR($A490="",$B490=""),"",IFERROR($C490*INDEX(INSUMOS!$K$5:$K$67,MATCH($B490,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="7" t="n"/>
@@ -13763,6 +15728,10 @@
         <f>IFERROR(C491*D491,0)</f>
         <v/>
       </c>
+      <c r="F491" s="10">
+        <f>IF(OR($A491="",$B491=""),"",IFERROR($C491*INDEX(INSUMOS!$K$5:$K$67,MATCH($B491,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="7" t="n"/>
@@ -13776,6 +15745,10 @@
         <f>IFERROR(C492*D492,0)</f>
         <v/>
       </c>
+      <c r="F492" s="10">
+        <f>IF(OR($A492="",$B492=""),"",IFERROR($C492*INDEX(INSUMOS!$K$5:$K$67,MATCH($B492,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="7" t="n"/>
@@ -13789,6 +15762,10 @@
         <f>IFERROR(C493*D493,0)</f>
         <v/>
       </c>
+      <c r="F493" s="10">
+        <f>IF(OR($A493="",$B493=""),"",IFERROR($C493*INDEX(INSUMOS!$K$5:$K$67,MATCH($B493,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="7" t="n"/>
@@ -13802,6 +15779,10 @@
         <f>IFERROR(C494*D494,0)</f>
         <v/>
       </c>
+      <c r="F494" s="10">
+        <f>IF(OR($A494="",$B494=""),"",IFERROR($C494*INDEX(INSUMOS!$K$5:$K$67,MATCH($B494,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="7" t="n"/>
@@ -13815,6 +15796,10 @@
         <f>IFERROR(C495*D495,0)</f>
         <v/>
       </c>
+      <c r="F495" s="10">
+        <f>IF(OR($A495="",$B495=""),"",IFERROR($C495*INDEX(INSUMOS!$K$5:$K$67,MATCH($B495,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="496">
       <c r="A496" s="7" t="n"/>
@@ -13828,6 +15813,10 @@
         <f>IFERROR(C496*D496,0)</f>
         <v/>
       </c>
+      <c r="F496" s="10">
+        <f>IF(OR($A496="",$B496=""),"",IFERROR($C496*INDEX(INSUMOS!$K$5:$K$67,MATCH($B496,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="497">
       <c r="A497" s="7" t="n"/>
@@ -13841,6 +15830,10 @@
         <f>IFERROR(C497*D497,0)</f>
         <v/>
       </c>
+      <c r="F497" s="10">
+        <f>IF(OR($A497="",$B497=""),"",IFERROR($C497*INDEX(INSUMOS!$K$5:$K$67,MATCH($B497,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="7" t="n"/>
@@ -13854,6 +15847,10 @@
         <f>IFERROR(C498*D498,0)</f>
         <v/>
       </c>
+      <c r="F498" s="10">
+        <f>IF(OR($A498="",$B498=""),"",IFERROR($C498*INDEX(INSUMOS!$K$5:$K$67,MATCH($B498,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="499">
       <c r="A499" s="7" t="n"/>
@@ -13867,6 +15864,10 @@
         <f>IFERROR(C499*D499,0)</f>
         <v/>
       </c>
+      <c r="F499" s="10">
+        <f>IF(OR($A499="",$B499=""),"",IFERROR($C499*INDEX(INSUMOS!$K$5:$K$67,MATCH($B499,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="500">
       <c r="A500" s="7" t="n"/>
@@ -13880,6 +15881,10 @@
         <f>IFERROR(C500*D500,0)</f>
         <v/>
       </c>
+      <c r="F500" s="10">
+        <f>IF(OR($A500="",$B500=""),"",IFERROR($C500*INDEX(INSUMOS!$K$5:$K$67,MATCH($B500,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="501">
       <c r="A501" s="7" t="n"/>
@@ -13893,6 +15898,10 @@
         <f>IFERROR(C501*D501,0)</f>
         <v/>
       </c>
+      <c r="F501" s="10">
+        <f>IF(OR($A501="",$B501=""),"",IFERROR($C501*INDEX(INSUMOS!$K$5:$K$67,MATCH($B501,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="502">
       <c r="A502" s="7" t="n"/>
@@ -13906,6 +15915,10 @@
         <f>IFERROR(C502*D502,0)</f>
         <v/>
       </c>
+      <c r="F502" s="10">
+        <f>IF(OR($A502="",$B502=""),"",IFERROR($C502*INDEX(INSUMOS!$K$5:$K$67,MATCH($B502,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="503">
       <c r="A503" s="7" t="n"/>
@@ -13919,6 +15932,10 @@
         <f>IFERROR(C503*D503,0)</f>
         <v/>
       </c>
+      <c r="F503" s="10">
+        <f>IF(OR($A503="",$B503=""),"",IFERROR($C503*INDEX(INSUMOS!$K$5:$K$67,MATCH($B503,INSUMOS!$B$5:$B$67,0)),0))</f>
+        <v/>
+      </c>
     </row>
     <row r="504">
       <c r="A504" s="7" t="n"/>
@@ -13930,6 +15947,10 @@
       </c>
       <c r="E504" s="8">
         <f>IFERROR(C504*D504,0)</f>
+        <v/>
+      </c>
+      <c r="F504" s="10">
+        <f>IF(OR($A504="",$B504=""),"",IFERROR($C504*INDEX(INSUMOS!$K$5:$K$67,MATCH($B504,INSUMOS!$B$5:$B$67,0)),0))</f>
         <v/>
       </c>
     </row>
@@ -28494,4 +30515,3420 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J104"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>🏷️ PRECIOS - costo, precio de venta, IVA y ganancia por producto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Los productos y su costo de insumos se traen solos (si sube el precio de un insumo, el costo sube solo). Vos llenás lo amarillo: otros costos y el precio de venta (con IVA incluido).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>IVA aplicado (editable) →</t>
+        </is>
+      </c>
+      <c r="B3" s="21" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Costo
+insumos</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Otros
+costos</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Costo
+total</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Precio de
+venta (c/IVA)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>IVA
+incluido</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Precio neto
+(sin IVA)</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Ganancia
+por unidad</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Margen
+%</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8">
+        <f>IF(PRODUCTOS!B5="","",PRODUCTOS!B5)</f>
+        <v/>
+      </c>
+      <c r="B5" s="10">
+        <f>IF($A5="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A5))</f>
+        <v/>
+      </c>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="10">
+        <f>IF($A5="","",B5+IF(C5="",0,C5))</f>
+        <v/>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F5" s="10">
+        <f>IF(OR($A5="",$E5=""),"",ROUND($E5-$E5/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G5" s="10">
+        <f>IF(OR($A5="",$E5=""),"",ROUND($E5/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H5" s="10">
+        <f>IF(OR($A5="",$E5=""),"",G5-D5)</f>
+        <v/>
+      </c>
+      <c r="I5" s="22">
+        <f>IF(OR($A5="",$E5="",$E5=0),"",H5/G5)</f>
+        <v/>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>EJEMPLO: borrá este precio y poné el tuyo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8">
+        <f>IF(PRODUCTOS!B6="","",PRODUCTOS!B6)</f>
+        <v/>
+      </c>
+      <c r="B6" s="10">
+        <f>IF($A6="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A6))</f>
+        <v/>
+      </c>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="10">
+        <f>IF($A6="","",B6+IF(C6="",0,C6))</f>
+        <v/>
+      </c>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="10">
+        <f>IF(OR($A6="",$E6=""),"",ROUND($E6-$E6/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G6" s="10">
+        <f>IF(OR($A6="",$E6=""),"",ROUND($E6/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H6" s="10">
+        <f>IF(OR($A6="",$E6=""),"",G6-D6)</f>
+        <v/>
+      </c>
+      <c r="I6" s="22">
+        <f>IF(OR($A6="",$E6="",$E6=0),"",H6/G6)</f>
+        <v/>
+      </c>
+      <c r="J6" s="7" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8">
+        <f>IF(PRODUCTOS!B7="","",PRODUCTOS!B7)</f>
+        <v/>
+      </c>
+      <c r="B7" s="10">
+        <f>IF($A7="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A7))</f>
+        <v/>
+      </c>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="10">
+        <f>IF($A7="","",B7+IF(C7="",0,C7))</f>
+        <v/>
+      </c>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="10">
+        <f>IF(OR($A7="",$E7=""),"",ROUND($E7-$E7/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G7" s="10">
+        <f>IF(OR($A7="",$E7=""),"",ROUND($E7/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H7" s="10">
+        <f>IF(OR($A7="",$E7=""),"",G7-D7)</f>
+        <v/>
+      </c>
+      <c r="I7" s="22">
+        <f>IF(OR($A7="",$E7="",$E7=0),"",H7/G7)</f>
+        <v/>
+      </c>
+      <c r="J7" s="7" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8">
+        <f>IF(PRODUCTOS!B8="","",PRODUCTOS!B8)</f>
+        <v/>
+      </c>
+      <c r="B8" s="10">
+        <f>IF($A8="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A8))</f>
+        <v/>
+      </c>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="10">
+        <f>IF($A8="","",B8+IF(C8="",0,C8))</f>
+        <v/>
+      </c>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="10">
+        <f>IF(OR($A8="",$E8=""),"",ROUND($E8-$E8/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G8" s="10">
+        <f>IF(OR($A8="",$E8=""),"",ROUND($E8/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H8" s="10">
+        <f>IF(OR($A8="",$E8=""),"",G8-D8)</f>
+        <v/>
+      </c>
+      <c r="I8" s="22">
+        <f>IF(OR($A8="",$E8="",$E8=0),"",H8/G8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8">
+        <f>IF(PRODUCTOS!B9="","",PRODUCTOS!B9)</f>
+        <v/>
+      </c>
+      <c r="B9" s="10">
+        <f>IF($A9="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A9))</f>
+        <v/>
+      </c>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="10">
+        <f>IF($A9="","",B9+IF(C9="",0,C9))</f>
+        <v/>
+      </c>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="10">
+        <f>IF(OR($A9="",$E9=""),"",ROUND($E9-$E9/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G9" s="10">
+        <f>IF(OR($A9="",$E9=""),"",ROUND($E9/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H9" s="10">
+        <f>IF(OR($A9="",$E9=""),"",G9-D9)</f>
+        <v/>
+      </c>
+      <c r="I9" s="22">
+        <f>IF(OR($A9="",$E9="",$E9=0),"",H9/G9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8">
+        <f>IF(PRODUCTOS!B10="","",PRODUCTOS!B10)</f>
+        <v/>
+      </c>
+      <c r="B10" s="10">
+        <f>IF($A10="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A10))</f>
+        <v/>
+      </c>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="10">
+        <f>IF($A10="","",B10+IF(C10="",0,C10))</f>
+        <v/>
+      </c>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="10">
+        <f>IF(OR($A10="",$E10=""),"",ROUND($E10-$E10/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G10" s="10">
+        <f>IF(OR($A10="",$E10=""),"",ROUND($E10/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H10" s="10">
+        <f>IF(OR($A10="",$E10=""),"",G10-D10)</f>
+        <v/>
+      </c>
+      <c r="I10" s="22">
+        <f>IF(OR($A10="",$E10="",$E10=0),"",H10/G10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8">
+        <f>IF(PRODUCTOS!B11="","",PRODUCTOS!B11)</f>
+        <v/>
+      </c>
+      <c r="B11" s="10">
+        <f>IF($A11="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A11))</f>
+        <v/>
+      </c>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="10">
+        <f>IF($A11="","",B11+IF(C11="",0,C11))</f>
+        <v/>
+      </c>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="10">
+        <f>IF(OR($A11="",$E11=""),"",ROUND($E11-$E11/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G11" s="10">
+        <f>IF(OR($A11="",$E11=""),"",ROUND($E11/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H11" s="10">
+        <f>IF(OR($A11="",$E11=""),"",G11-D11)</f>
+        <v/>
+      </c>
+      <c r="I11" s="22">
+        <f>IF(OR($A11="",$E11="",$E11=0),"",H11/G11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8">
+        <f>IF(PRODUCTOS!B12="","",PRODUCTOS!B12)</f>
+        <v/>
+      </c>
+      <c r="B12" s="10">
+        <f>IF($A12="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A12))</f>
+        <v/>
+      </c>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="10">
+        <f>IF($A12="","",B12+IF(C12="",0,C12))</f>
+        <v/>
+      </c>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="10">
+        <f>IF(OR($A12="",$E12=""),"",ROUND($E12-$E12/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G12" s="10">
+        <f>IF(OR($A12="",$E12=""),"",ROUND($E12/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H12" s="10">
+        <f>IF(OR($A12="",$E12=""),"",G12-D12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="22">
+        <f>IF(OR($A12="",$E12="",$E12=0),"",H12/G12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8">
+        <f>IF(PRODUCTOS!B13="","",PRODUCTOS!B13)</f>
+        <v/>
+      </c>
+      <c r="B13" s="10">
+        <f>IF($A13="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A13))</f>
+        <v/>
+      </c>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="10">
+        <f>IF($A13="","",B13+IF(C13="",0,C13))</f>
+        <v/>
+      </c>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="10">
+        <f>IF(OR($A13="",$E13=""),"",ROUND($E13-$E13/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G13" s="10">
+        <f>IF(OR($A13="",$E13=""),"",ROUND($E13/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H13" s="10">
+        <f>IF(OR($A13="",$E13=""),"",G13-D13)</f>
+        <v/>
+      </c>
+      <c r="I13" s="22">
+        <f>IF(OR($A13="",$E13="",$E13=0),"",H13/G13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8">
+        <f>IF(PRODUCTOS!B14="","",PRODUCTOS!B14)</f>
+        <v/>
+      </c>
+      <c r="B14" s="10">
+        <f>IF($A14="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A14))</f>
+        <v/>
+      </c>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="10">
+        <f>IF($A14="","",B14+IF(C14="",0,C14))</f>
+        <v/>
+      </c>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="10">
+        <f>IF(OR($A14="",$E14=""),"",ROUND($E14-$E14/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G14" s="10">
+        <f>IF(OR($A14="",$E14=""),"",ROUND($E14/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H14" s="10">
+        <f>IF(OR($A14="",$E14=""),"",G14-D14)</f>
+        <v/>
+      </c>
+      <c r="I14" s="22">
+        <f>IF(OR($A14="",$E14="",$E14=0),"",H14/G14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8">
+        <f>IF(PRODUCTOS!B15="","",PRODUCTOS!B15)</f>
+        <v/>
+      </c>
+      <c r="B15" s="10">
+        <f>IF($A15="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A15))</f>
+        <v/>
+      </c>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="10">
+        <f>IF($A15="","",B15+IF(C15="",0,C15))</f>
+        <v/>
+      </c>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="10">
+        <f>IF(OR($A15="",$E15=""),"",ROUND($E15-$E15/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G15" s="10">
+        <f>IF(OR($A15="",$E15=""),"",ROUND($E15/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H15" s="10">
+        <f>IF(OR($A15="",$E15=""),"",G15-D15)</f>
+        <v/>
+      </c>
+      <c r="I15" s="22">
+        <f>IF(OR($A15="",$E15="",$E15=0),"",H15/G15)</f>
+        <v/>
+      </c>
+      <c r="J15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8">
+        <f>IF(PRODUCTOS!B16="","",PRODUCTOS!B16)</f>
+        <v/>
+      </c>
+      <c r="B16" s="10">
+        <f>IF($A16="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A16))</f>
+        <v/>
+      </c>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="10">
+        <f>IF($A16="","",B16+IF(C16="",0,C16))</f>
+        <v/>
+      </c>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="10">
+        <f>IF(OR($A16="",$E16=""),"",ROUND($E16-$E16/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G16" s="10">
+        <f>IF(OR($A16="",$E16=""),"",ROUND($E16/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H16" s="10">
+        <f>IF(OR($A16="",$E16=""),"",G16-D16)</f>
+        <v/>
+      </c>
+      <c r="I16" s="22">
+        <f>IF(OR($A16="",$E16="",$E16=0),"",H16/G16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8">
+        <f>IF(PRODUCTOS!B17="","",PRODUCTOS!B17)</f>
+        <v/>
+      </c>
+      <c r="B17" s="10">
+        <f>IF($A17="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A17))</f>
+        <v/>
+      </c>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="10">
+        <f>IF($A17="","",B17+IF(C17="",0,C17))</f>
+        <v/>
+      </c>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="10">
+        <f>IF(OR($A17="",$E17=""),"",ROUND($E17-$E17/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G17" s="10">
+        <f>IF(OR($A17="",$E17=""),"",ROUND($E17/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H17" s="10">
+        <f>IF(OR($A17="",$E17=""),"",G17-D17)</f>
+        <v/>
+      </c>
+      <c r="I17" s="22">
+        <f>IF(OR($A17="",$E17="",$E17=0),"",H17/G17)</f>
+        <v/>
+      </c>
+      <c r="J17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8">
+        <f>IF(PRODUCTOS!B18="","",PRODUCTOS!B18)</f>
+        <v/>
+      </c>
+      <c r="B18" s="10">
+        <f>IF($A18="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A18))</f>
+        <v/>
+      </c>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="10">
+        <f>IF($A18="","",B18+IF(C18="",0,C18))</f>
+        <v/>
+      </c>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="10">
+        <f>IF(OR($A18="",$E18=""),"",ROUND($E18-$E18/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G18" s="10">
+        <f>IF(OR($A18="",$E18=""),"",ROUND($E18/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H18" s="10">
+        <f>IF(OR($A18="",$E18=""),"",G18-D18)</f>
+        <v/>
+      </c>
+      <c r="I18" s="22">
+        <f>IF(OR($A18="",$E18="",$E18=0),"",H18/G18)</f>
+        <v/>
+      </c>
+      <c r="J18" s="7" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8">
+        <f>IF(PRODUCTOS!B19="","",PRODUCTOS!B19)</f>
+        <v/>
+      </c>
+      <c r="B19" s="10">
+        <f>IF($A19="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A19))</f>
+        <v/>
+      </c>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="10">
+        <f>IF($A19="","",B19+IF(C19="",0,C19))</f>
+        <v/>
+      </c>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="10">
+        <f>IF(OR($A19="",$E19=""),"",ROUND($E19-$E19/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G19" s="10">
+        <f>IF(OR($A19="",$E19=""),"",ROUND($E19/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H19" s="10">
+        <f>IF(OR($A19="",$E19=""),"",G19-D19)</f>
+        <v/>
+      </c>
+      <c r="I19" s="22">
+        <f>IF(OR($A19="",$E19="",$E19=0),"",H19/G19)</f>
+        <v/>
+      </c>
+      <c r="J19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8">
+        <f>IF(PRODUCTOS!B20="","",PRODUCTOS!B20)</f>
+        <v/>
+      </c>
+      <c r="B20" s="10">
+        <f>IF($A20="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A20))</f>
+        <v/>
+      </c>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="10">
+        <f>IF($A20="","",B20+IF(C20="",0,C20))</f>
+        <v/>
+      </c>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="10">
+        <f>IF(OR($A20="",$E20=""),"",ROUND($E20-$E20/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G20" s="10">
+        <f>IF(OR($A20="",$E20=""),"",ROUND($E20/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H20" s="10">
+        <f>IF(OR($A20="",$E20=""),"",G20-D20)</f>
+        <v/>
+      </c>
+      <c r="I20" s="22">
+        <f>IF(OR($A20="",$E20="",$E20=0),"",H20/G20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8">
+        <f>IF(PRODUCTOS!B21="","",PRODUCTOS!B21)</f>
+        <v/>
+      </c>
+      <c r="B21" s="10">
+        <f>IF($A21="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A21))</f>
+        <v/>
+      </c>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="10">
+        <f>IF($A21="","",B21+IF(C21="",0,C21))</f>
+        <v/>
+      </c>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="10">
+        <f>IF(OR($A21="",$E21=""),"",ROUND($E21-$E21/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G21" s="10">
+        <f>IF(OR($A21="",$E21=""),"",ROUND($E21/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H21" s="10">
+        <f>IF(OR($A21="",$E21=""),"",G21-D21)</f>
+        <v/>
+      </c>
+      <c r="I21" s="22">
+        <f>IF(OR($A21="",$E21="",$E21=0),"",H21/G21)</f>
+        <v/>
+      </c>
+      <c r="J21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8">
+        <f>IF(PRODUCTOS!B22="","",PRODUCTOS!B22)</f>
+        <v/>
+      </c>
+      <c r="B22" s="10">
+        <f>IF($A22="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A22))</f>
+        <v/>
+      </c>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="10">
+        <f>IF($A22="","",B22+IF(C22="",0,C22))</f>
+        <v/>
+      </c>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="10">
+        <f>IF(OR($A22="",$E22=""),"",ROUND($E22-$E22/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G22" s="10">
+        <f>IF(OR($A22="",$E22=""),"",ROUND($E22/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H22" s="10">
+        <f>IF(OR($A22="",$E22=""),"",G22-D22)</f>
+        <v/>
+      </c>
+      <c r="I22" s="22">
+        <f>IF(OR($A22="",$E22="",$E22=0),"",H22/G22)</f>
+        <v/>
+      </c>
+      <c r="J22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8">
+        <f>IF(PRODUCTOS!B23="","",PRODUCTOS!B23)</f>
+        <v/>
+      </c>
+      <c r="B23" s="10">
+        <f>IF($A23="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A23))</f>
+        <v/>
+      </c>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="10">
+        <f>IF($A23="","",B23+IF(C23="",0,C23))</f>
+        <v/>
+      </c>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="10">
+        <f>IF(OR($A23="",$E23=""),"",ROUND($E23-$E23/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G23" s="10">
+        <f>IF(OR($A23="",$E23=""),"",ROUND($E23/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H23" s="10">
+        <f>IF(OR($A23="",$E23=""),"",G23-D23)</f>
+        <v/>
+      </c>
+      <c r="I23" s="22">
+        <f>IF(OR($A23="",$E23="",$E23=0),"",H23/G23)</f>
+        <v/>
+      </c>
+      <c r="J23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8">
+        <f>IF(PRODUCTOS!B24="","",PRODUCTOS!B24)</f>
+        <v/>
+      </c>
+      <c r="B24" s="10">
+        <f>IF($A24="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A24))</f>
+        <v/>
+      </c>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="10">
+        <f>IF($A24="","",B24+IF(C24="",0,C24))</f>
+        <v/>
+      </c>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="10">
+        <f>IF(OR($A24="",$E24=""),"",ROUND($E24-$E24/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G24" s="10">
+        <f>IF(OR($A24="",$E24=""),"",ROUND($E24/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H24" s="10">
+        <f>IF(OR($A24="",$E24=""),"",G24-D24)</f>
+        <v/>
+      </c>
+      <c r="I24" s="22">
+        <f>IF(OR($A24="",$E24="",$E24=0),"",H24/G24)</f>
+        <v/>
+      </c>
+      <c r="J24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8">
+        <f>IF(PRODUCTOS!B25="","",PRODUCTOS!B25)</f>
+        <v/>
+      </c>
+      <c r="B25" s="10">
+        <f>IF($A25="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A25))</f>
+        <v/>
+      </c>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="10">
+        <f>IF($A25="","",B25+IF(C25="",0,C25))</f>
+        <v/>
+      </c>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="10">
+        <f>IF(OR($A25="",$E25=""),"",ROUND($E25-$E25/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G25" s="10">
+        <f>IF(OR($A25="",$E25=""),"",ROUND($E25/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H25" s="10">
+        <f>IF(OR($A25="",$E25=""),"",G25-D25)</f>
+        <v/>
+      </c>
+      <c r="I25" s="22">
+        <f>IF(OR($A25="",$E25="",$E25=0),"",H25/G25)</f>
+        <v/>
+      </c>
+      <c r="J25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8">
+        <f>IF(PRODUCTOS!B26="","",PRODUCTOS!B26)</f>
+        <v/>
+      </c>
+      <c r="B26" s="10">
+        <f>IF($A26="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A26))</f>
+        <v/>
+      </c>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="10">
+        <f>IF($A26="","",B26+IF(C26="",0,C26))</f>
+        <v/>
+      </c>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="10">
+        <f>IF(OR($A26="",$E26=""),"",ROUND($E26-$E26/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G26" s="10">
+        <f>IF(OR($A26="",$E26=""),"",ROUND($E26/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H26" s="10">
+        <f>IF(OR($A26="",$E26=""),"",G26-D26)</f>
+        <v/>
+      </c>
+      <c r="I26" s="22">
+        <f>IF(OR($A26="",$E26="",$E26=0),"",H26/G26)</f>
+        <v/>
+      </c>
+      <c r="J26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8">
+        <f>IF(PRODUCTOS!B27="","",PRODUCTOS!B27)</f>
+        <v/>
+      </c>
+      <c r="B27" s="10">
+        <f>IF($A27="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A27))</f>
+        <v/>
+      </c>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="10">
+        <f>IF($A27="","",B27+IF(C27="",0,C27))</f>
+        <v/>
+      </c>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="10">
+        <f>IF(OR($A27="",$E27=""),"",ROUND($E27-$E27/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G27" s="10">
+        <f>IF(OR($A27="",$E27=""),"",ROUND($E27/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H27" s="10">
+        <f>IF(OR($A27="",$E27=""),"",G27-D27)</f>
+        <v/>
+      </c>
+      <c r="I27" s="22">
+        <f>IF(OR($A27="",$E27="",$E27=0),"",H27/G27)</f>
+        <v/>
+      </c>
+      <c r="J27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8">
+        <f>IF(PRODUCTOS!B28="","",PRODUCTOS!B28)</f>
+        <v/>
+      </c>
+      <c r="B28" s="10">
+        <f>IF($A28="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A28))</f>
+        <v/>
+      </c>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="10">
+        <f>IF($A28="","",B28+IF(C28="",0,C28))</f>
+        <v/>
+      </c>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="10">
+        <f>IF(OR($A28="",$E28=""),"",ROUND($E28-$E28/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G28" s="10">
+        <f>IF(OR($A28="",$E28=""),"",ROUND($E28/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H28" s="10">
+        <f>IF(OR($A28="",$E28=""),"",G28-D28)</f>
+        <v/>
+      </c>
+      <c r="I28" s="22">
+        <f>IF(OR($A28="",$E28="",$E28=0),"",H28/G28)</f>
+        <v/>
+      </c>
+      <c r="J28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8">
+        <f>IF(PRODUCTOS!B29="","",PRODUCTOS!B29)</f>
+        <v/>
+      </c>
+      <c r="B29" s="10">
+        <f>IF($A29="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A29))</f>
+        <v/>
+      </c>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="10">
+        <f>IF($A29="","",B29+IF(C29="",0,C29))</f>
+        <v/>
+      </c>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="10">
+        <f>IF(OR($A29="",$E29=""),"",ROUND($E29-$E29/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G29" s="10">
+        <f>IF(OR($A29="",$E29=""),"",ROUND($E29/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H29" s="10">
+        <f>IF(OR($A29="",$E29=""),"",G29-D29)</f>
+        <v/>
+      </c>
+      <c r="I29" s="22">
+        <f>IF(OR($A29="",$E29="",$E29=0),"",H29/G29)</f>
+        <v/>
+      </c>
+      <c r="J29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8">
+        <f>IF(PRODUCTOS!B30="","",PRODUCTOS!B30)</f>
+        <v/>
+      </c>
+      <c r="B30" s="10">
+        <f>IF($A30="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A30))</f>
+        <v/>
+      </c>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="10">
+        <f>IF($A30="","",B30+IF(C30="",0,C30))</f>
+        <v/>
+      </c>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="10">
+        <f>IF(OR($A30="",$E30=""),"",ROUND($E30-$E30/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G30" s="10">
+        <f>IF(OR($A30="",$E30=""),"",ROUND($E30/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H30" s="10">
+        <f>IF(OR($A30="",$E30=""),"",G30-D30)</f>
+        <v/>
+      </c>
+      <c r="I30" s="22">
+        <f>IF(OR($A30="",$E30="",$E30=0),"",H30/G30)</f>
+        <v/>
+      </c>
+      <c r="J30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8">
+        <f>IF(PRODUCTOS!B31="","",PRODUCTOS!B31)</f>
+        <v/>
+      </c>
+      <c r="B31" s="10">
+        <f>IF($A31="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A31))</f>
+        <v/>
+      </c>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="10">
+        <f>IF($A31="","",B31+IF(C31="",0,C31))</f>
+        <v/>
+      </c>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="10">
+        <f>IF(OR($A31="",$E31=""),"",ROUND($E31-$E31/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G31" s="10">
+        <f>IF(OR($A31="",$E31=""),"",ROUND($E31/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H31" s="10">
+        <f>IF(OR($A31="",$E31=""),"",G31-D31)</f>
+        <v/>
+      </c>
+      <c r="I31" s="22">
+        <f>IF(OR($A31="",$E31="",$E31=0),"",H31/G31)</f>
+        <v/>
+      </c>
+      <c r="J31" s="7" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8">
+        <f>IF(PRODUCTOS!B32="","",PRODUCTOS!B32)</f>
+        <v/>
+      </c>
+      <c r="B32" s="10">
+        <f>IF($A32="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A32))</f>
+        <v/>
+      </c>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="10">
+        <f>IF($A32="","",B32+IF(C32="",0,C32))</f>
+        <v/>
+      </c>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="10">
+        <f>IF(OR($A32="",$E32=""),"",ROUND($E32-$E32/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G32" s="10">
+        <f>IF(OR($A32="",$E32=""),"",ROUND($E32/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H32" s="10">
+        <f>IF(OR($A32="",$E32=""),"",G32-D32)</f>
+        <v/>
+      </c>
+      <c r="I32" s="22">
+        <f>IF(OR($A32="",$E32="",$E32=0),"",H32/G32)</f>
+        <v/>
+      </c>
+      <c r="J32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8">
+        <f>IF(PRODUCTOS!B33="","",PRODUCTOS!B33)</f>
+        <v/>
+      </c>
+      <c r="B33" s="10">
+        <f>IF($A33="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A33))</f>
+        <v/>
+      </c>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="10">
+        <f>IF($A33="","",B33+IF(C33="",0,C33))</f>
+        <v/>
+      </c>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="10">
+        <f>IF(OR($A33="",$E33=""),"",ROUND($E33-$E33/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G33" s="10">
+        <f>IF(OR($A33="",$E33=""),"",ROUND($E33/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H33" s="10">
+        <f>IF(OR($A33="",$E33=""),"",G33-D33)</f>
+        <v/>
+      </c>
+      <c r="I33" s="22">
+        <f>IF(OR($A33="",$E33="",$E33=0),"",H33/G33)</f>
+        <v/>
+      </c>
+      <c r="J33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8">
+        <f>IF(PRODUCTOS!B34="","",PRODUCTOS!B34)</f>
+        <v/>
+      </c>
+      <c r="B34" s="10">
+        <f>IF($A34="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A34))</f>
+        <v/>
+      </c>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="10">
+        <f>IF($A34="","",B34+IF(C34="",0,C34))</f>
+        <v/>
+      </c>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="10">
+        <f>IF(OR($A34="",$E34=""),"",ROUND($E34-$E34/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G34" s="10">
+        <f>IF(OR($A34="",$E34=""),"",ROUND($E34/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H34" s="10">
+        <f>IF(OR($A34="",$E34=""),"",G34-D34)</f>
+        <v/>
+      </c>
+      <c r="I34" s="22">
+        <f>IF(OR($A34="",$E34="",$E34=0),"",H34/G34)</f>
+        <v/>
+      </c>
+      <c r="J34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8">
+        <f>IF(PRODUCTOS!B35="","",PRODUCTOS!B35)</f>
+        <v/>
+      </c>
+      <c r="B35" s="10">
+        <f>IF($A35="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A35))</f>
+        <v/>
+      </c>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="10">
+        <f>IF($A35="","",B35+IF(C35="",0,C35))</f>
+        <v/>
+      </c>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="10">
+        <f>IF(OR($A35="",$E35=""),"",ROUND($E35-$E35/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G35" s="10">
+        <f>IF(OR($A35="",$E35=""),"",ROUND($E35/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H35" s="10">
+        <f>IF(OR($A35="",$E35=""),"",G35-D35)</f>
+        <v/>
+      </c>
+      <c r="I35" s="22">
+        <f>IF(OR($A35="",$E35="",$E35=0),"",H35/G35)</f>
+        <v/>
+      </c>
+      <c r="J35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8">
+        <f>IF(PRODUCTOS!B36="","",PRODUCTOS!B36)</f>
+        <v/>
+      </c>
+      <c r="B36" s="10">
+        <f>IF($A36="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A36))</f>
+        <v/>
+      </c>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="10">
+        <f>IF($A36="","",B36+IF(C36="",0,C36))</f>
+        <v/>
+      </c>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="10">
+        <f>IF(OR($A36="",$E36=""),"",ROUND($E36-$E36/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G36" s="10">
+        <f>IF(OR($A36="",$E36=""),"",ROUND($E36/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H36" s="10">
+        <f>IF(OR($A36="",$E36=""),"",G36-D36)</f>
+        <v/>
+      </c>
+      <c r="I36" s="22">
+        <f>IF(OR($A36="",$E36="",$E36=0),"",H36/G36)</f>
+        <v/>
+      </c>
+      <c r="J36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8">
+        <f>IF(PRODUCTOS!B37="","",PRODUCTOS!B37)</f>
+        <v/>
+      </c>
+      <c r="B37" s="10">
+        <f>IF($A37="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A37))</f>
+        <v/>
+      </c>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="10">
+        <f>IF($A37="","",B37+IF(C37="",0,C37))</f>
+        <v/>
+      </c>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="10">
+        <f>IF(OR($A37="",$E37=""),"",ROUND($E37-$E37/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G37" s="10">
+        <f>IF(OR($A37="",$E37=""),"",ROUND($E37/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H37" s="10">
+        <f>IF(OR($A37="",$E37=""),"",G37-D37)</f>
+        <v/>
+      </c>
+      <c r="I37" s="22">
+        <f>IF(OR($A37="",$E37="",$E37=0),"",H37/G37)</f>
+        <v/>
+      </c>
+      <c r="J37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8">
+        <f>IF(PRODUCTOS!B38="","",PRODUCTOS!B38)</f>
+        <v/>
+      </c>
+      <c r="B38" s="10">
+        <f>IF($A38="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A38))</f>
+        <v/>
+      </c>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="10">
+        <f>IF($A38="","",B38+IF(C38="",0,C38))</f>
+        <v/>
+      </c>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="10">
+        <f>IF(OR($A38="",$E38=""),"",ROUND($E38-$E38/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G38" s="10">
+        <f>IF(OR($A38="",$E38=""),"",ROUND($E38/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H38" s="10">
+        <f>IF(OR($A38="",$E38=""),"",G38-D38)</f>
+        <v/>
+      </c>
+      <c r="I38" s="22">
+        <f>IF(OR($A38="",$E38="",$E38=0),"",H38/G38)</f>
+        <v/>
+      </c>
+      <c r="J38" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8">
+        <f>IF(PRODUCTOS!B39="","",PRODUCTOS!B39)</f>
+        <v/>
+      </c>
+      <c r="B39" s="10">
+        <f>IF($A39="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A39))</f>
+        <v/>
+      </c>
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="10">
+        <f>IF($A39="","",B39+IF(C39="",0,C39))</f>
+        <v/>
+      </c>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="10">
+        <f>IF(OR($A39="",$E39=""),"",ROUND($E39-$E39/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G39" s="10">
+        <f>IF(OR($A39="",$E39=""),"",ROUND($E39/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H39" s="10">
+        <f>IF(OR($A39="",$E39=""),"",G39-D39)</f>
+        <v/>
+      </c>
+      <c r="I39" s="22">
+        <f>IF(OR($A39="",$E39="",$E39=0),"",H39/G39)</f>
+        <v/>
+      </c>
+      <c r="J39" s="7" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8">
+        <f>IF(PRODUCTOS!B40="","",PRODUCTOS!B40)</f>
+        <v/>
+      </c>
+      <c r="B40" s="10">
+        <f>IF($A40="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A40))</f>
+        <v/>
+      </c>
+      <c r="C40" s="9" t="n"/>
+      <c r="D40" s="10">
+        <f>IF($A40="","",B40+IF(C40="",0,C40))</f>
+        <v/>
+      </c>
+      <c r="E40" s="9" t="n"/>
+      <c r="F40" s="10">
+        <f>IF(OR($A40="",$E40=""),"",ROUND($E40-$E40/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G40" s="10">
+        <f>IF(OR($A40="",$E40=""),"",ROUND($E40/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H40" s="10">
+        <f>IF(OR($A40="",$E40=""),"",G40-D40)</f>
+        <v/>
+      </c>
+      <c r="I40" s="22">
+        <f>IF(OR($A40="",$E40="",$E40=0),"",H40/G40)</f>
+        <v/>
+      </c>
+      <c r="J40" s="7" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="8">
+        <f>IF(PRODUCTOS!B41="","",PRODUCTOS!B41)</f>
+        <v/>
+      </c>
+      <c r="B41" s="10">
+        <f>IF($A41="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A41))</f>
+        <v/>
+      </c>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="10">
+        <f>IF($A41="","",B41+IF(C41="",0,C41))</f>
+        <v/>
+      </c>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="10">
+        <f>IF(OR($A41="",$E41=""),"",ROUND($E41-$E41/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G41" s="10">
+        <f>IF(OR($A41="",$E41=""),"",ROUND($E41/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H41" s="10">
+        <f>IF(OR($A41="",$E41=""),"",G41-D41)</f>
+        <v/>
+      </c>
+      <c r="I41" s="22">
+        <f>IF(OR($A41="",$E41="",$E41=0),"",H41/G41)</f>
+        <v/>
+      </c>
+      <c r="J41" s="7" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8">
+        <f>IF(PRODUCTOS!B42="","",PRODUCTOS!B42)</f>
+        <v/>
+      </c>
+      <c r="B42" s="10">
+        <f>IF($A42="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A42))</f>
+        <v/>
+      </c>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="10">
+        <f>IF($A42="","",B42+IF(C42="",0,C42))</f>
+        <v/>
+      </c>
+      <c r="E42" s="9" t="n"/>
+      <c r="F42" s="10">
+        <f>IF(OR($A42="",$E42=""),"",ROUND($E42-$E42/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G42" s="10">
+        <f>IF(OR($A42="",$E42=""),"",ROUND($E42/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H42" s="10">
+        <f>IF(OR($A42="",$E42=""),"",G42-D42)</f>
+        <v/>
+      </c>
+      <c r="I42" s="22">
+        <f>IF(OR($A42="",$E42="",$E42=0),"",H42/G42)</f>
+        <v/>
+      </c>
+      <c r="J42" s="7" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8">
+        <f>IF(PRODUCTOS!B43="","",PRODUCTOS!B43)</f>
+        <v/>
+      </c>
+      <c r="B43" s="10">
+        <f>IF($A43="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A43))</f>
+        <v/>
+      </c>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="10">
+        <f>IF($A43="","",B43+IF(C43="",0,C43))</f>
+        <v/>
+      </c>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="10">
+        <f>IF(OR($A43="",$E43=""),"",ROUND($E43-$E43/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G43" s="10">
+        <f>IF(OR($A43="",$E43=""),"",ROUND($E43/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H43" s="10">
+        <f>IF(OR($A43="",$E43=""),"",G43-D43)</f>
+        <v/>
+      </c>
+      <c r="I43" s="22">
+        <f>IF(OR($A43="",$E43="",$E43=0),"",H43/G43)</f>
+        <v/>
+      </c>
+      <c r="J43" s="7" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="8">
+        <f>IF(PRODUCTOS!B44="","",PRODUCTOS!B44)</f>
+        <v/>
+      </c>
+      <c r="B44" s="10">
+        <f>IF($A44="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A44))</f>
+        <v/>
+      </c>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="10">
+        <f>IF($A44="","",B44+IF(C44="",0,C44))</f>
+        <v/>
+      </c>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="10">
+        <f>IF(OR($A44="",$E44=""),"",ROUND($E44-$E44/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G44" s="10">
+        <f>IF(OR($A44="",$E44=""),"",ROUND($E44/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H44" s="10">
+        <f>IF(OR($A44="",$E44=""),"",G44-D44)</f>
+        <v/>
+      </c>
+      <c r="I44" s="22">
+        <f>IF(OR($A44="",$E44="",$E44=0),"",H44/G44)</f>
+        <v/>
+      </c>
+      <c r="J44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8">
+        <f>IF(PRODUCTOS!B45="","",PRODUCTOS!B45)</f>
+        <v/>
+      </c>
+      <c r="B45" s="10">
+        <f>IF($A45="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A45))</f>
+        <v/>
+      </c>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="10">
+        <f>IF($A45="","",B45+IF(C45="",0,C45))</f>
+        <v/>
+      </c>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="10">
+        <f>IF(OR($A45="",$E45=""),"",ROUND($E45-$E45/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G45" s="10">
+        <f>IF(OR($A45="",$E45=""),"",ROUND($E45/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H45" s="10">
+        <f>IF(OR($A45="",$E45=""),"",G45-D45)</f>
+        <v/>
+      </c>
+      <c r="I45" s="22">
+        <f>IF(OR($A45="",$E45="",$E45=0),"",H45/G45)</f>
+        <v/>
+      </c>
+      <c r="J45" s="7" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="8">
+        <f>IF(PRODUCTOS!B46="","",PRODUCTOS!B46)</f>
+        <v/>
+      </c>
+      <c r="B46" s="10">
+        <f>IF($A46="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A46))</f>
+        <v/>
+      </c>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="10">
+        <f>IF($A46="","",B46+IF(C46="",0,C46))</f>
+        <v/>
+      </c>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="10">
+        <f>IF(OR($A46="",$E46=""),"",ROUND($E46-$E46/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G46" s="10">
+        <f>IF(OR($A46="",$E46=""),"",ROUND($E46/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H46" s="10">
+        <f>IF(OR($A46="",$E46=""),"",G46-D46)</f>
+        <v/>
+      </c>
+      <c r="I46" s="22">
+        <f>IF(OR($A46="",$E46="",$E46=0),"",H46/G46)</f>
+        <v/>
+      </c>
+      <c r="J46" s="7" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="8">
+        <f>IF(PRODUCTOS!B47="","",PRODUCTOS!B47)</f>
+        <v/>
+      </c>
+      <c r="B47" s="10">
+        <f>IF($A47="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A47))</f>
+        <v/>
+      </c>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="10">
+        <f>IF($A47="","",B47+IF(C47="",0,C47))</f>
+        <v/>
+      </c>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="10">
+        <f>IF(OR($A47="",$E47=""),"",ROUND($E47-$E47/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G47" s="10">
+        <f>IF(OR($A47="",$E47=""),"",ROUND($E47/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H47" s="10">
+        <f>IF(OR($A47="",$E47=""),"",G47-D47)</f>
+        <v/>
+      </c>
+      <c r="I47" s="22">
+        <f>IF(OR($A47="",$E47="",$E47=0),"",H47/G47)</f>
+        <v/>
+      </c>
+      <c r="J47" s="7" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8">
+        <f>IF(PRODUCTOS!B48="","",PRODUCTOS!B48)</f>
+        <v/>
+      </c>
+      <c r="B48" s="10">
+        <f>IF($A48="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A48))</f>
+        <v/>
+      </c>
+      <c r="C48" s="9" t="n"/>
+      <c r="D48" s="10">
+        <f>IF($A48="","",B48+IF(C48="",0,C48))</f>
+        <v/>
+      </c>
+      <c r="E48" s="9" t="n"/>
+      <c r="F48" s="10">
+        <f>IF(OR($A48="",$E48=""),"",ROUND($E48-$E48/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G48" s="10">
+        <f>IF(OR($A48="",$E48=""),"",ROUND($E48/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H48" s="10">
+        <f>IF(OR($A48="",$E48=""),"",G48-D48)</f>
+        <v/>
+      </c>
+      <c r="I48" s="22">
+        <f>IF(OR($A48="",$E48="",$E48=0),"",H48/G48)</f>
+        <v/>
+      </c>
+      <c r="J48" s="7" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="8">
+        <f>IF(PRODUCTOS!B49="","",PRODUCTOS!B49)</f>
+        <v/>
+      </c>
+      <c r="B49" s="10">
+        <f>IF($A49="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A49))</f>
+        <v/>
+      </c>
+      <c r="C49" s="9" t="n"/>
+      <c r="D49" s="10">
+        <f>IF($A49="","",B49+IF(C49="",0,C49))</f>
+        <v/>
+      </c>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="10">
+        <f>IF(OR($A49="",$E49=""),"",ROUND($E49-$E49/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G49" s="10">
+        <f>IF(OR($A49="",$E49=""),"",ROUND($E49/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H49" s="10">
+        <f>IF(OR($A49="",$E49=""),"",G49-D49)</f>
+        <v/>
+      </c>
+      <c r="I49" s="22">
+        <f>IF(OR($A49="",$E49="",$E49=0),"",H49/G49)</f>
+        <v/>
+      </c>
+      <c r="J49" s="7" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8">
+        <f>IF(PRODUCTOS!B50="","",PRODUCTOS!B50)</f>
+        <v/>
+      </c>
+      <c r="B50" s="10">
+        <f>IF($A50="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A50))</f>
+        <v/>
+      </c>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="10">
+        <f>IF($A50="","",B50+IF(C50="",0,C50))</f>
+        <v/>
+      </c>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="10">
+        <f>IF(OR($A50="",$E50=""),"",ROUND($E50-$E50/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G50" s="10">
+        <f>IF(OR($A50="",$E50=""),"",ROUND($E50/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H50" s="10">
+        <f>IF(OR($A50="",$E50=""),"",G50-D50)</f>
+        <v/>
+      </c>
+      <c r="I50" s="22">
+        <f>IF(OR($A50="",$E50="",$E50=0),"",H50/G50)</f>
+        <v/>
+      </c>
+      <c r="J50" s="7" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="8">
+        <f>IF(PRODUCTOS!B51="","",PRODUCTOS!B51)</f>
+        <v/>
+      </c>
+      <c r="B51" s="10">
+        <f>IF($A51="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A51))</f>
+        <v/>
+      </c>
+      <c r="C51" s="9" t="n"/>
+      <c r="D51" s="10">
+        <f>IF($A51="","",B51+IF(C51="",0,C51))</f>
+        <v/>
+      </c>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="10">
+        <f>IF(OR($A51="",$E51=""),"",ROUND($E51-$E51/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G51" s="10">
+        <f>IF(OR($A51="",$E51=""),"",ROUND($E51/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H51" s="10">
+        <f>IF(OR($A51="",$E51=""),"",G51-D51)</f>
+        <v/>
+      </c>
+      <c r="I51" s="22">
+        <f>IF(OR($A51="",$E51="",$E51=0),"",H51/G51)</f>
+        <v/>
+      </c>
+      <c r="J51" s="7" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="8">
+        <f>IF(PRODUCTOS!B52="","",PRODUCTOS!B52)</f>
+        <v/>
+      </c>
+      <c r="B52" s="10">
+        <f>IF($A52="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A52))</f>
+        <v/>
+      </c>
+      <c r="C52" s="9" t="n"/>
+      <c r="D52" s="10">
+        <f>IF($A52="","",B52+IF(C52="",0,C52))</f>
+        <v/>
+      </c>
+      <c r="E52" s="9" t="n"/>
+      <c r="F52" s="10">
+        <f>IF(OR($A52="",$E52=""),"",ROUND($E52-$E52/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G52" s="10">
+        <f>IF(OR($A52="",$E52=""),"",ROUND($E52/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H52" s="10">
+        <f>IF(OR($A52="",$E52=""),"",G52-D52)</f>
+        <v/>
+      </c>
+      <c r="I52" s="22">
+        <f>IF(OR($A52="",$E52="",$E52=0),"",H52/G52)</f>
+        <v/>
+      </c>
+      <c r="J52" s="7" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="8">
+        <f>IF(PRODUCTOS!B53="","",PRODUCTOS!B53)</f>
+        <v/>
+      </c>
+      <c r="B53" s="10">
+        <f>IF($A53="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A53))</f>
+        <v/>
+      </c>
+      <c r="C53" s="9" t="n"/>
+      <c r="D53" s="10">
+        <f>IF($A53="","",B53+IF(C53="",0,C53))</f>
+        <v/>
+      </c>
+      <c r="E53" s="9" t="n"/>
+      <c r="F53" s="10">
+        <f>IF(OR($A53="",$E53=""),"",ROUND($E53-$E53/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G53" s="10">
+        <f>IF(OR($A53="",$E53=""),"",ROUND($E53/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H53" s="10">
+        <f>IF(OR($A53="",$E53=""),"",G53-D53)</f>
+        <v/>
+      </c>
+      <c r="I53" s="22">
+        <f>IF(OR($A53="",$E53="",$E53=0),"",H53/G53)</f>
+        <v/>
+      </c>
+      <c r="J53" s="7" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="8">
+        <f>IF(PRODUCTOS!B54="","",PRODUCTOS!B54)</f>
+        <v/>
+      </c>
+      <c r="B54" s="10">
+        <f>IF($A54="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A54))</f>
+        <v/>
+      </c>
+      <c r="C54" s="9" t="n"/>
+      <c r="D54" s="10">
+        <f>IF($A54="","",B54+IF(C54="",0,C54))</f>
+        <v/>
+      </c>
+      <c r="E54" s="9" t="n"/>
+      <c r="F54" s="10">
+        <f>IF(OR($A54="",$E54=""),"",ROUND($E54-$E54/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G54" s="10">
+        <f>IF(OR($A54="",$E54=""),"",ROUND($E54/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H54" s="10">
+        <f>IF(OR($A54="",$E54=""),"",G54-D54)</f>
+        <v/>
+      </c>
+      <c r="I54" s="22">
+        <f>IF(OR($A54="",$E54="",$E54=0),"",H54/G54)</f>
+        <v/>
+      </c>
+      <c r="J54" s="7" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="8">
+        <f>IF(PRODUCTOS!B55="","",PRODUCTOS!B55)</f>
+        <v/>
+      </c>
+      <c r="B55" s="10">
+        <f>IF($A55="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A55))</f>
+        <v/>
+      </c>
+      <c r="C55" s="9" t="n"/>
+      <c r="D55" s="10">
+        <f>IF($A55="","",B55+IF(C55="",0,C55))</f>
+        <v/>
+      </c>
+      <c r="E55" s="9" t="n"/>
+      <c r="F55" s="10">
+        <f>IF(OR($A55="",$E55=""),"",ROUND($E55-$E55/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G55" s="10">
+        <f>IF(OR($A55="",$E55=""),"",ROUND($E55/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H55" s="10">
+        <f>IF(OR($A55="",$E55=""),"",G55-D55)</f>
+        <v/>
+      </c>
+      <c r="I55" s="22">
+        <f>IF(OR($A55="",$E55="",$E55=0),"",H55/G55)</f>
+        <v/>
+      </c>
+      <c r="J55" s="7" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="8">
+        <f>IF(PRODUCTOS!B56="","",PRODUCTOS!B56)</f>
+        <v/>
+      </c>
+      <c r="B56" s="10">
+        <f>IF($A56="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A56))</f>
+        <v/>
+      </c>
+      <c r="C56" s="9" t="n"/>
+      <c r="D56" s="10">
+        <f>IF($A56="","",B56+IF(C56="",0,C56))</f>
+        <v/>
+      </c>
+      <c r="E56" s="9" t="n"/>
+      <c r="F56" s="10">
+        <f>IF(OR($A56="",$E56=""),"",ROUND($E56-$E56/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G56" s="10">
+        <f>IF(OR($A56="",$E56=""),"",ROUND($E56/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H56" s="10">
+        <f>IF(OR($A56="",$E56=""),"",G56-D56)</f>
+        <v/>
+      </c>
+      <c r="I56" s="22">
+        <f>IF(OR($A56="",$E56="",$E56=0),"",H56/G56)</f>
+        <v/>
+      </c>
+      <c r="J56" s="7" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="8">
+        <f>IF(PRODUCTOS!B57="","",PRODUCTOS!B57)</f>
+        <v/>
+      </c>
+      <c r="B57" s="10">
+        <f>IF($A57="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A57))</f>
+        <v/>
+      </c>
+      <c r="C57" s="9" t="n"/>
+      <c r="D57" s="10">
+        <f>IF($A57="","",B57+IF(C57="",0,C57))</f>
+        <v/>
+      </c>
+      <c r="E57" s="9" t="n"/>
+      <c r="F57" s="10">
+        <f>IF(OR($A57="",$E57=""),"",ROUND($E57-$E57/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G57" s="10">
+        <f>IF(OR($A57="",$E57=""),"",ROUND($E57/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H57" s="10">
+        <f>IF(OR($A57="",$E57=""),"",G57-D57)</f>
+        <v/>
+      </c>
+      <c r="I57" s="22">
+        <f>IF(OR($A57="",$E57="",$E57=0),"",H57/G57)</f>
+        <v/>
+      </c>
+      <c r="J57" s="7" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="8">
+        <f>IF(PRODUCTOS!B58="","",PRODUCTOS!B58)</f>
+        <v/>
+      </c>
+      <c r="B58" s="10">
+        <f>IF($A58="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A58))</f>
+        <v/>
+      </c>
+      <c r="C58" s="9" t="n"/>
+      <c r="D58" s="10">
+        <f>IF($A58="","",B58+IF(C58="",0,C58))</f>
+        <v/>
+      </c>
+      <c r="E58" s="9" t="n"/>
+      <c r="F58" s="10">
+        <f>IF(OR($A58="",$E58=""),"",ROUND($E58-$E58/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G58" s="10">
+        <f>IF(OR($A58="",$E58=""),"",ROUND($E58/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H58" s="10">
+        <f>IF(OR($A58="",$E58=""),"",G58-D58)</f>
+        <v/>
+      </c>
+      <c r="I58" s="22">
+        <f>IF(OR($A58="",$E58="",$E58=0),"",H58/G58)</f>
+        <v/>
+      </c>
+      <c r="J58" s="7" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="8">
+        <f>IF(PRODUCTOS!B59="","",PRODUCTOS!B59)</f>
+        <v/>
+      </c>
+      <c r="B59" s="10">
+        <f>IF($A59="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A59))</f>
+        <v/>
+      </c>
+      <c r="C59" s="9" t="n"/>
+      <c r="D59" s="10">
+        <f>IF($A59="","",B59+IF(C59="",0,C59))</f>
+        <v/>
+      </c>
+      <c r="E59" s="9" t="n"/>
+      <c r="F59" s="10">
+        <f>IF(OR($A59="",$E59=""),"",ROUND($E59-$E59/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G59" s="10">
+        <f>IF(OR($A59="",$E59=""),"",ROUND($E59/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H59" s="10">
+        <f>IF(OR($A59="",$E59=""),"",G59-D59)</f>
+        <v/>
+      </c>
+      <c r="I59" s="22">
+        <f>IF(OR($A59="",$E59="",$E59=0),"",H59/G59)</f>
+        <v/>
+      </c>
+      <c r="J59" s="7" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="8">
+        <f>IF(PRODUCTOS!B60="","",PRODUCTOS!B60)</f>
+        <v/>
+      </c>
+      <c r="B60" s="10">
+        <f>IF($A60="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A60))</f>
+        <v/>
+      </c>
+      <c r="C60" s="9" t="n"/>
+      <c r="D60" s="10">
+        <f>IF($A60="","",B60+IF(C60="",0,C60))</f>
+        <v/>
+      </c>
+      <c r="E60" s="9" t="n"/>
+      <c r="F60" s="10">
+        <f>IF(OR($A60="",$E60=""),"",ROUND($E60-$E60/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G60" s="10">
+        <f>IF(OR($A60="",$E60=""),"",ROUND($E60/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H60" s="10">
+        <f>IF(OR($A60="",$E60=""),"",G60-D60)</f>
+        <v/>
+      </c>
+      <c r="I60" s="22">
+        <f>IF(OR($A60="",$E60="",$E60=0),"",H60/G60)</f>
+        <v/>
+      </c>
+      <c r="J60" s="7" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="8">
+        <f>IF(PRODUCTOS!B61="","",PRODUCTOS!B61)</f>
+        <v/>
+      </c>
+      <c r="B61" s="10">
+        <f>IF($A61="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A61))</f>
+        <v/>
+      </c>
+      <c r="C61" s="9" t="n"/>
+      <c r="D61" s="10">
+        <f>IF($A61="","",B61+IF(C61="",0,C61))</f>
+        <v/>
+      </c>
+      <c r="E61" s="9" t="n"/>
+      <c r="F61" s="10">
+        <f>IF(OR($A61="",$E61=""),"",ROUND($E61-$E61/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G61" s="10">
+        <f>IF(OR($A61="",$E61=""),"",ROUND($E61/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H61" s="10">
+        <f>IF(OR($A61="",$E61=""),"",G61-D61)</f>
+        <v/>
+      </c>
+      <c r="I61" s="22">
+        <f>IF(OR($A61="",$E61="",$E61=0),"",H61/G61)</f>
+        <v/>
+      </c>
+      <c r="J61" s="7" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="8">
+        <f>IF(PRODUCTOS!B62="","",PRODUCTOS!B62)</f>
+        <v/>
+      </c>
+      <c r="B62" s="10">
+        <f>IF($A62="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A62))</f>
+        <v/>
+      </c>
+      <c r="C62" s="9" t="n"/>
+      <c r="D62" s="10">
+        <f>IF($A62="","",B62+IF(C62="",0,C62))</f>
+        <v/>
+      </c>
+      <c r="E62" s="9" t="n"/>
+      <c r="F62" s="10">
+        <f>IF(OR($A62="",$E62=""),"",ROUND($E62-$E62/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G62" s="10">
+        <f>IF(OR($A62="",$E62=""),"",ROUND($E62/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H62" s="10">
+        <f>IF(OR($A62="",$E62=""),"",G62-D62)</f>
+        <v/>
+      </c>
+      <c r="I62" s="22">
+        <f>IF(OR($A62="",$E62="",$E62=0),"",H62/G62)</f>
+        <v/>
+      </c>
+      <c r="J62" s="7" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="8">
+        <f>IF(PRODUCTOS!B63="","",PRODUCTOS!B63)</f>
+        <v/>
+      </c>
+      <c r="B63" s="10">
+        <f>IF($A63="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A63))</f>
+        <v/>
+      </c>
+      <c r="C63" s="9" t="n"/>
+      <c r="D63" s="10">
+        <f>IF($A63="","",B63+IF(C63="",0,C63))</f>
+        <v/>
+      </c>
+      <c r="E63" s="9" t="n"/>
+      <c r="F63" s="10">
+        <f>IF(OR($A63="",$E63=""),"",ROUND($E63-$E63/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G63" s="10">
+        <f>IF(OR($A63="",$E63=""),"",ROUND($E63/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H63" s="10">
+        <f>IF(OR($A63="",$E63=""),"",G63-D63)</f>
+        <v/>
+      </c>
+      <c r="I63" s="22">
+        <f>IF(OR($A63="",$E63="",$E63=0),"",H63/G63)</f>
+        <v/>
+      </c>
+      <c r="J63" s="7" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="8">
+        <f>IF(PRODUCTOS!B64="","",PRODUCTOS!B64)</f>
+        <v/>
+      </c>
+      <c r="B64" s="10">
+        <f>IF($A64="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A64))</f>
+        <v/>
+      </c>
+      <c r="C64" s="9" t="n"/>
+      <c r="D64" s="10">
+        <f>IF($A64="","",B64+IF(C64="",0,C64))</f>
+        <v/>
+      </c>
+      <c r="E64" s="9" t="n"/>
+      <c r="F64" s="10">
+        <f>IF(OR($A64="",$E64=""),"",ROUND($E64-$E64/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G64" s="10">
+        <f>IF(OR($A64="",$E64=""),"",ROUND($E64/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H64" s="10">
+        <f>IF(OR($A64="",$E64=""),"",G64-D64)</f>
+        <v/>
+      </c>
+      <c r="I64" s="22">
+        <f>IF(OR($A64="",$E64="",$E64=0),"",H64/G64)</f>
+        <v/>
+      </c>
+      <c r="J64" s="7" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="8">
+        <f>IF(PRODUCTOS!B65="","",PRODUCTOS!B65)</f>
+        <v/>
+      </c>
+      <c r="B65" s="10">
+        <f>IF($A65="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A65))</f>
+        <v/>
+      </c>
+      <c r="C65" s="9" t="n"/>
+      <c r="D65" s="10">
+        <f>IF($A65="","",B65+IF(C65="",0,C65))</f>
+        <v/>
+      </c>
+      <c r="E65" s="9" t="n"/>
+      <c r="F65" s="10">
+        <f>IF(OR($A65="",$E65=""),"",ROUND($E65-$E65/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G65" s="10">
+        <f>IF(OR($A65="",$E65=""),"",ROUND($E65/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H65" s="10">
+        <f>IF(OR($A65="",$E65=""),"",G65-D65)</f>
+        <v/>
+      </c>
+      <c r="I65" s="22">
+        <f>IF(OR($A65="",$E65="",$E65=0),"",H65/G65)</f>
+        <v/>
+      </c>
+      <c r="J65" s="7" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="8">
+        <f>IF(PRODUCTOS!B66="","",PRODUCTOS!B66)</f>
+        <v/>
+      </c>
+      <c r="B66" s="10">
+        <f>IF($A66="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A66))</f>
+        <v/>
+      </c>
+      <c r="C66" s="9" t="n"/>
+      <c r="D66" s="10">
+        <f>IF($A66="","",B66+IF(C66="",0,C66))</f>
+        <v/>
+      </c>
+      <c r="E66" s="9" t="n"/>
+      <c r="F66" s="10">
+        <f>IF(OR($A66="",$E66=""),"",ROUND($E66-$E66/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G66" s="10">
+        <f>IF(OR($A66="",$E66=""),"",ROUND($E66/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H66" s="10">
+        <f>IF(OR($A66="",$E66=""),"",G66-D66)</f>
+        <v/>
+      </c>
+      <c r="I66" s="22">
+        <f>IF(OR($A66="",$E66="",$E66=0),"",H66/G66)</f>
+        <v/>
+      </c>
+      <c r="J66" s="7" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="8">
+        <f>IF(PRODUCTOS!B67="","",PRODUCTOS!B67)</f>
+        <v/>
+      </c>
+      <c r="B67" s="10">
+        <f>IF($A67="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A67))</f>
+        <v/>
+      </c>
+      <c r="C67" s="9" t="n"/>
+      <c r="D67" s="10">
+        <f>IF($A67="","",B67+IF(C67="",0,C67))</f>
+        <v/>
+      </c>
+      <c r="E67" s="9" t="n"/>
+      <c r="F67" s="10">
+        <f>IF(OR($A67="",$E67=""),"",ROUND($E67-$E67/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G67" s="10">
+        <f>IF(OR($A67="",$E67=""),"",ROUND($E67/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H67" s="10">
+        <f>IF(OR($A67="",$E67=""),"",G67-D67)</f>
+        <v/>
+      </c>
+      <c r="I67" s="22">
+        <f>IF(OR($A67="",$E67="",$E67=0),"",H67/G67)</f>
+        <v/>
+      </c>
+      <c r="J67" s="7" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="8">
+        <f>IF(PRODUCTOS!B68="","",PRODUCTOS!B68)</f>
+        <v/>
+      </c>
+      <c r="B68" s="10">
+        <f>IF($A68="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A68))</f>
+        <v/>
+      </c>
+      <c r="C68" s="9" t="n"/>
+      <c r="D68" s="10">
+        <f>IF($A68="","",B68+IF(C68="",0,C68))</f>
+        <v/>
+      </c>
+      <c r="E68" s="9" t="n"/>
+      <c r="F68" s="10">
+        <f>IF(OR($A68="",$E68=""),"",ROUND($E68-$E68/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G68" s="10">
+        <f>IF(OR($A68="",$E68=""),"",ROUND($E68/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H68" s="10">
+        <f>IF(OR($A68="",$E68=""),"",G68-D68)</f>
+        <v/>
+      </c>
+      <c r="I68" s="22">
+        <f>IF(OR($A68="",$E68="",$E68=0),"",H68/G68)</f>
+        <v/>
+      </c>
+      <c r="J68" s="7" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="8">
+        <f>IF(PRODUCTOS!B69="","",PRODUCTOS!B69)</f>
+        <v/>
+      </c>
+      <c r="B69" s="10">
+        <f>IF($A69="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A69))</f>
+        <v/>
+      </c>
+      <c r="C69" s="9" t="n"/>
+      <c r="D69" s="10">
+        <f>IF($A69="","",B69+IF(C69="",0,C69))</f>
+        <v/>
+      </c>
+      <c r="E69" s="9" t="n"/>
+      <c r="F69" s="10">
+        <f>IF(OR($A69="",$E69=""),"",ROUND($E69-$E69/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G69" s="10">
+        <f>IF(OR($A69="",$E69=""),"",ROUND($E69/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H69" s="10">
+        <f>IF(OR($A69="",$E69=""),"",G69-D69)</f>
+        <v/>
+      </c>
+      <c r="I69" s="22">
+        <f>IF(OR($A69="",$E69="",$E69=0),"",H69/G69)</f>
+        <v/>
+      </c>
+      <c r="J69" s="7" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="8">
+        <f>IF(PRODUCTOS!B70="","",PRODUCTOS!B70)</f>
+        <v/>
+      </c>
+      <c r="B70" s="10">
+        <f>IF($A70="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A70))</f>
+        <v/>
+      </c>
+      <c r="C70" s="9" t="n"/>
+      <c r="D70" s="10">
+        <f>IF($A70="","",B70+IF(C70="",0,C70))</f>
+        <v/>
+      </c>
+      <c r="E70" s="9" t="n"/>
+      <c r="F70" s="10">
+        <f>IF(OR($A70="",$E70=""),"",ROUND($E70-$E70/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G70" s="10">
+        <f>IF(OR($A70="",$E70=""),"",ROUND($E70/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H70" s="10">
+        <f>IF(OR($A70="",$E70=""),"",G70-D70)</f>
+        <v/>
+      </c>
+      <c r="I70" s="22">
+        <f>IF(OR($A70="",$E70="",$E70=0),"",H70/G70)</f>
+        <v/>
+      </c>
+      <c r="J70" s="7" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="8">
+        <f>IF(PRODUCTOS!B71="","",PRODUCTOS!B71)</f>
+        <v/>
+      </c>
+      <c r="B71" s="10">
+        <f>IF($A71="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A71))</f>
+        <v/>
+      </c>
+      <c r="C71" s="9" t="n"/>
+      <c r="D71" s="10">
+        <f>IF($A71="","",B71+IF(C71="",0,C71))</f>
+        <v/>
+      </c>
+      <c r="E71" s="9" t="n"/>
+      <c r="F71" s="10">
+        <f>IF(OR($A71="",$E71=""),"",ROUND($E71-$E71/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G71" s="10">
+        <f>IF(OR($A71="",$E71=""),"",ROUND($E71/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H71" s="10">
+        <f>IF(OR($A71="",$E71=""),"",G71-D71)</f>
+        <v/>
+      </c>
+      <c r="I71" s="22">
+        <f>IF(OR($A71="",$E71="",$E71=0),"",H71/G71)</f>
+        <v/>
+      </c>
+      <c r="J71" s="7" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="8">
+        <f>IF(PRODUCTOS!B72="","",PRODUCTOS!B72)</f>
+        <v/>
+      </c>
+      <c r="B72" s="10">
+        <f>IF($A72="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A72))</f>
+        <v/>
+      </c>
+      <c r="C72" s="9" t="n"/>
+      <c r="D72" s="10">
+        <f>IF($A72="","",B72+IF(C72="",0,C72))</f>
+        <v/>
+      </c>
+      <c r="E72" s="9" t="n"/>
+      <c r="F72" s="10">
+        <f>IF(OR($A72="",$E72=""),"",ROUND($E72-$E72/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G72" s="10">
+        <f>IF(OR($A72="",$E72=""),"",ROUND($E72/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H72" s="10">
+        <f>IF(OR($A72="",$E72=""),"",G72-D72)</f>
+        <v/>
+      </c>
+      <c r="I72" s="22">
+        <f>IF(OR($A72="",$E72="",$E72=0),"",H72/G72)</f>
+        <v/>
+      </c>
+      <c r="J72" s="7" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="8">
+        <f>IF(PRODUCTOS!B73="","",PRODUCTOS!B73)</f>
+        <v/>
+      </c>
+      <c r="B73" s="10">
+        <f>IF($A73="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A73))</f>
+        <v/>
+      </c>
+      <c r="C73" s="9" t="n"/>
+      <c r="D73" s="10">
+        <f>IF($A73="","",B73+IF(C73="",0,C73))</f>
+        <v/>
+      </c>
+      <c r="E73" s="9" t="n"/>
+      <c r="F73" s="10">
+        <f>IF(OR($A73="",$E73=""),"",ROUND($E73-$E73/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G73" s="10">
+        <f>IF(OR($A73="",$E73=""),"",ROUND($E73/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H73" s="10">
+        <f>IF(OR($A73="",$E73=""),"",G73-D73)</f>
+        <v/>
+      </c>
+      <c r="I73" s="22">
+        <f>IF(OR($A73="",$E73="",$E73=0),"",H73/G73)</f>
+        <v/>
+      </c>
+      <c r="J73" s="7" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="8">
+        <f>IF(PRODUCTOS!B74="","",PRODUCTOS!B74)</f>
+        <v/>
+      </c>
+      <c r="B74" s="10">
+        <f>IF($A74="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A74))</f>
+        <v/>
+      </c>
+      <c r="C74" s="9" t="n"/>
+      <c r="D74" s="10">
+        <f>IF($A74="","",B74+IF(C74="",0,C74))</f>
+        <v/>
+      </c>
+      <c r="E74" s="9" t="n"/>
+      <c r="F74" s="10">
+        <f>IF(OR($A74="",$E74=""),"",ROUND($E74-$E74/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G74" s="10">
+        <f>IF(OR($A74="",$E74=""),"",ROUND($E74/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H74" s="10">
+        <f>IF(OR($A74="",$E74=""),"",G74-D74)</f>
+        <v/>
+      </c>
+      <c r="I74" s="22">
+        <f>IF(OR($A74="",$E74="",$E74=0),"",H74/G74)</f>
+        <v/>
+      </c>
+      <c r="J74" s="7" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="8">
+        <f>IF(PRODUCTOS!B75="","",PRODUCTOS!B75)</f>
+        <v/>
+      </c>
+      <c r="B75" s="10">
+        <f>IF($A75="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A75))</f>
+        <v/>
+      </c>
+      <c r="C75" s="9" t="n"/>
+      <c r="D75" s="10">
+        <f>IF($A75="","",B75+IF(C75="",0,C75))</f>
+        <v/>
+      </c>
+      <c r="E75" s="9" t="n"/>
+      <c r="F75" s="10">
+        <f>IF(OR($A75="",$E75=""),"",ROUND($E75-$E75/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G75" s="10">
+        <f>IF(OR($A75="",$E75=""),"",ROUND($E75/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H75" s="10">
+        <f>IF(OR($A75="",$E75=""),"",G75-D75)</f>
+        <v/>
+      </c>
+      <c r="I75" s="22">
+        <f>IF(OR($A75="",$E75="",$E75=0),"",H75/G75)</f>
+        <v/>
+      </c>
+      <c r="J75" s="7" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="8">
+        <f>IF(PRODUCTOS!B76="","",PRODUCTOS!B76)</f>
+        <v/>
+      </c>
+      <c r="B76" s="10">
+        <f>IF($A76="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A76))</f>
+        <v/>
+      </c>
+      <c r="C76" s="9" t="n"/>
+      <c r="D76" s="10">
+        <f>IF($A76="","",B76+IF(C76="",0,C76))</f>
+        <v/>
+      </c>
+      <c r="E76" s="9" t="n"/>
+      <c r="F76" s="10">
+        <f>IF(OR($A76="",$E76=""),"",ROUND($E76-$E76/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G76" s="10">
+        <f>IF(OR($A76="",$E76=""),"",ROUND($E76/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H76" s="10">
+        <f>IF(OR($A76="",$E76=""),"",G76-D76)</f>
+        <v/>
+      </c>
+      <c r="I76" s="22">
+        <f>IF(OR($A76="",$E76="",$E76=0),"",H76/G76)</f>
+        <v/>
+      </c>
+      <c r="J76" s="7" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="8">
+        <f>IF(PRODUCTOS!B77="","",PRODUCTOS!B77)</f>
+        <v/>
+      </c>
+      <c r="B77" s="10">
+        <f>IF($A77="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A77))</f>
+        <v/>
+      </c>
+      <c r="C77" s="9" t="n"/>
+      <c r="D77" s="10">
+        <f>IF($A77="","",B77+IF(C77="",0,C77))</f>
+        <v/>
+      </c>
+      <c r="E77" s="9" t="n"/>
+      <c r="F77" s="10">
+        <f>IF(OR($A77="",$E77=""),"",ROUND($E77-$E77/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G77" s="10">
+        <f>IF(OR($A77="",$E77=""),"",ROUND($E77/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H77" s="10">
+        <f>IF(OR($A77="",$E77=""),"",G77-D77)</f>
+        <v/>
+      </c>
+      <c r="I77" s="22">
+        <f>IF(OR($A77="",$E77="",$E77=0),"",H77/G77)</f>
+        <v/>
+      </c>
+      <c r="J77" s="7" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="8">
+        <f>IF(PRODUCTOS!B78="","",PRODUCTOS!B78)</f>
+        <v/>
+      </c>
+      <c r="B78" s="10">
+        <f>IF($A78="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A78))</f>
+        <v/>
+      </c>
+      <c r="C78" s="9" t="n"/>
+      <c r="D78" s="10">
+        <f>IF($A78="","",B78+IF(C78="",0,C78))</f>
+        <v/>
+      </c>
+      <c r="E78" s="9" t="n"/>
+      <c r="F78" s="10">
+        <f>IF(OR($A78="",$E78=""),"",ROUND($E78-$E78/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G78" s="10">
+        <f>IF(OR($A78="",$E78=""),"",ROUND($E78/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H78" s="10">
+        <f>IF(OR($A78="",$E78=""),"",G78-D78)</f>
+        <v/>
+      </c>
+      <c r="I78" s="22">
+        <f>IF(OR($A78="",$E78="",$E78=0),"",H78/G78)</f>
+        <v/>
+      </c>
+      <c r="J78" s="7" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="8">
+        <f>IF(PRODUCTOS!B79="","",PRODUCTOS!B79)</f>
+        <v/>
+      </c>
+      <c r="B79" s="10">
+        <f>IF($A79="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A79))</f>
+        <v/>
+      </c>
+      <c r="C79" s="9" t="n"/>
+      <c r="D79" s="10">
+        <f>IF($A79="","",B79+IF(C79="",0,C79))</f>
+        <v/>
+      </c>
+      <c r="E79" s="9" t="n"/>
+      <c r="F79" s="10">
+        <f>IF(OR($A79="",$E79=""),"",ROUND($E79-$E79/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G79" s="10">
+        <f>IF(OR($A79="",$E79=""),"",ROUND($E79/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H79" s="10">
+        <f>IF(OR($A79="",$E79=""),"",G79-D79)</f>
+        <v/>
+      </c>
+      <c r="I79" s="22">
+        <f>IF(OR($A79="",$E79="",$E79=0),"",H79/G79)</f>
+        <v/>
+      </c>
+      <c r="J79" s="7" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="8">
+        <f>IF(PRODUCTOS!B80="","",PRODUCTOS!B80)</f>
+        <v/>
+      </c>
+      <c r="B80" s="10">
+        <f>IF($A80="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A80))</f>
+        <v/>
+      </c>
+      <c r="C80" s="9" t="n"/>
+      <c r="D80" s="10">
+        <f>IF($A80="","",B80+IF(C80="",0,C80))</f>
+        <v/>
+      </c>
+      <c r="E80" s="9" t="n"/>
+      <c r="F80" s="10">
+        <f>IF(OR($A80="",$E80=""),"",ROUND($E80-$E80/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G80" s="10">
+        <f>IF(OR($A80="",$E80=""),"",ROUND($E80/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H80" s="10">
+        <f>IF(OR($A80="",$E80=""),"",G80-D80)</f>
+        <v/>
+      </c>
+      <c r="I80" s="22">
+        <f>IF(OR($A80="",$E80="",$E80=0),"",H80/G80)</f>
+        <v/>
+      </c>
+      <c r="J80" s="7" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="8">
+        <f>IF(PRODUCTOS!B81="","",PRODUCTOS!B81)</f>
+        <v/>
+      </c>
+      <c r="B81" s="10">
+        <f>IF($A81="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A81))</f>
+        <v/>
+      </c>
+      <c r="C81" s="9" t="n"/>
+      <c r="D81" s="10">
+        <f>IF($A81="","",B81+IF(C81="",0,C81))</f>
+        <v/>
+      </c>
+      <c r="E81" s="9" t="n"/>
+      <c r="F81" s="10">
+        <f>IF(OR($A81="",$E81=""),"",ROUND($E81-$E81/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G81" s="10">
+        <f>IF(OR($A81="",$E81=""),"",ROUND($E81/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H81" s="10">
+        <f>IF(OR($A81="",$E81=""),"",G81-D81)</f>
+        <v/>
+      </c>
+      <c r="I81" s="22">
+        <f>IF(OR($A81="",$E81="",$E81=0),"",H81/G81)</f>
+        <v/>
+      </c>
+      <c r="J81" s="7" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="8">
+        <f>IF(PRODUCTOS!B82="","",PRODUCTOS!B82)</f>
+        <v/>
+      </c>
+      <c r="B82" s="10">
+        <f>IF($A82="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A82))</f>
+        <v/>
+      </c>
+      <c r="C82" s="9" t="n"/>
+      <c r="D82" s="10">
+        <f>IF($A82="","",B82+IF(C82="",0,C82))</f>
+        <v/>
+      </c>
+      <c r="E82" s="9" t="n"/>
+      <c r="F82" s="10">
+        <f>IF(OR($A82="",$E82=""),"",ROUND($E82-$E82/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G82" s="10">
+        <f>IF(OR($A82="",$E82=""),"",ROUND($E82/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H82" s="10">
+        <f>IF(OR($A82="",$E82=""),"",G82-D82)</f>
+        <v/>
+      </c>
+      <c r="I82" s="22">
+        <f>IF(OR($A82="",$E82="",$E82=0),"",H82/G82)</f>
+        <v/>
+      </c>
+      <c r="J82" s="7" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="8">
+        <f>IF(PRODUCTOS!B83="","",PRODUCTOS!B83)</f>
+        <v/>
+      </c>
+      <c r="B83" s="10">
+        <f>IF($A83="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A83))</f>
+        <v/>
+      </c>
+      <c r="C83" s="9" t="n"/>
+      <c r="D83" s="10">
+        <f>IF($A83="","",B83+IF(C83="",0,C83))</f>
+        <v/>
+      </c>
+      <c r="E83" s="9" t="n"/>
+      <c r="F83" s="10">
+        <f>IF(OR($A83="",$E83=""),"",ROUND($E83-$E83/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G83" s="10">
+        <f>IF(OR($A83="",$E83=""),"",ROUND($E83/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H83" s="10">
+        <f>IF(OR($A83="",$E83=""),"",G83-D83)</f>
+        <v/>
+      </c>
+      <c r="I83" s="22">
+        <f>IF(OR($A83="",$E83="",$E83=0),"",H83/G83)</f>
+        <v/>
+      </c>
+      <c r="J83" s="7" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="8">
+        <f>IF(PRODUCTOS!B84="","",PRODUCTOS!B84)</f>
+        <v/>
+      </c>
+      <c r="B84" s="10">
+        <f>IF($A84="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A84))</f>
+        <v/>
+      </c>
+      <c r="C84" s="9" t="n"/>
+      <c r="D84" s="10">
+        <f>IF($A84="","",B84+IF(C84="",0,C84))</f>
+        <v/>
+      </c>
+      <c r="E84" s="9" t="n"/>
+      <c r="F84" s="10">
+        <f>IF(OR($A84="",$E84=""),"",ROUND($E84-$E84/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G84" s="10">
+        <f>IF(OR($A84="",$E84=""),"",ROUND($E84/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H84" s="10">
+        <f>IF(OR($A84="",$E84=""),"",G84-D84)</f>
+        <v/>
+      </c>
+      <c r="I84" s="22">
+        <f>IF(OR($A84="",$E84="",$E84=0),"",H84/G84)</f>
+        <v/>
+      </c>
+      <c r="J84" s="7" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="8">
+        <f>IF(PRODUCTOS!B85="","",PRODUCTOS!B85)</f>
+        <v/>
+      </c>
+      <c r="B85" s="10">
+        <f>IF($A85="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A85))</f>
+        <v/>
+      </c>
+      <c r="C85" s="9" t="n"/>
+      <c r="D85" s="10">
+        <f>IF($A85="","",B85+IF(C85="",0,C85))</f>
+        <v/>
+      </c>
+      <c r="E85" s="9" t="n"/>
+      <c r="F85" s="10">
+        <f>IF(OR($A85="",$E85=""),"",ROUND($E85-$E85/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G85" s="10">
+        <f>IF(OR($A85="",$E85=""),"",ROUND($E85/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H85" s="10">
+        <f>IF(OR($A85="",$E85=""),"",G85-D85)</f>
+        <v/>
+      </c>
+      <c r="I85" s="22">
+        <f>IF(OR($A85="",$E85="",$E85=0),"",H85/G85)</f>
+        <v/>
+      </c>
+      <c r="J85" s="7" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="8">
+        <f>IF(PRODUCTOS!B86="","",PRODUCTOS!B86)</f>
+        <v/>
+      </c>
+      <c r="B86" s="10">
+        <f>IF($A86="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A86))</f>
+        <v/>
+      </c>
+      <c r="C86" s="9" t="n"/>
+      <c r="D86" s="10">
+        <f>IF($A86="","",B86+IF(C86="",0,C86))</f>
+        <v/>
+      </c>
+      <c r="E86" s="9" t="n"/>
+      <c r="F86" s="10">
+        <f>IF(OR($A86="",$E86=""),"",ROUND($E86-$E86/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G86" s="10">
+        <f>IF(OR($A86="",$E86=""),"",ROUND($E86/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H86" s="10">
+        <f>IF(OR($A86="",$E86=""),"",G86-D86)</f>
+        <v/>
+      </c>
+      <c r="I86" s="22">
+        <f>IF(OR($A86="",$E86="",$E86=0),"",H86/G86)</f>
+        <v/>
+      </c>
+      <c r="J86" s="7" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="8">
+        <f>IF(PRODUCTOS!B87="","",PRODUCTOS!B87)</f>
+        <v/>
+      </c>
+      <c r="B87" s="10">
+        <f>IF($A87="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A87))</f>
+        <v/>
+      </c>
+      <c r="C87" s="9" t="n"/>
+      <c r="D87" s="10">
+        <f>IF($A87="","",B87+IF(C87="",0,C87))</f>
+        <v/>
+      </c>
+      <c r="E87" s="9" t="n"/>
+      <c r="F87" s="10">
+        <f>IF(OR($A87="",$E87=""),"",ROUND($E87-$E87/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G87" s="10">
+        <f>IF(OR($A87="",$E87=""),"",ROUND($E87/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H87" s="10">
+        <f>IF(OR($A87="",$E87=""),"",G87-D87)</f>
+        <v/>
+      </c>
+      <c r="I87" s="22">
+        <f>IF(OR($A87="",$E87="",$E87=0),"",H87/G87)</f>
+        <v/>
+      </c>
+      <c r="J87" s="7" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="8">
+        <f>IF(PRODUCTOS!B88="","",PRODUCTOS!B88)</f>
+        <v/>
+      </c>
+      <c r="B88" s="10">
+        <f>IF($A88="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A88))</f>
+        <v/>
+      </c>
+      <c r="C88" s="9" t="n"/>
+      <c r="D88" s="10">
+        <f>IF($A88="","",B88+IF(C88="",0,C88))</f>
+        <v/>
+      </c>
+      <c r="E88" s="9" t="n"/>
+      <c r="F88" s="10">
+        <f>IF(OR($A88="",$E88=""),"",ROUND($E88-$E88/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G88" s="10">
+        <f>IF(OR($A88="",$E88=""),"",ROUND($E88/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H88" s="10">
+        <f>IF(OR($A88="",$E88=""),"",G88-D88)</f>
+        <v/>
+      </c>
+      <c r="I88" s="22">
+        <f>IF(OR($A88="",$E88="",$E88=0),"",H88/G88)</f>
+        <v/>
+      </c>
+      <c r="J88" s="7" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="8">
+        <f>IF(PRODUCTOS!B89="","",PRODUCTOS!B89)</f>
+        <v/>
+      </c>
+      <c r="B89" s="10">
+        <f>IF($A89="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A89))</f>
+        <v/>
+      </c>
+      <c r="C89" s="9" t="n"/>
+      <c r="D89" s="10">
+        <f>IF($A89="","",B89+IF(C89="",0,C89))</f>
+        <v/>
+      </c>
+      <c r="E89" s="9" t="n"/>
+      <c r="F89" s="10">
+        <f>IF(OR($A89="",$E89=""),"",ROUND($E89-$E89/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G89" s="10">
+        <f>IF(OR($A89="",$E89=""),"",ROUND($E89/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H89" s="10">
+        <f>IF(OR($A89="",$E89=""),"",G89-D89)</f>
+        <v/>
+      </c>
+      <c r="I89" s="22">
+        <f>IF(OR($A89="",$E89="",$E89=0),"",H89/G89)</f>
+        <v/>
+      </c>
+      <c r="J89" s="7" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="8">
+        <f>IF(PRODUCTOS!B90="","",PRODUCTOS!B90)</f>
+        <v/>
+      </c>
+      <c r="B90" s="10">
+        <f>IF($A90="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A90))</f>
+        <v/>
+      </c>
+      <c r="C90" s="9" t="n"/>
+      <c r="D90" s="10">
+        <f>IF($A90="","",B90+IF(C90="",0,C90))</f>
+        <v/>
+      </c>
+      <c r="E90" s="9" t="n"/>
+      <c r="F90" s="10">
+        <f>IF(OR($A90="",$E90=""),"",ROUND($E90-$E90/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G90" s="10">
+        <f>IF(OR($A90="",$E90=""),"",ROUND($E90/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H90" s="10">
+        <f>IF(OR($A90="",$E90=""),"",G90-D90)</f>
+        <v/>
+      </c>
+      <c r="I90" s="22">
+        <f>IF(OR($A90="",$E90="",$E90=0),"",H90/G90)</f>
+        <v/>
+      </c>
+      <c r="J90" s="7" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="8">
+        <f>IF(PRODUCTOS!B91="","",PRODUCTOS!B91)</f>
+        <v/>
+      </c>
+      <c r="B91" s="10">
+        <f>IF($A91="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A91))</f>
+        <v/>
+      </c>
+      <c r="C91" s="9" t="n"/>
+      <c r="D91" s="10">
+        <f>IF($A91="","",B91+IF(C91="",0,C91))</f>
+        <v/>
+      </c>
+      <c r="E91" s="9" t="n"/>
+      <c r="F91" s="10">
+        <f>IF(OR($A91="",$E91=""),"",ROUND($E91-$E91/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G91" s="10">
+        <f>IF(OR($A91="",$E91=""),"",ROUND($E91/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H91" s="10">
+        <f>IF(OR($A91="",$E91=""),"",G91-D91)</f>
+        <v/>
+      </c>
+      <c r="I91" s="22">
+        <f>IF(OR($A91="",$E91="",$E91=0),"",H91/G91)</f>
+        <v/>
+      </c>
+      <c r="J91" s="7" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="8">
+        <f>IF(PRODUCTOS!B92="","",PRODUCTOS!B92)</f>
+        <v/>
+      </c>
+      <c r="B92" s="10">
+        <f>IF($A92="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A92))</f>
+        <v/>
+      </c>
+      <c r="C92" s="9" t="n"/>
+      <c r="D92" s="10">
+        <f>IF($A92="","",B92+IF(C92="",0,C92))</f>
+        <v/>
+      </c>
+      <c r="E92" s="9" t="n"/>
+      <c r="F92" s="10">
+        <f>IF(OR($A92="",$E92=""),"",ROUND($E92-$E92/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G92" s="10">
+        <f>IF(OR($A92="",$E92=""),"",ROUND($E92/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H92" s="10">
+        <f>IF(OR($A92="",$E92=""),"",G92-D92)</f>
+        <v/>
+      </c>
+      <c r="I92" s="22">
+        <f>IF(OR($A92="",$E92="",$E92=0),"",H92/G92)</f>
+        <v/>
+      </c>
+      <c r="J92" s="7" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="8">
+        <f>IF(PRODUCTOS!B93="","",PRODUCTOS!B93)</f>
+        <v/>
+      </c>
+      <c r="B93" s="10">
+        <f>IF($A93="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A93))</f>
+        <v/>
+      </c>
+      <c r="C93" s="9" t="n"/>
+      <c r="D93" s="10">
+        <f>IF($A93="","",B93+IF(C93="",0,C93))</f>
+        <v/>
+      </c>
+      <c r="E93" s="9" t="n"/>
+      <c r="F93" s="10">
+        <f>IF(OR($A93="",$E93=""),"",ROUND($E93-$E93/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G93" s="10">
+        <f>IF(OR($A93="",$E93=""),"",ROUND($E93/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H93" s="10">
+        <f>IF(OR($A93="",$E93=""),"",G93-D93)</f>
+        <v/>
+      </c>
+      <c r="I93" s="22">
+        <f>IF(OR($A93="",$E93="",$E93=0),"",H93/G93)</f>
+        <v/>
+      </c>
+      <c r="J93" s="7" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="8">
+        <f>IF(PRODUCTOS!B94="","",PRODUCTOS!B94)</f>
+        <v/>
+      </c>
+      <c r="B94" s="10">
+        <f>IF($A94="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A94))</f>
+        <v/>
+      </c>
+      <c r="C94" s="9" t="n"/>
+      <c r="D94" s="10">
+        <f>IF($A94="","",B94+IF(C94="",0,C94))</f>
+        <v/>
+      </c>
+      <c r="E94" s="9" t="n"/>
+      <c r="F94" s="10">
+        <f>IF(OR($A94="",$E94=""),"",ROUND($E94-$E94/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G94" s="10">
+        <f>IF(OR($A94="",$E94=""),"",ROUND($E94/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H94" s="10">
+        <f>IF(OR($A94="",$E94=""),"",G94-D94)</f>
+        <v/>
+      </c>
+      <c r="I94" s="22">
+        <f>IF(OR($A94="",$E94="",$E94=0),"",H94/G94)</f>
+        <v/>
+      </c>
+      <c r="J94" s="7" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="8">
+        <f>IF(PRODUCTOS!B95="","",PRODUCTOS!B95)</f>
+        <v/>
+      </c>
+      <c r="B95" s="10">
+        <f>IF($A95="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A95))</f>
+        <v/>
+      </c>
+      <c r="C95" s="9" t="n"/>
+      <c r="D95" s="10">
+        <f>IF($A95="","",B95+IF(C95="",0,C95))</f>
+        <v/>
+      </c>
+      <c r="E95" s="9" t="n"/>
+      <c r="F95" s="10">
+        <f>IF(OR($A95="",$E95=""),"",ROUND($E95-$E95/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G95" s="10">
+        <f>IF(OR($A95="",$E95=""),"",ROUND($E95/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H95" s="10">
+        <f>IF(OR($A95="",$E95=""),"",G95-D95)</f>
+        <v/>
+      </c>
+      <c r="I95" s="22">
+        <f>IF(OR($A95="",$E95="",$E95=0),"",H95/G95)</f>
+        <v/>
+      </c>
+      <c r="J95" s="7" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="8">
+        <f>IF(PRODUCTOS!B96="","",PRODUCTOS!B96)</f>
+        <v/>
+      </c>
+      <c r="B96" s="10">
+        <f>IF($A96="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A96))</f>
+        <v/>
+      </c>
+      <c r="C96" s="9" t="n"/>
+      <c r="D96" s="10">
+        <f>IF($A96="","",B96+IF(C96="",0,C96))</f>
+        <v/>
+      </c>
+      <c r="E96" s="9" t="n"/>
+      <c r="F96" s="10">
+        <f>IF(OR($A96="",$E96=""),"",ROUND($E96-$E96/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G96" s="10">
+        <f>IF(OR($A96="",$E96=""),"",ROUND($E96/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H96" s="10">
+        <f>IF(OR($A96="",$E96=""),"",G96-D96)</f>
+        <v/>
+      </c>
+      <c r="I96" s="22">
+        <f>IF(OR($A96="",$E96="",$E96=0),"",H96/G96)</f>
+        <v/>
+      </c>
+      <c r="J96" s="7" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="8">
+        <f>IF(PRODUCTOS!B97="","",PRODUCTOS!B97)</f>
+        <v/>
+      </c>
+      <c r="B97" s="10">
+        <f>IF($A97="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A97))</f>
+        <v/>
+      </c>
+      <c r="C97" s="9" t="n"/>
+      <c r="D97" s="10">
+        <f>IF($A97="","",B97+IF(C97="",0,C97))</f>
+        <v/>
+      </c>
+      <c r="E97" s="9" t="n"/>
+      <c r="F97" s="10">
+        <f>IF(OR($A97="",$E97=""),"",ROUND($E97-$E97/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G97" s="10">
+        <f>IF(OR($A97="",$E97=""),"",ROUND($E97/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H97" s="10">
+        <f>IF(OR($A97="",$E97=""),"",G97-D97)</f>
+        <v/>
+      </c>
+      <c r="I97" s="22">
+        <f>IF(OR($A97="",$E97="",$E97=0),"",H97/G97)</f>
+        <v/>
+      </c>
+      <c r="J97" s="7" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="8">
+        <f>IF(PRODUCTOS!B98="","",PRODUCTOS!B98)</f>
+        <v/>
+      </c>
+      <c r="B98" s="10">
+        <f>IF($A98="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A98))</f>
+        <v/>
+      </c>
+      <c r="C98" s="9" t="n"/>
+      <c r="D98" s="10">
+        <f>IF($A98="","",B98+IF(C98="",0,C98))</f>
+        <v/>
+      </c>
+      <c r="E98" s="9" t="n"/>
+      <c r="F98" s="10">
+        <f>IF(OR($A98="",$E98=""),"",ROUND($E98-$E98/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G98" s="10">
+        <f>IF(OR($A98="",$E98=""),"",ROUND($E98/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H98" s="10">
+        <f>IF(OR($A98="",$E98=""),"",G98-D98)</f>
+        <v/>
+      </c>
+      <c r="I98" s="22">
+        <f>IF(OR($A98="",$E98="",$E98=0),"",H98/G98)</f>
+        <v/>
+      </c>
+      <c r="J98" s="7" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="8">
+        <f>IF(PRODUCTOS!B99="","",PRODUCTOS!B99)</f>
+        <v/>
+      </c>
+      <c r="B99" s="10">
+        <f>IF($A99="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A99))</f>
+        <v/>
+      </c>
+      <c r="C99" s="9" t="n"/>
+      <c r="D99" s="10">
+        <f>IF($A99="","",B99+IF(C99="",0,C99))</f>
+        <v/>
+      </c>
+      <c r="E99" s="9" t="n"/>
+      <c r="F99" s="10">
+        <f>IF(OR($A99="",$E99=""),"",ROUND($E99-$E99/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G99" s="10">
+        <f>IF(OR($A99="",$E99=""),"",ROUND($E99/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H99" s="10">
+        <f>IF(OR($A99="",$E99=""),"",G99-D99)</f>
+        <v/>
+      </c>
+      <c r="I99" s="22">
+        <f>IF(OR($A99="",$E99="",$E99=0),"",H99/G99)</f>
+        <v/>
+      </c>
+      <c r="J99" s="7" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="8">
+        <f>IF(PRODUCTOS!B100="","",PRODUCTOS!B100)</f>
+        <v/>
+      </c>
+      <c r="B100" s="10">
+        <f>IF($A100="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A100))</f>
+        <v/>
+      </c>
+      <c r="C100" s="9" t="n"/>
+      <c r="D100" s="10">
+        <f>IF($A100="","",B100+IF(C100="",0,C100))</f>
+        <v/>
+      </c>
+      <c r="E100" s="9" t="n"/>
+      <c r="F100" s="10">
+        <f>IF(OR($A100="",$E100=""),"",ROUND($E100-$E100/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G100" s="10">
+        <f>IF(OR($A100="",$E100=""),"",ROUND($E100/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H100" s="10">
+        <f>IF(OR($A100="",$E100=""),"",G100-D100)</f>
+        <v/>
+      </c>
+      <c r="I100" s="22">
+        <f>IF(OR($A100="",$E100="",$E100=0),"",H100/G100)</f>
+        <v/>
+      </c>
+      <c r="J100" s="7" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="8">
+        <f>IF(PRODUCTOS!B101="","",PRODUCTOS!B101)</f>
+        <v/>
+      </c>
+      <c r="B101" s="10">
+        <f>IF($A101="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A101))</f>
+        <v/>
+      </c>
+      <c r="C101" s="9" t="n"/>
+      <c r="D101" s="10">
+        <f>IF($A101="","",B101+IF(C101="",0,C101))</f>
+        <v/>
+      </c>
+      <c r="E101" s="9" t="n"/>
+      <c r="F101" s="10">
+        <f>IF(OR($A101="",$E101=""),"",ROUND($E101-$E101/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G101" s="10">
+        <f>IF(OR($A101="",$E101=""),"",ROUND($E101/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H101" s="10">
+        <f>IF(OR($A101="",$E101=""),"",G101-D101)</f>
+        <v/>
+      </c>
+      <c r="I101" s="22">
+        <f>IF(OR($A101="",$E101="",$E101=0),"",H101/G101)</f>
+        <v/>
+      </c>
+      <c r="J101" s="7" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="8">
+        <f>IF(PRODUCTOS!B102="","",PRODUCTOS!B102)</f>
+        <v/>
+      </c>
+      <c r="B102" s="10">
+        <f>IF($A102="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A102))</f>
+        <v/>
+      </c>
+      <c r="C102" s="9" t="n"/>
+      <c r="D102" s="10">
+        <f>IF($A102="","",B102+IF(C102="",0,C102))</f>
+        <v/>
+      </c>
+      <c r="E102" s="9" t="n"/>
+      <c r="F102" s="10">
+        <f>IF(OR($A102="",$E102=""),"",ROUND($E102-$E102/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G102" s="10">
+        <f>IF(OR($A102="",$E102=""),"",ROUND($E102/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H102" s="10">
+        <f>IF(OR($A102="",$E102=""),"",G102-D102)</f>
+        <v/>
+      </c>
+      <c r="I102" s="22">
+        <f>IF(OR($A102="",$E102="",$E102=0),"",H102/G102)</f>
+        <v/>
+      </c>
+      <c r="J102" s="7" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="8">
+        <f>IF(PRODUCTOS!B103="","",PRODUCTOS!B103)</f>
+        <v/>
+      </c>
+      <c r="B103" s="10">
+        <f>IF($A103="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A103))</f>
+        <v/>
+      </c>
+      <c r="C103" s="9" t="n"/>
+      <c r="D103" s="10">
+        <f>IF($A103="","",B103+IF(C103="",0,C103))</f>
+        <v/>
+      </c>
+      <c r="E103" s="9" t="n"/>
+      <c r="F103" s="10">
+        <f>IF(OR($A103="",$E103=""),"",ROUND($E103-$E103/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G103" s="10">
+        <f>IF(OR($A103="",$E103=""),"",ROUND($E103/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H103" s="10">
+        <f>IF(OR($A103="",$E103=""),"",G103-D103)</f>
+        <v/>
+      </c>
+      <c r="I103" s="22">
+        <f>IF(OR($A103="",$E103="",$E103=0),"",H103/G103)</f>
+        <v/>
+      </c>
+      <c r="J103" s="7" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="8">
+        <f>IF(PRODUCTOS!B104="","",PRODUCTOS!B104)</f>
+        <v/>
+      </c>
+      <c r="B104" s="10">
+        <f>IF($A104="","",SUMIFS(RECETAS!$F:$F,RECETAS!$A:$A,$A104))</f>
+        <v/>
+      </c>
+      <c r="C104" s="9" t="n"/>
+      <c r="D104" s="10">
+        <f>IF($A104="","",B104+IF(C104="",0,C104))</f>
+        <v/>
+      </c>
+      <c r="E104" s="9" t="n"/>
+      <c r="F104" s="10">
+        <f>IF(OR($A104="",$E104=""),"",ROUND($E104-$E104/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="G104" s="10">
+        <f>IF(OR($A104="",$E104=""),"",ROUND($E104/(1+$B$3),0))</f>
+        <v/>
+      </c>
+      <c r="H104" s="10">
+        <f>IF(OR($A104="",$E104=""),"",G104-D104)</f>
+        <v/>
+      </c>
+      <c r="I104" s="22">
+        <f>IF(OR($A104="",$E104="",$E104=0),"",H104/G104)</f>
+        <v/>
+      </c>
+      <c r="J104" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>